--- a/Planilhas/previsoes_icms_estados_com_pib.xlsx
+++ b/Planilhas/previsoes_icms_estados_com_pib.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="previsoes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="modelos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="pib_tratado" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="previsoes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pib_tratado" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,21 +495,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>199790275.1609515</v>
+        <v>201144841.727717</v>
       </c>
       <c r="G2" t="n">
-        <v>151613032.0343603</v>
+        <v>152218491.6984012</v>
       </c>
       <c r="H2" t="n">
-        <v>263276537.0713149</v>
+        <v>265797189.9618638</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7.296692260048432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -533,21 +533,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>202306103.2204053</v>
+        <v>202330371.1512801</v>
       </c>
       <c r="G3" t="n">
-        <v>152360914.3163261</v>
+        <v>152193070.5191996</v>
       </c>
       <c r="H3" t="n">
-        <v>268623745.0324863</v>
+        <v>268984513.8846211</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7.369960553576971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -571,21 +571,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>208205943.9160616</v>
+        <v>205094428.9025959</v>
       </c>
       <c r="G4" t="n">
-        <v>156711068.7691956</v>
+        <v>154127495.3525468</v>
       </c>
       <c r="H4" t="n">
-        <v>276621909.4952618</v>
+        <v>272915125.6929637</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6.339104426528941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -609,21 +609,21 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>208773025.612404</v>
+        <v>206351750.4558651</v>
       </c>
       <c r="G5" t="n">
-        <v>157120347.386218</v>
+        <v>154989277.5375612</v>
       </c>
       <c r="H5" t="n">
-        <v>277406312.7305731</v>
+        <v>274735424.2352684</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6.365548028661205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -647,21 +647,21 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>212874712.4604037</v>
+        <v>208160276.0869583</v>
       </c>
       <c r="G6" t="n">
-        <v>160198214.0224706</v>
+        <v>156272395.6723575</v>
       </c>
       <c r="H6" t="n">
-        <v>282872337.1331921</v>
+        <v>277276740.7459877</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7.430178721321767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -685,21 +685,21 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>209813606.5080492</v>
+        <v>208078551.3091615</v>
       </c>
       <c r="G7" t="n">
-        <v>157887240.8888706</v>
+        <v>156137274.7077459</v>
       </c>
       <c r="H7" t="n">
-        <v>278817650.0398745</v>
+        <v>277298829.481692</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7.21752999809735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -723,21 +723,21 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>215530360.2187219</v>
+        <v>211263032.6695561</v>
       </c>
       <c r="G8" t="n">
-        <v>162181959.4539155</v>
+        <v>158452304.8760527</v>
       </c>
       <c r="H8" t="n">
-        <v>286427271.7657715</v>
+        <v>281675100.9564094</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.231297900402511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -761,21 +761,21 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>224300759.5565793</v>
+        <v>215167199.8416976</v>
       </c>
       <c r="G9" t="n">
-        <v>168774164.8231046</v>
+        <v>161304808.6534995</v>
       </c>
       <c r="H9" t="n">
-        <v>298095569.2501288</v>
+        <v>287015150.2251116</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7.311710033254837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -799,13 +799,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>801596891.4868338</v>
+        <v>812763808.0149031</v>
       </c>
       <c r="G10" t="n">
-        <v>689550313.2516267</v>
+        <v>698878439.5212696</v>
       </c>
       <c r="H10" t="n">
-        <v>931850169.7306552</v>
+        <v>945207306.8263284</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>814170693.5373673</v>
+        <v>823899992.1041374</v>
       </c>
       <c r="G11" t="n">
-        <v>686366754.2690977</v>
+        <v>697772132.379402</v>
       </c>
       <c r="H11" t="n">
-        <v>965772182.4260018</v>
+        <v>972826465.1017982</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>792518184.8641464</v>
+        <v>794851996.8900816</v>
       </c>
       <c r="G12" t="n">
-        <v>662656954.8019634</v>
+        <v>664473794.9145648</v>
       </c>
       <c r="H12" t="n">
-        <v>947828388.1108075</v>
+        <v>950812058.79817</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>812010565.2655433</v>
+        <v>809901839.1283407</v>
       </c>
       <c r="G13" t="n">
-        <v>675483589.067592</v>
+        <v>669432375.7467784</v>
       </c>
       <c r="H13" t="n">
-        <v>976132016.7867004</v>
+        <v>979846527.876308</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>823441532.4767466</v>
+        <v>823848900.1751066</v>
       </c>
       <c r="G14" t="n">
-        <v>682181453.9942293</v>
+        <v>674199722.0185164</v>
       </c>
       <c r="H14" t="n">
-        <v>993952493.7794464</v>
+        <v>1006715055.12886</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>862575976.046383</v>
+        <v>856412782.7027391</v>
       </c>
       <c r="G15" t="n">
-        <v>711952091.2513782</v>
+        <v>694658160.6049932</v>
       </c>
       <c r="H15" t="n">
-        <v>1045066548.150167</v>
+        <v>1055832776.423266</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>902191176.2434137</v>
+        <v>893014486.7291858</v>
       </c>
       <c r="G16" t="n">
-        <v>742024014.8633182</v>
+        <v>718616108.2178848</v>
       </c>
       <c r="H16" t="n">
-        <v>1096930695.216656</v>
+        <v>1109736985.281154</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>968530750.4849898</v>
+        <v>947948288.832033</v>
       </c>
       <c r="G17" t="n">
-        <v>793860061.4851458</v>
+        <v>757387047.1836559</v>
       </c>
       <c r="H17" t="n">
-        <v>1181633716.249838</v>
+        <v>1186455408.289654</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1103,21 +1103,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1547201151.88338</v>
+        <v>1496970306.27053</v>
       </c>
       <c r="G18" t="n">
-        <v>1312154477.089787</v>
+        <v>1271660856.496703</v>
       </c>
       <c r="H18" t="n">
-        <v>1824351816.943468</v>
+        <v>1762199478.270639</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7.296692260048432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1501238129.412555</v>
+        <v>1474665432.865554</v>
       </c>
       <c r="G19" t="n">
-        <v>1261880711.465823</v>
+        <v>1241449234.848161</v>
       </c>
       <c r="H19" t="n">
-        <v>1785997599.237531</v>
+        <v>1751693164.605742</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7.369960553576971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1179,21 +1179,21 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1496118408.576743</v>
+        <v>1464880227.654236</v>
       </c>
       <c r="G20" t="n">
-        <v>1246964951.7249</v>
+        <v>1228550602.732646</v>
       </c>
       <c r="H20" t="n">
-        <v>1795054696.113085</v>
+        <v>1746671302.426854</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>6.339104426528941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1217,21 +1217,21 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1553976818.855672</v>
+        <v>1549826754.819362</v>
       </c>
       <c r="G21" t="n">
-        <v>1284742682.823263</v>
+        <v>1295796026.319239</v>
       </c>
       <c r="H21" t="n">
-        <v>1879632385.400397</v>
+        <v>1853658231.054147</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6.365548028661205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1255,21 +1255,21 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1629485905.007175</v>
+        <v>1553472564.063539</v>
       </c>
       <c r="G22" t="n">
-        <v>1336747069.374565</v>
+        <v>1295049019.80447</v>
       </c>
       <c r="H22" t="n">
-        <v>1986332624.510167</v>
+        <v>1863463830.629755</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7.430178721321767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1578566882.232506</v>
+        <v>1538902481.233127</v>
       </c>
       <c r="G23" t="n">
-        <v>1285334078.71098</v>
+        <v>1279235168.765736</v>
       </c>
       <c r="H23" t="n">
-        <v>1938697061.685528</v>
+        <v>1851278720.730012</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7.21752999809735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1331,21 +1331,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1593024287.445176</v>
+        <v>1516918318.821532</v>
       </c>
       <c r="G24" t="n">
-        <v>1287786281.575021</v>
+        <v>1257414286.887153</v>
       </c>
       <c r="H24" t="n">
-        <v>1970611441.276154</v>
+        <v>1829978559.948438</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7.231297900402511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1651707314.933842</v>
+        <v>1591238677.12587</v>
       </c>
       <c r="G25" t="n">
-        <v>1325945239.456838</v>
+        <v>1315366357.464474</v>
       </c>
       <c r="H25" t="n">
-        <v>2057503562.759138</v>
+        <v>1924969810.283198</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>7.311710033254837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1407,13 +1407,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>140136551.0001003</v>
+        <v>145670889.4184657</v>
       </c>
       <c r="G26" t="n">
-        <v>115323734.7655242</v>
+        <v>118952796.6946274</v>
       </c>
       <c r="H26" t="n">
-        <v>170288041.4524566</v>
+        <v>178390156.5462335</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>146539016.452551</v>
+        <v>143673525.272121</v>
       </c>
       <c r="G27" t="n">
-        <v>119081204.7528789</v>
+        <v>114016567.7201367</v>
       </c>
       <c r="H27" t="n">
-        <v>180328065.9399094</v>
+        <v>181044582.1767458</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>146568520.8198806</v>
+        <v>142317442.8640734</v>
       </c>
       <c r="G28" t="n">
-        <v>117697626.0903696</v>
+        <v>108697764.7277297</v>
       </c>
       <c r="H28" t="n">
-        <v>182521364.3547356</v>
+        <v>186335520.2758992</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>149310674.2977044</v>
+        <v>139760933.6346915</v>
       </c>
       <c r="G29" t="n">
-        <v>118555214.6569154</v>
+        <v>104117753.20292</v>
       </c>
       <c r="H29" t="n">
-        <v>188044680.478631</v>
+        <v>187606032.3004822</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>159312560.0398339</v>
+        <v>149302249.5191127</v>
       </c>
       <c r="G30" t="n">
-        <v>125144317.3795906</v>
+        <v>108724213.1557895</v>
       </c>
       <c r="H30" t="n">
-        <v>202809782.4806618</v>
+        <v>205024815.2132099</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>153392333.7007306</v>
+        <v>146828099.2450211</v>
       </c>
       <c r="G31" t="n">
-        <v>119260138.2320812</v>
+        <v>104958211.9925798</v>
       </c>
       <c r="H31" t="n">
-        <v>197293147.4586107</v>
+        <v>205400704.896058</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>156895205.8618486</v>
+        <v>142316693.8669907</v>
       </c>
       <c r="G32" t="n">
-        <v>120783488.8513056</v>
+        <v>100101516.7021672</v>
       </c>
       <c r="H32" t="n">
-        <v>203803565.0115744</v>
+        <v>202335009.7031273</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>157710510.265792</v>
+        <v>145019117.6770089</v>
       </c>
       <c r="G33" t="n">
-        <v>120260016.4574137</v>
+        <v>100593609.7327695</v>
       </c>
       <c r="H33" t="n">
-        <v>206823562.6518837</v>
+        <v>209064418.1840829</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3530026935.116783</v>
+        <v>3509275303.644835</v>
       </c>
       <c r="G34" t="n">
-        <v>3046301174.604792</v>
+        <v>3061336679.133401</v>
       </c>
       <c r="H34" t="n">
-        <v>4090564080.311795</v>
+        <v>4022756869.805534</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1.641478178511924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3666062415.975138</v>
+        <v>3674458918.388084</v>
       </c>
       <c r="G35" t="n">
-        <v>3097107087.075675</v>
+        <v>3142967817.088032</v>
       </c>
       <c r="H35" t="n">
-        <v>4339537917.145668</v>
+        <v>4295827742.655998</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1.801993558891857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1787,21 +1787,21 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3727090516.31464</v>
+        <v>3704190890.712381</v>
       </c>
       <c r="G36" t="n">
-        <v>3127759936.227486</v>
+        <v>3148444869.22049</v>
       </c>
       <c r="H36" t="n">
-        <v>4441262756.743812</v>
+        <v>4358034116.771343</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>-2.238291510711132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3828420227.956456</v>
+        <v>3829521345.141211</v>
       </c>
       <c r="G37" t="n">
-        <v>3204590049.20303</v>
+        <v>3246628521.599275</v>
       </c>
       <c r="H37" t="n">
-        <v>4573689993.661203</v>
+        <v>4517065514.371849</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1.721493938411056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3815380030.709611</v>
+        <v>3791982288.848207</v>
       </c>
       <c r="G38" t="n">
-        <v>3189823300.319758</v>
+        <v>3210581060.125864</v>
       </c>
       <c r="H38" t="n">
-        <v>4563614786.21039</v>
+        <v>4478668941.74439</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1.075411853094543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3904642542.137632</v>
+        <v>3908269144.672167</v>
       </c>
       <c r="G39" t="n">
-        <v>3262150330.834144</v>
+        <v>3306268386.007235</v>
       </c>
       <c r="H39" t="n">
-        <v>4673675899.532352</v>
+        <v>4619881365.90527</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0.7603971048866009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1939,21 +1939,21 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4036136703.183482</v>
+        <v>4140268975.976509</v>
       </c>
       <c r="G40" t="n">
-        <v>3370329738.3381</v>
+        <v>3500308539.433388</v>
       </c>
       <c r="H40" t="n">
-        <v>4833473503.045898</v>
+        <v>4897233201.10758</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>-0.2119867351621618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1977,21 +1977,21 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4023122456.361246</v>
+        <v>3978665829.92912</v>
       </c>
       <c r="G41" t="n">
-        <v>3358102542.093516</v>
+        <v>3361860451.566027</v>
       </c>
       <c r="H41" t="n">
-        <v>4819839208.598953</v>
+        <v>4708637379.303391</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>-0.2854178679703168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1829940048.499526</v>
+        <v>1933630915.514416</v>
       </c>
       <c r="G42" t="n">
-        <v>1624513576.975134</v>
+        <v>1707702491.396431</v>
       </c>
       <c r="H42" t="n">
-        <v>2061343548.348631</v>
+        <v>2189449588.713607</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1958772548.358034</v>
+        <v>2052791531.901081</v>
       </c>
       <c r="G43" t="n">
-        <v>1692172606.238481</v>
+        <v>1781608282.582524</v>
       </c>
       <c r="H43" t="n">
-        <v>2267375019.579002</v>
+        <v>2365252291.786873</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1986170430.254234</v>
+        <v>2017906435.684634</v>
       </c>
       <c r="G44" t="n">
-        <v>1691880028.185815</v>
+        <v>1725040497.169393</v>
       </c>
       <c r="H44" t="n">
-        <v>2331650538.038643</v>
+        <v>2360493211.526972</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2055359102.470725</v>
+        <v>2092404863.532368</v>
       </c>
       <c r="G45" t="n">
-        <v>1735005644.855289</v>
+        <v>1764840223.481233</v>
       </c>
       <c r="H45" t="n">
-        <v>2434862994.616721</v>
+        <v>2480767411.509798</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2093703420.229436</v>
+        <v>2117285997.169888</v>
       </c>
       <c r="G46" t="n">
-        <v>1755400504.53564</v>
+        <v>1764272787.325152</v>
       </c>
       <c r="H46" t="n">
-        <v>2497204484.420518</v>
+        <v>2540933593.726341</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2098040613.927634</v>
+        <v>2164025913.170582</v>
       </c>
       <c r="G47" t="n">
-        <v>1749141633.806016</v>
+        <v>1783325014.108567</v>
       </c>
       <c r="H47" t="n">
-        <v>2516534014.52224</v>
+        <v>2625998130.360255</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2243,13 +2243,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2148570900.289603</v>
+        <v>2227540591.079204</v>
       </c>
       <c r="G48" t="n">
-        <v>1782329276.960636</v>
+        <v>1816993043.64883</v>
       </c>
       <c r="H48" t="n">
-        <v>2590069620.268731</v>
+        <v>2730850897.998529</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2188864659.875579</v>
+        <v>2246802442.494786</v>
       </c>
       <c r="G49" t="n">
-        <v>1807378483.214914</v>
+        <v>1815401171.950237</v>
       </c>
       <c r="H49" t="n">
-        <v>2650871714.888356</v>
+        <v>2780719376.851274</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1160983309.211747</v>
+        <v>1157954058.574419</v>
       </c>
       <c r="G50" t="n">
-        <v>1037473587.292596</v>
+        <v>1029507149.676434</v>
       </c>
       <c r="H50" t="n">
-        <v>1299196683.923018</v>
+        <v>1302426702.12673</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1220975948.9892</v>
+        <v>1231262045.685788</v>
       </c>
       <c r="G51" t="n">
-        <v>1074554823.955683</v>
+        <v>1083589884.528877</v>
       </c>
       <c r="H51" t="n">
-        <v>1387348727.840768</v>
+        <v>1399059041.424589</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1214612244.944551</v>
+        <v>1210910392.209627</v>
       </c>
       <c r="G52" t="n">
-        <v>1054487076.880888</v>
+        <v>1048553886.072649</v>
       </c>
       <c r="H52" t="n">
-        <v>1399052618.011255</v>
+        <v>1398405935.486351</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1202113279.10846</v>
+        <v>1215982486.229436</v>
       </c>
       <c r="G53" t="n">
-        <v>1030750199.921389</v>
+        <v>1037944955.156128</v>
       </c>
       <c r="H53" t="n">
-        <v>1401965612.928432</v>
+        <v>1424558594.819037</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1218259348.770742</v>
+        <v>1222171901.219644</v>
       </c>
       <c r="G54" t="n">
-        <v>1032658278.77293</v>
+        <v>1029788330.033626</v>
       </c>
       <c r="H54" t="n">
-        <v>1437218750.263523</v>
+        <v>1450496293.818035</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2509,13 +2509,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1248495165.751487</v>
+        <v>1262814159.576966</v>
       </c>
       <c r="G55" t="n">
-        <v>1046978482.190571</v>
+        <v>1051466557.399026</v>
       </c>
       <c r="H55" t="n">
-        <v>1488798676.782271</v>
+        <v>1516643197.452545</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1271224039.686902</v>
+        <v>1280231626.175827</v>
       </c>
       <c r="G56" t="n">
-        <v>1055299780.925767</v>
+        <v>1054311489.324948</v>
       </c>
       <c r="H56" t="n">
-        <v>1531328432.249112</v>
+        <v>1554562416.568383</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1273256553.295514</v>
+        <v>1301856031.347813</v>
       </c>
       <c r="G57" t="n">
-        <v>1046886628.596642</v>
+        <v>1061179295.131924</v>
       </c>
       <c r="H57" t="n">
-        <v>1548574799.052669</v>
+        <v>1597118539.846727</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2029995154.796231</v>
+        <v>2128307541.277436</v>
       </c>
       <c r="G58" t="n">
-        <v>1784183220.925698</v>
+        <v>1860580023.404764</v>
       </c>
       <c r="H58" t="n">
-        <v>2309673289.247791</v>
+        <v>2434559617.5806</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2661,13 +2661,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2140095100.424424</v>
+        <v>2156567374.633869</v>
       </c>
       <c r="G59" t="n">
-        <v>1859007569.082811</v>
+        <v>1860909643.843592</v>
       </c>
       <c r="H59" t="n">
-        <v>2463683911.2604</v>
+        <v>2499198634.775903</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2699,13 +2699,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2102458174.369939</v>
+        <v>2132312548.768114</v>
       </c>
       <c r="G60" t="n">
-        <v>1806642853.091123</v>
+        <v>1831974557.622239</v>
       </c>
       <c r="H60" t="n">
-        <v>2446709579.268473</v>
+        <v>2481888619.422371</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2147610465.425344</v>
+        <v>2120066105.416293</v>
       </c>
       <c r="G61" t="n">
-        <v>1826886239.649811</v>
+        <v>1804183131.80246</v>
       </c>
       <c r="H61" t="n">
-        <v>2524640347.659834</v>
+        <v>2491255024.008911</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2150197265.971653</v>
+        <v>2151281741.612897</v>
       </c>
       <c r="G62" t="n">
-        <v>1811773479.118177</v>
+        <v>1822469822.854725</v>
       </c>
       <c r="H62" t="n">
-        <v>2551835721.120189</v>
+        <v>2539418251.956391</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2813,13 +2813,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2161322279.877908</v>
+        <v>2173751598.986602</v>
       </c>
       <c r="G63" t="n">
-        <v>1804813533.095415</v>
+        <v>1827810300.24447</v>
       </c>
       <c r="H63" t="n">
-        <v>2588252975.632846</v>
+        <v>2585167625.691141</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2851,13 +2851,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2216788527.891916</v>
+        <v>2200723251.066004</v>
       </c>
       <c r="G64" t="n">
-        <v>1835315584.459988</v>
+        <v>1842230572.388456</v>
       </c>
       <c r="H64" t="n">
-        <v>2677551162.86397</v>
+        <v>2628977555.997957</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2221799623.709804</v>
+        <v>2210862309.633856</v>
       </c>
       <c r="G65" t="n">
-        <v>1824429798.061938</v>
+        <v>1839401680.30488</v>
       </c>
       <c r="H65" t="n">
-        <v>2705718561.032535</v>
+        <v>2657338092.324337</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2828096475.013487</v>
+        <v>2882119703.238029</v>
       </c>
       <c r="G66" t="n">
-        <v>2565366474.933987</v>
+        <v>2603033772.308602</v>
       </c>
       <c r="H66" t="n">
-        <v>3117733762.45962</v>
+        <v>3191128010.769455</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2932532919.206392</v>
+        <v>3000411518.924531</v>
       </c>
       <c r="G67" t="n">
-        <v>2624597508.767952</v>
+        <v>2675042319.167103</v>
       </c>
       <c r="H67" t="n">
-        <v>3276597380.550776</v>
+        <v>3365355836.949152</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2908278870.02498</v>
+        <v>2875723549.133305</v>
       </c>
       <c r="G68" t="n">
-        <v>2571903162.717882</v>
+        <v>2530450071.264087</v>
       </c>
       <c r="H68" t="n">
-        <v>3288648697.369933</v>
+        <v>3268108715.106431</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3041,13 +3041,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2940077799.576092</v>
+        <v>2986672783.656042</v>
       </c>
       <c r="G69" t="n">
-        <v>2571815220.409141</v>
+        <v>2597405622.009667</v>
       </c>
       <c r="H69" t="n">
-        <v>3361072521.448506</v>
+        <v>3434278512.776134</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3079,13 +3079,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2988298691.297549</v>
+        <v>3036479702.933442</v>
       </c>
       <c r="G70" t="n">
-        <v>2587768503.788194</v>
+        <v>2612660274.846903</v>
       </c>
       <c r="H70" t="n">
-        <v>3450822225.921004</v>
+        <v>3529050093.153442</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3036953739.596653</v>
+        <v>3094003394.864051</v>
       </c>
       <c r="G71" t="n">
-        <v>2605238481.003703</v>
+        <v>2636088645.438329</v>
       </c>
       <c r="H71" t="n">
-        <v>3540208730.87088</v>
+        <v>3631462479.077026</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3045812634.82175</v>
+        <v>3101155121.558821</v>
       </c>
       <c r="G72" t="n">
-        <v>2589749085.59434</v>
+        <v>2618128669.343953</v>
       </c>
       <c r="H72" t="n">
-        <v>3582190513.375843</v>
+        <v>3673296580.332073</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3193,13 +3193,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3002379276.178881</v>
+        <v>3062991075.61414</v>
       </c>
       <c r="G73" t="n">
-        <v>2531427637.895275</v>
+        <v>2563869198.405659</v>
       </c>
       <c r="H73" t="n">
-        <v>3560947657.790146</v>
+        <v>3659279629.056742</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3231,16 +3231,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1424347984.360333</v>
+        <v>1408499788.415067</v>
       </c>
       <c r="G74" t="n">
-        <v>1114110429.151695</v>
+        <v>1104384844.36908</v>
       </c>
       <c r="H74" t="n">
-        <v>1820974947.785101</v>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+        <v>1796358999.383631</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3263,16 +3269,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1440688813.158811</v>
+        <v>1499219511.379821</v>
       </c>
       <c r="G75" t="n">
-        <v>1114381863.752934</v>
+        <v>1156773063.812278</v>
       </c>
       <c r="H75" t="n">
-        <v>1862543104.722596</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+        <v>1943042428.645884</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3295,16 +3307,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1423169106.952244</v>
+        <v>1520154187.705391</v>
       </c>
       <c r="G76" t="n">
-        <v>1086589611.349072</v>
+        <v>1168468791.906185</v>
       </c>
       <c r="H76" t="n">
-        <v>1864006691.973218</v>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+        <v>1977689751.24136</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3327,16 +3345,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1437309876.675672</v>
+        <v>1537997138.084643</v>
       </c>
       <c r="G77" t="n">
-        <v>1095746176.772727</v>
+        <v>1180002525.561687</v>
       </c>
       <c r="H77" t="n">
-        <v>1885345096.68467</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+        <v>2004601808.483921</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3359,16 +3383,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1440764683.257871</v>
+        <v>1684036249.54192</v>
       </c>
       <c r="G78" t="n">
-        <v>1096458415.7864</v>
+        <v>1290239858.422942</v>
       </c>
       <c r="H78" t="n">
-        <v>1893188873.04481</v>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+        <v>2198023934.276553</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3391,16 +3421,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1454412437.610426</v>
+        <v>1556491453.146218</v>
       </c>
       <c r="G79" t="n">
-        <v>1106474743.529784</v>
+        <v>1190997910.031682</v>
       </c>
       <c r="H79" t="n">
-        <v>1911761249.902368</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+        <v>2034147686.835804</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3423,16 +3459,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1464713280.803406</v>
+        <v>1623585351.178072</v>
       </c>
       <c r="G80" t="n">
-        <v>1113897164.600176</v>
+        <v>1240799414.817153</v>
       </c>
       <c r="H80" t="n">
-        <v>1926017107.451695</v>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+        <v>2124460538.167222</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3455,16 +3497,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1478383494.964889</v>
+        <v>1559411329.465246</v>
       </c>
       <c r="G81" t="n">
-        <v>1124138540.719923</v>
+        <v>1190298193.913932</v>
       </c>
       <c r="H81" t="n">
-        <v>1944260141.44563</v>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+        <v>2042986964.861683</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3487,13 +3535,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>7593403878.76088</v>
+        <v>7502093075.503323</v>
       </c>
       <c r="G82" t="n">
-        <v>6750986182.160496</v>
+        <v>6720405384.745891</v>
       </c>
       <c r="H82" t="n">
-        <v>8540942154.251028</v>
+        <v>8374703204.848852</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3525,13 +3573,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>8108688462.25431</v>
+        <v>7958113645.739474</v>
       </c>
       <c r="G83" t="n">
-        <v>6991302693.626983</v>
+        <v>6982966779.680179</v>
       </c>
       <c r="H83" t="n">
-        <v>9404660541.708805</v>
+        <v>9069436358.023951</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3563,13 +3611,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8014367346.824121</v>
+        <v>7883503997.032608</v>
       </c>
       <c r="G84" t="n">
-        <v>6841942124.406405</v>
+        <v>6854354301.496282</v>
       </c>
       <c r="H84" t="n">
-        <v>9387697645.193571</v>
+        <v>9067175774.333996</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3601,13 +3649,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>8118166166.123243</v>
+        <v>8035665341.97107</v>
       </c>
       <c r="G85" t="n">
-        <v>6881089850.565547</v>
+        <v>6949661887.696855</v>
       </c>
       <c r="H85" t="n">
-        <v>9577642979.82122</v>
+        <v>9291375398.056152</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3639,13 +3687,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>8326516790.086038</v>
+        <v>8181701896.306039</v>
       </c>
       <c r="G86" t="n">
-        <v>7039627120.891569</v>
+        <v>7049553066.264688</v>
       </c>
       <c r="H86" t="n">
-        <v>9848658269.105017</v>
+        <v>9495672320.044983</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3677,13 +3725,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>8083430248.853286</v>
+        <v>8031347472.1318</v>
       </c>
       <c r="G87" t="n">
-        <v>6815919571.105204</v>
+        <v>6899134654.348756</v>
       </c>
       <c r="H87" t="n">
-        <v>9586651354.438017</v>
+        <v>9349367051.048893</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3715,13 +3763,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>8414743675.287252</v>
+        <v>8266068714.1381</v>
       </c>
       <c r="G88" t="n">
-        <v>7088022084.301569</v>
+        <v>7081898053.3889</v>
       </c>
       <c r="H88" t="n">
-        <v>9989798321.538948</v>
+        <v>9648245635.808857</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3753,13 +3801,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>8560083168.560143</v>
+        <v>8449192922.082244</v>
       </c>
       <c r="G89" t="n">
-        <v>7200220829.762348</v>
+        <v>7220955554.935182</v>
       </c>
       <c r="H89" t="n">
-        <v>10176774516.38455</v>
+        <v>9886345441.604855</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -3791,16 +3839,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1480586405.835367</v>
+        <v>1491892776.79771</v>
       </c>
       <c r="G90" t="n">
-        <v>1341732063.96767</v>
+        <v>1352152952.862457</v>
       </c>
       <c r="H90" t="n">
-        <v>1633810627.3335</v>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+        <v>1646074175.816696</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1.641478178511924</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3823,16 +3877,22 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1503001776.850226</v>
+        <v>1511014659.146811</v>
       </c>
       <c r="G91" t="n">
-        <v>1325136502.406708</v>
+        <v>1339512959.721898</v>
       </c>
       <c r="H91" t="n">
-        <v>1704740860.365799</v>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+        <v>1704474214.740386</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>1.801993558891857</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3855,16 +3915,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1528384536.870561</v>
+        <v>1540582122.393147</v>
       </c>
       <c r="G92" t="n">
-        <v>1337459604.143246</v>
+        <v>1360245675.254028</v>
       </c>
       <c r="H92" t="n">
-        <v>1746564371.221826</v>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+        <v>1744826922.823435</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>-2.238291510711132</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3887,16 +3953,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1588046108.564927</v>
+        <v>1583647003.604861</v>
       </c>
       <c r="G93" t="n">
-        <v>1379847878.144205</v>
+        <v>1392835321.933887</v>
       </c>
       <c r="H93" t="n">
-        <v>1827658311.378475</v>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+        <v>1800598959.929089</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>1.721493938411056</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3919,16 +3991,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1583059945.011347</v>
+        <v>1576724187.102649</v>
       </c>
       <c r="G94" t="n">
-        <v>1366260956.200724</v>
+        <v>1381515648.254139</v>
       </c>
       <c r="H94" t="n">
-        <v>1834260708.487339</v>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+        <v>1799515745.866661</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>1.075411853094543</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3951,16 +4029,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1569339482.878874</v>
+        <v>1571129657.235829</v>
       </c>
       <c r="G95" t="n">
-        <v>1345705440.878763</v>
+        <v>1371565146.673565</v>
       </c>
       <c r="H95" t="n">
-        <v>1830137813.007782</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+        <v>1799731063.327661</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0.7603971048866009</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3983,16 +4067,22 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1628332103.743407</v>
+        <v>1619449028.863847</v>
       </c>
       <c r="G96" t="n">
-        <v>1387669181.373198</v>
+        <v>1408698554.374662</v>
       </c>
       <c r="H96" t="n">
-        <v>1910733102.437004</v>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+        <v>1861729146.341224</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>-0.2119867351621618</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4015,16 +4105,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1627815777.891288</v>
+        <v>1619754982.455185</v>
       </c>
       <c r="G97" t="n">
-        <v>1378981461.458694</v>
+        <v>1404059010.327936</v>
       </c>
       <c r="H97" t="n">
-        <v>1921551725.53869</v>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+        <v>1868586849.904278</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>-0.2854178679703168</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4047,21 +4143,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2309775423.985768</v>
+        <v>2292333902.236731</v>
       </c>
       <c r="G98" t="n">
-        <v>1959266413.706715</v>
+        <v>1947552399.207723</v>
       </c>
       <c r="H98" t="n">
-        <v>2722989825.133218</v>
+        <v>2698153190.374527</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>7.038139446553543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4085,21 +4181,21 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>2398437522.800867</v>
+        <v>2379290488.606303</v>
       </c>
       <c r="G99" t="n">
-        <v>1980309893.97624</v>
+        <v>1952479644.815221</v>
       </c>
       <c r="H99" t="n">
-        <v>2904849674.425844</v>
+        <v>2899401919.095638</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>7.055998947583368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4123,21 +4219,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2462398742.30107</v>
+        <v>2491198274.412746</v>
       </c>
       <c r="G100" t="n">
-        <v>2005807832.399647</v>
+        <v>2010406487.246928</v>
       </c>
       <c r="H100" t="n">
-        <v>3022925460.826394</v>
+        <v>3086972153.047367</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>7.033361733229282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -4161,21 +4257,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2532234556.231949</v>
+        <v>2543776595.049114</v>
       </c>
       <c r="G101" t="n">
-        <v>2042665575.044657</v>
+        <v>2032122829.395818</v>
       </c>
       <c r="H101" t="n">
-        <v>3139139331.525198</v>
+        <v>3184256026.218422</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>7.050430174458898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4199,21 +4295,21 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2630916554.408489</v>
+        <v>2640927750.009299</v>
       </c>
       <c r="G102" t="n">
-        <v>2104567775.834089</v>
+        <v>2094492440.615757</v>
       </c>
       <c r="H102" t="n">
-        <v>3288904256.607936</v>
+        <v>3329923396.008415</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>7.061126878716963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4237,21 +4333,21 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2629123053.105182</v>
+        <v>2642299239.256086</v>
       </c>
       <c r="G103" t="n">
-        <v>2086916407.1554</v>
+        <v>2083393618.328112</v>
       </c>
       <c r="H103" t="n">
-        <v>3312201679.314507</v>
+        <v>3351140758.209687</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>7.068702085302047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4275,21 +4371,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2618591297.020188</v>
+        <v>2644747107.258755</v>
       </c>
       <c r="G104" t="n">
-        <v>2063290430.985645</v>
+        <v>2074759916.391812</v>
       </c>
       <c r="H104" t="n">
-        <v>3323342306.954932</v>
+        <v>3371323692.004771</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>7.066579967851128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4313,21 +4409,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2627533965.303871</v>
+        <v>2638956041.155229</v>
       </c>
       <c r="G105" t="n">
-        <v>2055671565.221465</v>
+        <v>2060613512.965738</v>
       </c>
       <c r="H105" t="n">
-        <v>3358481410.955207</v>
+        <v>3379619197.549865</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>7.063721708236462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4351,21 +4447,21 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2087252213.498531</v>
+        <v>2062161934.958723</v>
       </c>
       <c r="G106" t="n">
-        <v>1798199455.893524</v>
+        <v>1765380083.772797</v>
       </c>
       <c r="H106" t="n">
-        <v>2422768947.279942</v>
+        <v>2408836422.865185</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>1.641478178511924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4389,21 +4485,21 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2247705461.140539</v>
+        <v>2238019293.161846</v>
       </c>
       <c r="G107" t="n">
-        <v>1904617875.569444</v>
+        <v>1894756992.645194</v>
       </c>
       <c r="H107" t="n">
-        <v>2652594992.856768</v>
+        <v>2643468463.769681</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>1.801993558891857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -4427,21 +4523,21 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2391973609.614781</v>
+        <v>2326740581.917959</v>
       </c>
       <c r="G108" t="n">
-        <v>1996582415.792944</v>
+        <v>1949460293.683598</v>
       </c>
       <c r="H108" t="n">
-        <v>2865665701.468804</v>
+        <v>2777036163.847399</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>-2.238291510711132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -4465,21 +4561,21 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2275324112.761128</v>
+        <v>2265072668.074651</v>
       </c>
       <c r="G109" t="n">
-        <v>1873013086.223585</v>
+        <v>1879218067.616814</v>
       </c>
       <c r="H109" t="n">
-        <v>2764048930.67267</v>
+        <v>2730153716.628153</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>1.721493938411056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -4503,21 +4599,21 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2386710605.33337</v>
+        <v>2376007417.018144</v>
       </c>
       <c r="G110" t="n">
-        <v>1939398017.397213</v>
+        <v>1952924295.612866</v>
       </c>
       <c r="H110" t="n">
-        <v>2937193635.608472</v>
+        <v>2890747612.904057</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>1.075411853094543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4541,21 +4637,21 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2335866093.830607</v>
+        <v>2327916077.024906</v>
       </c>
       <c r="G111" t="n">
-        <v>1875065218.552778</v>
+        <v>1896409936.069477</v>
       </c>
       <c r="H111" t="n">
-        <v>2909909668.378759</v>
+        <v>2857606448.162212</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>0.7603971048866009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4579,21 +4675,21 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>2662002305.821826</v>
+        <v>2547347244.497967</v>
       </c>
       <c r="G112" t="n">
-        <v>2112307941.895675</v>
+        <v>2057509775.598479</v>
       </c>
       <c r="H112" t="n">
-        <v>3354745837.78784</v>
+        <v>3153801775.82092</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>-0.2119867351621618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -4617,21 +4713,21 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2373922767.401633</v>
+        <v>2393457647.590253</v>
       </c>
       <c r="G113" t="n">
-        <v>1863094689.73882</v>
+        <v>1917393490.506634</v>
       </c>
       <c r="H113" t="n">
-        <v>3024810996.792572</v>
+        <v>2987722415.441489</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>-0.2854178679703168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -4655,13 +4751,13 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>921787419.1117277</v>
+        <v>906418755.6910527</v>
       </c>
       <c r="G114" t="n">
-        <v>820783221.5346916</v>
+        <v>804093747.911567</v>
       </c>
       <c r="H114" t="n">
-        <v>1035221022.724995</v>
+        <v>1021765139.702186</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -4693,13 +4789,13 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>966661781.7083695</v>
+        <v>991093357.1815255</v>
       </c>
       <c r="G115" t="n">
-        <v>851026984.2686673</v>
+        <v>868617660.8798639</v>
       </c>
       <c r="H115" t="n">
-        <v>1098008661.874111</v>
+        <v>1130838212.124726</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -4731,13 +4827,13 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>967025802.1849028</v>
+        <v>956295291.849102</v>
       </c>
       <c r="G116" t="n">
-        <v>842524319.8027744</v>
+        <v>816076952.2173102</v>
       </c>
       <c r="H116" t="n">
-        <v>1109925114.458726</v>
+        <v>1120605946.201554</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -4769,13 +4865,13 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1012076526.000833</v>
+        <v>1054115547.082218</v>
       </c>
       <c r="G117" t="n">
-        <v>873277126.2034867</v>
+        <v>886585745.0224161</v>
       </c>
       <c r="H117" t="n">
-        <v>1172936818.962595</v>
+        <v>1253301886.296795</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -4807,13 +4903,13 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>991848116.1499991</v>
+        <v>980772574.3370674</v>
       </c>
       <c r="G118" t="n">
-        <v>848081991.8625494</v>
+        <v>811212425.9775143</v>
       </c>
       <c r="H118" t="n">
-        <v>1159985349.234656</v>
+        <v>1185774295.0777</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -4845,13 +4941,13 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>980532216.9309431</v>
+        <v>965363658.3465452</v>
       </c>
       <c r="G119" t="n">
-        <v>831237655.1019082</v>
+        <v>787957967.5821838</v>
       </c>
       <c r="H119" t="n">
-        <v>1156640850.590003</v>
+        <v>1182711554.673157</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -4883,13 +4979,13 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1027939693.9677</v>
+        <v>1011414264.819498</v>
       </c>
       <c r="G120" t="n">
-        <v>864343098.7306674</v>
+        <v>814849470.7830199</v>
       </c>
       <c r="H120" t="n">
-        <v>1222500666.675269</v>
+        <v>1255396059.958614</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -4921,13 +5017,13 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1077634652.301204</v>
+        <v>1069701291.417508</v>
       </c>
       <c r="G121" t="n">
-        <v>899093467.978738</v>
+        <v>851870355.3839366</v>
       </c>
       <c r="H121" t="n">
-        <v>1291630386.82848</v>
+        <v>1343233563.21581</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -4959,16 +5055,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>2295068218.921602</v>
+        <v>2363679924.434914</v>
       </c>
       <c r="G122" t="n">
-        <v>1966052217.606561</v>
+        <v>2010978749.105327</v>
       </c>
       <c r="H122" t="n">
-        <v>2679144573.238418</v>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
+        <v>2778240589.395715</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4991,16 +5093,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2393069001.550677</v>
+        <v>2448316962.25159</v>
       </c>
       <c r="G123" t="n">
-        <v>2019275645.040153</v>
+        <v>2051267157.120923</v>
       </c>
       <c r="H123" t="n">
-        <v>2836056216.618648</v>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+        <v>2922220992.443594</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5023,16 +5131,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>2422214319.578368</v>
+        <v>2466922059.263552</v>
       </c>
       <c r="G124" t="n">
-        <v>2037090239.018677</v>
+        <v>2057800554.790018</v>
       </c>
       <c r="H124" t="n">
-        <v>2880148408.544164</v>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+        <v>2957383033.217288</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5055,16 +5169,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2499138850.691993</v>
+        <v>2528524828.91779</v>
       </c>
       <c r="G125" t="n">
-        <v>2099780199.782313</v>
+        <v>2104683644.356298</v>
       </c>
       <c r="H125" t="n">
-        <v>2974451800.091074</v>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
+        <v>3037719149.667799</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5087,16 +5207,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2513986404.752535</v>
+        <v>2556707925.295156</v>
       </c>
       <c r="G126" t="n">
-        <v>2111452832.501827</v>
+        <v>2124908096.559451</v>
       </c>
       <c r="H126" t="n">
-        <v>2993260160.015964</v>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+        <v>3076253239.305297</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5119,16 +5245,22 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>2501273430.346691</v>
+        <v>2543729519.845525</v>
       </c>
       <c r="G127" t="n">
-        <v>2100323748.683295</v>
+        <v>2111333639.064824</v>
       </c>
       <c r="H127" t="n">
-        <v>2978764001.159563</v>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+        <v>3064679002.130405</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5151,16 +5283,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2626492355.019824</v>
+        <v>2653442963.248927</v>
       </c>
       <c r="G128" t="n">
-        <v>2205109962.328624</v>
+        <v>2199655845.913389</v>
       </c>
       <c r="H128" t="n">
-        <v>3128398224.500659</v>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+        <v>3200845974.28996</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5183,16 +5321,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>2689360253.284368</v>
+        <v>2707913505.024736</v>
       </c>
       <c r="G129" t="n">
-        <v>2257558116.736068</v>
+        <v>2242085620.521472</v>
       </c>
       <c r="H129" t="n">
-        <v>3203752992.371507</v>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+        <v>3270524320.5609</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5215,21 +5359,17 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>776329816.1880727</v>
+        <v>760450325.3336313</v>
       </c>
       <c r="G130" t="n">
-        <v>654987089.4000552</v>
+        <v>651974006.3989403</v>
       </c>
       <c r="H130" t="n">
-        <v>920152462.9357923</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>886975081.2522049</v>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="n">
-        <v>7.038139446553543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5253,21 +5393,17 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>842694713.7240454</v>
+        <v>794890804.3036025</v>
       </c>
       <c r="G131" t="n">
-        <v>702280383.8991631</v>
+        <v>669898620.4078972</v>
       </c>
       <c r="H131" t="n">
-        <v>1011183562.604556</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>943204496.1992868</v>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
-        <v>7.055998947583368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5291,21 +5427,17 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>824609077.9363045</v>
+        <v>805659650.6932331</v>
       </c>
       <c r="G132" t="n">
-        <v>679330444.3533374</v>
+        <v>675639742.7261997</v>
       </c>
       <c r="H132" t="n">
-        <v>1000956363.824152</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>960700550.4680361</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
-        <v>7.033361733229282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -5329,21 +5461,17 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>849613995.0147744</v>
+        <v>819446569.5820051</v>
       </c>
       <c r="G133" t="n">
-        <v>692355164.4897451</v>
+        <v>685759222.363798</v>
       </c>
       <c r="H133" t="n">
-        <v>1042591978.146004</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>979195989.6435581</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="n">
-        <v>7.050430174458898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -5367,21 +5495,17 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>858944374.6529102</v>
+        <v>818541963.4311334</v>
       </c>
       <c r="G134" t="n">
-        <v>692764267.9907845</v>
+        <v>684128963.0996222</v>
       </c>
       <c r="H134" t="n">
-        <v>1064987720.697069</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>979363514.8291895</v>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
-        <v>7.061126878716963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -5405,21 +5529,17 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>861054387.7892766</v>
+        <v>818278971.6860187</v>
       </c>
       <c r="G135" t="n">
-        <v>687654211.7152296</v>
+        <v>683233319.0905836</v>
       </c>
       <c r="H135" t="n">
-        <v>1078179477.563063</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>980017304.183543</v>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
-        <v>7.068702085302047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -5443,21 +5563,17 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>875499687.0300603</v>
+        <v>840660465.7380685</v>
       </c>
       <c r="G136" t="n">
-        <v>692619210.7736999</v>
+        <v>701305625.8302684</v>
       </c>
       <c r="H136" t="n">
-        <v>1106668267.450313</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>1007706187.752707</v>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
-        <v>7.066579967851128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -5481,21 +5597,17 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>887345466.723204</v>
+        <v>856956368.9243509</v>
       </c>
       <c r="G137" t="n">
-        <v>695647573.2417845</v>
+        <v>714306711.9186853</v>
       </c>
       <c r="H137" t="n">
-        <v>1131869077.96565</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+        <v>1028093682.98867</v>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
-        <v>7.063721708236462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -5519,13 +5631,13 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>4700873507.8629</v>
+        <v>4679651111.779834</v>
       </c>
       <c r="G138" t="n">
-        <v>3987500371.71895</v>
+        <v>4063699420.23765</v>
       </c>
       <c r="H138" t="n">
-        <v>5541870765.368994</v>
+        <v>5388965143.170344</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -5557,13 +5669,13 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>4897434507.038523</v>
+        <v>4892908498.493422</v>
       </c>
       <c r="G139" t="n">
-        <v>4116063167.224427</v>
+        <v>4197414692.501469</v>
       </c>
       <c r="H139" t="n">
-        <v>5827137188.204355</v>
+        <v>5703642677.336145</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -5595,13 +5707,13 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4918918367.814612</v>
+        <v>4895551042.900116</v>
       </c>
       <c r="G140" t="n">
-        <v>4098044251.718015</v>
+        <v>4199681617.1173</v>
       </c>
       <c r="H140" t="n">
-        <v>5904220750.930259</v>
+        <v>5706723080.139389</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -5633,13 +5745,13 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>5076228926.651343</v>
+        <v>4999136224.039076</v>
       </c>
       <c r="G141" t="n">
-        <v>4193883828.563647</v>
+        <v>4288542866.284739</v>
       </c>
       <c r="H141" t="n">
-        <v>6144209322.220807</v>
+        <v>5827471886.307681</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -5671,13 +5783,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>5143029359.10926</v>
+        <v>5020819133.33053</v>
       </c>
       <c r="G142" t="n">
-        <v>4215168022.458547</v>
+        <v>4307143696.867233</v>
       </c>
       <c r="H142" t="n">
-        <v>6275135616.83173</v>
+        <v>5852747561.673698</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -5709,13 +5821,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>5139796343.036514</v>
+        <v>5032135812.1834</v>
       </c>
       <c r="G143" t="n">
-        <v>4180202024.358973</v>
+        <v>4316851786.463019</v>
       </c>
       <c r="H143" t="n">
-        <v>6319672181.858869</v>
+        <v>5865939366.198718</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -5747,13 +5859,13 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>5206347862.596031</v>
+        <v>5093325960.42978</v>
       </c>
       <c r="G144" t="n">
-        <v>4203008327.885881</v>
+        <v>4369344169.54453</v>
       </c>
       <c r="H144" t="n">
-        <v>6449203987.181402</v>
+        <v>5937268462.395396</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -5785,13 +5897,13 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>5309146363.034813</v>
+        <v>5177260620.703897</v>
       </c>
       <c r="G145" t="n">
-        <v>4255353129.267638</v>
+        <v>4441348781.550331</v>
       </c>
       <c r="H145" t="n">
-        <v>6623900355.122085</v>
+        <v>6035109795.032776</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -5823,13 +5935,13 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>6358215750.313057</v>
+        <v>6401538949.94783</v>
       </c>
       <c r="G146" t="n">
-        <v>5453411117.384982</v>
+        <v>5467134555.328122</v>
       </c>
       <c r="H146" t="n">
-        <v>7413141363.696511</v>
+        <v>7495645207.371284</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -5861,13 +5973,13 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>6536552717.261557</v>
+        <v>6619467639.980528</v>
       </c>
       <c r="G147" t="n">
-        <v>5508647406.615261</v>
+        <v>5587769011.277956</v>
       </c>
       <c r="H147" t="n">
-        <v>7756263610.960056</v>
+        <v>7841654110.6677</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -5899,13 +6011,13 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>6290221762.819308</v>
+        <v>6247688847.608932</v>
       </c>
       <c r="G148" t="n">
-        <v>5217233203.533103</v>
+        <v>5218555016.389467</v>
       </c>
       <c r="H148" t="n">
-        <v>7583883695.030347</v>
+        <v>7479774729.584627</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -5937,13 +6049,13 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>6340202637.013812</v>
+        <v>6295055466.418747</v>
       </c>
       <c r="G149" t="n">
-        <v>5182039940.191045</v>
+        <v>5207596921.482076</v>
       </c>
       <c r="H149" t="n">
-        <v>7757209504.818083</v>
+        <v>7609598807.814517</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -5975,13 +6087,13 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>6731116034.726787</v>
+        <v>6823083563.317262</v>
       </c>
       <c r="G150" t="n">
-        <v>5426773441.043624</v>
+        <v>5594425153.146274</v>
       </c>
       <c r="H150" t="n">
-        <v>8348961600.328554</v>
+        <v>8321582296.230776</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -6013,13 +6125,13 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>6568945324.610422</v>
+        <v>6567032679.785151</v>
       </c>
       <c r="G151" t="n">
-        <v>5228328920.45984</v>
+        <v>5340284880.223224</v>
       </c>
       <c r="H151" t="n">
-        <v>8253314459.398228</v>
+        <v>8075583828.322559</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -6051,13 +6163,13 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6835736299.823831</v>
+        <v>6744166841.868417</v>
       </c>
       <c r="G152" t="n">
-        <v>5374817671.757554</v>
+        <v>5442408482.449597</v>
       </c>
       <c r="H152" t="n">
-        <v>8693744348.99658</v>
+        <v>8357290074.354254</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -6089,13 +6201,13 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>7088521877.497141</v>
+        <v>7002719318.857279</v>
       </c>
       <c r="G153" t="n">
-        <v>5509352449.22677</v>
+        <v>5610675060.604968</v>
       </c>
       <c r="H153" t="n">
-        <v>9120335442.4725</v>
+        <v>8740138633.765303</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -6127,21 +6239,21 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>840773939.7345476</v>
+        <v>843364878.7182848</v>
       </c>
       <c r="G154" t="n">
-        <v>712746862.8490018</v>
+        <v>738424937.0095915</v>
       </c>
       <c r="H154" t="n">
-        <v>991797866.2313838</v>
+        <v>963218172.9072193</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>7.296692260048432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -6165,21 +6277,21 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>850502024.7574371</v>
+        <v>845804075.9365823</v>
       </c>
       <c r="G155" t="n">
-        <v>712116097.4186304</v>
+        <v>731659067.6601061</v>
       </c>
       <c r="H155" t="n">
-        <v>1015780568.278972</v>
+        <v>977756671.7771747</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>7.369960553576971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -6203,21 +6315,21 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>884942668.1641413</v>
+        <v>874510997.491147</v>
       </c>
       <c r="G156" t="n">
-        <v>732422395.1750535</v>
+        <v>754030295.8495822</v>
       </c>
       <c r="H156" t="n">
-        <v>1069223894.703955</v>
+        <v>1014242383.817322</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>6.339104426528941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -6241,21 +6353,21 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>902730630.0805602</v>
+        <v>893033137.1501262</v>
       </c>
       <c r="G157" t="n">
-        <v>739037130.3118584</v>
+        <v>768846210.9615493</v>
       </c>
       <c r="H157" t="n">
-        <v>1102681525.814224</v>
+        <v>1037279201.845583</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>6.365548028661205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6279,21 +6391,21 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>878927658.8430147</v>
+        <v>878636146.6758419</v>
       </c>
       <c r="G158" t="n">
-        <v>712144579.4741423</v>
+        <v>755670499.819515</v>
       </c>
       <c r="H158" t="n">
-        <v>1084771058.778118</v>
+        <v>1021611242.505506</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>7.430178721321767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -6317,21 +6429,21 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>942535579.1381932</v>
+        <v>913135368.5036106</v>
       </c>
       <c r="G159" t="n">
-        <v>756189322.5650269</v>
+        <v>784648285.9198645</v>
       </c>
       <c r="H159" t="n">
-        <v>1174802779.452067</v>
+        <v>1062662362.455452</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>7.21752999809735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -6355,21 +6467,21 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>878499223.0298711</v>
+        <v>892033509.9026476</v>
       </c>
       <c r="G160" t="n">
-        <v>698193102.4445065</v>
+        <v>765880156.7214</v>
       </c>
       <c r="H160" t="n">
-        <v>1105368818.686415</v>
+        <v>1038966443.778348</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>7.231297900402511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -6393,21 +6505,21 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>891705363.8943101</v>
+        <v>895028363.7328022</v>
       </c>
       <c r="G161" t="n">
-        <v>702293741.735796</v>
+        <v>767830912.071409</v>
       </c>
       <c r="H161" t="n">
-        <v>1132202109.665127</v>
+        <v>1043297110.460325</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>7.311710033254837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -6431,21 +6543,21 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>742590871.1946707</v>
+        <v>745837403.4015963</v>
       </c>
       <c r="G162" t="n">
-        <v>624331116.0232921</v>
+        <v>620427113.6283931</v>
       </c>
       <c r="H162" t="n">
-        <v>883251191.2814662</v>
+        <v>896597553.674963</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>7.296692260048432</v>
+        <v>1.641478178511924</v>
       </c>
     </row>
     <row r="163">
@@ -6469,21 +6581,21 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>753846815.0159651</v>
+        <v>752967769.5501184</v>
       </c>
       <c r="G163" t="n">
-        <v>618971735.2732965</v>
+        <v>619500356.2856537</v>
       </c>
       <c r="H163" t="n">
-        <v>918111422.7433957</v>
+        <v>915189888.4782124</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>7.369960553576971</v>
+        <v>1.801993558891857</v>
       </c>
     </row>
     <row r="164">
@@ -6507,21 +6619,21 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>795878082.5794185</v>
+        <v>794453090.4412501</v>
       </c>
       <c r="G164" t="n">
-        <v>648646573.6497754</v>
+        <v>646856219.4988649</v>
       </c>
       <c r="H164" t="n">
-        <v>976528587.4650993</v>
+        <v>975727980.7877935</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>6.339104426528941</v>
+        <v>-2.238291510711132</v>
       </c>
     </row>
     <row r="165">
@@ -6545,21 +6657,21 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>779780098.3900414</v>
+        <v>772684796.725809</v>
       </c>
       <c r="G165" t="n">
-        <v>632170278.3923143</v>
+        <v>622923671.6263738</v>
       </c>
       <c r="H165" t="n">
-        <v>961856358.371585</v>
+        <v>958450966.4440992</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>6.365548028661205</v>
+        <v>1.721493938411056</v>
       </c>
     </row>
     <row r="166">
@@ -6583,21 +6695,21 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>760604877.8400031</v>
+        <v>758664501.1571186</v>
       </c>
       <c r="G166" t="n">
-        <v>613652430.308406</v>
+        <v>605849727.0478461</v>
       </c>
       <c r="H166" t="n">
-        <v>942748291.4118938</v>
+        <v>950024073.0000769</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>7.430178721321767</v>
+        <v>1.075411853094543</v>
       </c>
     </row>
     <row r="167">
@@ -6621,21 +6733,21 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>721015224.1398209</v>
+        <v>717778293.2653787</v>
       </c>
       <c r="G167" t="n">
-        <v>579005960.7974625</v>
+        <v>568008477.379993</v>
       </c>
       <c r="H167" t="n">
-        <v>897854234.048629</v>
+        <v>907038712.9773272</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>7.21752999809735</v>
+        <v>0.7603971048866009</v>
       </c>
     </row>
     <row r="168">
@@ -6659,21 +6771,21 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>726257356.2222816</v>
+        <v>722026153.3266592</v>
       </c>
       <c r="G168" t="n">
-        <v>580566274.0429301</v>
+        <v>566388846.9319447</v>
       </c>
       <c r="H168" t="n">
-        <v>908509107.4855919</v>
+        <v>920430846.955453</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>7.231297900402511</v>
+        <v>-0.2119867351621618</v>
       </c>
     </row>
     <row r="169">
@@ -6697,21 +6809,21 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>822019810.8462853</v>
+        <v>815786658.4198425</v>
       </c>
       <c r="G169" t="n">
-        <v>654193669.8418058</v>
+        <v>634553267.294571</v>
       </c>
       <c r="H169" t="n">
-        <v>1032899889.702634</v>
+        <v>1048781727.802328</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>7.311710033254837</v>
+        <v>-0.2854178679703168</v>
       </c>
     </row>
     <row r="170">
@@ -6735,21 +6847,17 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>190559863.8510597</v>
+        <v>188847930.625113</v>
       </c>
       <c r="G170" t="n">
-        <v>163116475.1122631</v>
+        <v>162679591.8082529</v>
       </c>
       <c r="H170" t="n">
-        <v>222620441.5338324</v>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>219225660.1149048</v>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
-        <v>7.296692260048432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -6773,21 +6881,17 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>186605729.0694608</v>
+        <v>188723536.0060115</v>
       </c>
       <c r="G171" t="n">
-        <v>158037366.240113</v>
+        <v>160186200.9276783</v>
       </c>
       <c r="H171" t="n">
-        <v>220338385.4716923</v>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>222344826.4354101</v>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
-        <v>7.369960553576971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -6811,21 +6915,17 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>184654451.8788018</v>
+        <v>182868533.4412706</v>
       </c>
       <c r="G172" t="n">
-        <v>154825627.1878196</v>
+        <v>153126136.1814338</v>
       </c>
       <c r="H172" t="n">
-        <v>220230120.9301558</v>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>218387934.0058457</v>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
-        <v>6.339104426528941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -6849,21 +6949,17 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>184850279.9188148</v>
+        <v>182102947.9602637</v>
       </c>
       <c r="G173" t="n">
-        <v>153527419.8355627</v>
+        <v>150576633.3429205</v>
       </c>
       <c r="H173" t="n">
-        <v>222563669.8816535</v>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>220229944.8434151</v>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
-        <v>6.365548028661205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -6887,21 +6983,17 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>197960607.6606989</v>
+        <v>198681337.9358</v>
       </c>
       <c r="G174" t="n">
-        <v>162939973.739519</v>
+        <v>162356047.4854878</v>
       </c>
       <c r="H174" t="n">
-        <v>240508214.6879499</v>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>243133992.5757183</v>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
-        <v>7.430178721321767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -6925,21 +7017,17 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>192160073.6573981</v>
+        <v>194733973.2355668</v>
       </c>
       <c r="G175" t="n">
-        <v>156808153.87709</v>
+        <v>157364869.7847825</v>
       </c>
       <c r="H175" t="n">
-        <v>235481975.8732683</v>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>240977038.8014359</v>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
-        <v>7.21752999809735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -6963,21 +7051,17 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>197200998.4408369</v>
+        <v>196944870.0930901</v>
       </c>
       <c r="G176" t="n">
-        <v>159596584.8233462</v>
+        <v>157473250.5752093</v>
       </c>
       <c r="H176" t="n">
-        <v>243665826.7412642</v>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>246310288.9811709</v>
+      </c>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
-        <v>7.231297900402511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -7001,21 +7085,17 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>205166425.9006822</v>
+        <v>206444196.8187611</v>
       </c>
       <c r="G177" t="n">
-        <v>164727055.0091867</v>
+        <v>163406528.5951537</v>
       </c>
       <c r="H177" t="n">
-        <v>255533387.1203648</v>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>260817035.6873203</v>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
-        <v>7.311710033254837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7039,22 +7119,16 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>4440163844.559254</v>
+        <v>4307449173.562239</v>
       </c>
       <c r="G178" t="n">
-        <v>3701014765.621196</v>
+        <v>3579951876.017474</v>
       </c>
       <c r="H178" t="n">
-        <v>5326932264.541275</v>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J178" t="n">
-        <v>7.038139446553543</v>
-      </c>
+        <v>5182784301.408707</v>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7077,22 +7151,16 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>4541374420.67653</v>
+        <v>4356283428.751451</v>
       </c>
       <c r="G179" t="n">
-        <v>3741802408.06418</v>
+        <v>3559987816.73091</v>
       </c>
       <c r="H179" t="n">
-        <v>5511804039.766213</v>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J179" t="n">
-        <v>7.055998947583368</v>
-      </c>
+        <v>5330693892.38557</v>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7115,22 +7183,16 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>4665967326.118124</v>
+        <v>4663080977.543185</v>
       </c>
       <c r="G180" t="n">
-        <v>3802691219.041688</v>
+        <v>3751864745.374832</v>
       </c>
       <c r="H180" t="n">
-        <v>5725221911.099177</v>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J180" t="n">
-        <v>7.033361733229282</v>
-      </c>
+        <v>5795604500.383643</v>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7153,22 +7215,16 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>4723586515.848181</v>
+        <v>4602152226.971789</v>
       </c>
       <c r="G181" t="n">
-        <v>3809937531.215553</v>
+        <v>3649466860.94908</v>
       </c>
       <c r="H181" t="n">
-        <v>5856334753.495045</v>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J181" t="n">
-        <v>7.050430174458898</v>
-      </c>
+        <v>5803534030.368858</v>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7191,22 +7247,16 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>4817552556.770709</v>
+        <v>4737207981.516734</v>
       </c>
       <c r="G182" t="n">
-        <v>3847481316.346987</v>
+        <v>3705589071.181089</v>
       </c>
       <c r="H182" t="n">
-        <v>6032209315.387588</v>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J182" t="n">
-        <v>7.061126878716963</v>
-      </c>
+        <v>6056024839.525215</v>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7229,22 +7279,16 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>4697804638.612934</v>
+        <v>4618682979.031115</v>
       </c>
       <c r="G183" t="n">
-        <v>3716466959.757485</v>
+        <v>3566419615.271504</v>
       </c>
       <c r="H183" t="n">
-        <v>5938265740.431422</v>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J183" t="n">
-        <v>7.068702085302047</v>
-      </c>
+        <v>5981414068.453006</v>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7267,22 +7311,16 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>4874916940.408082</v>
+        <v>4827984007.7943</v>
       </c>
       <c r="G184" t="n">
-        <v>3821622977.417405</v>
+        <v>3682373377.448606</v>
       </c>
       <c r="H184" t="n">
-        <v>6218513787.547299</v>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J184" t="n">
-        <v>7.066579967851128</v>
-      </c>
+        <v>6330001656.613062</v>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7305,22 +7343,16 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>4994768724.054286</v>
+        <v>5010264227.930561</v>
       </c>
       <c r="G185" t="n">
-        <v>3881360591.678516</v>
+        <v>3776621698.424227</v>
       </c>
       <c r="H185" t="n">
-        <v>6427569409.623469</v>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J185" t="n">
-        <v>7.063721708236462</v>
-      </c>
+        <v>6646879046.464887</v>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7343,21 +7375,21 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>4051756434.349584</v>
+        <v>4221629041.903661</v>
       </c>
       <c r="G186" t="n">
-        <v>3530743809.954148</v>
+        <v>3712031010.872674</v>
       </c>
       <c r="H186" t="n">
-        <v>4649652052.638294</v>
+        <v>4801186120.278277</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>7.038139446553543</v>
+        <v>7.296692260048432</v>
       </c>
     </row>
     <row r="187">
@@ -7381,21 +7413,21 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>4112869167.953981</v>
+        <v>4242144866.288332</v>
       </c>
       <c r="G187" t="n">
-        <v>3474857866.45359</v>
+        <v>3670439531.891995</v>
       </c>
       <c r="H187" t="n">
-        <v>4868024374.755357</v>
+        <v>4902898661.103999</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>7.055998947583368</v>
+        <v>7.369960553576971</v>
       </c>
     </row>
     <row r="188">
@@ -7419,21 +7451,21 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>4088896279.75337</v>
+        <v>4284835805.689812</v>
       </c>
       <c r="G188" t="n">
-        <v>3445064740.625077</v>
+        <v>3706114793.860527</v>
       </c>
       <c r="H188" t="n">
-        <v>4853050391.020349</v>
+        <v>4953925850.363825</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>7.033361733229282</v>
+        <v>6.339104426528941</v>
       </c>
     </row>
     <row r="189">
@@ -7457,21 +7489,21 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>4201424126.697165</v>
+        <v>4321001616.518609</v>
       </c>
       <c r="G189" t="n">
-        <v>3525952573.39592</v>
+        <v>3733404836.198475</v>
       </c>
       <c r="H189" t="n">
-        <v>5006296688.611456</v>
+        <v>5001079654.937224</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>7.050430174458898</v>
+        <v>6.365548028661205</v>
       </c>
     </row>
     <row r="190">
@@ -7495,21 +7527,21 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>4319016254.68482</v>
+        <v>4350702013.061773</v>
       </c>
       <c r="G190" t="n">
-        <v>3611137123.835731</v>
+        <v>3758969850.134525</v>
       </c>
       <c r="H190" t="n">
-        <v>5165658563.643137</v>
+        <v>5035583886.309264</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>7.061126878716963</v>
+        <v>7.430178721321767</v>
       </c>
     </row>
     <row r="191">
@@ -7533,21 +7565,21 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>4304938271.675729</v>
+        <v>4391201318.211674</v>
       </c>
       <c r="G191" t="n">
-        <v>3586191259.595227</v>
+        <v>3792684758.512973</v>
       </c>
       <c r="H191" t="n">
-        <v>5167737072.960847</v>
+        <v>5084168668.060944</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>7.068702085302047</v>
+        <v>7.21752999809735</v>
       </c>
     </row>
     <row r="192">
@@ -7571,21 +7603,21 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>4280284015.02238</v>
+        <v>4430693319.222906</v>
       </c>
       <c r="G192" t="n">
-        <v>3552867679.026701</v>
+        <v>3826576975.101882</v>
       </c>
       <c r="H192" t="n">
-        <v>5156632023.592573</v>
+        <v>5130183821.399233</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>7.066579967851128</v>
+        <v>7.231297900402511</v>
       </c>
     </row>
     <row r="193">
@@ -7609,21 +7641,21 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>4441494647.645471</v>
+        <v>4469668848.835292</v>
       </c>
       <c r="G193" t="n">
-        <v>3673693407.841547</v>
+        <v>3859441552.119452</v>
       </c>
       <c r="H193" t="n">
-        <v>5369766203.939634</v>
+        <v>5176380921.555222</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J193" t="n">
-        <v>7.063721708236462</v>
+        <v>7.311710033254837</v>
       </c>
     </row>
     <row r="194">
@@ -7647,21 +7679,21 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>500235599.6422268</v>
+        <v>522877221.0320866</v>
       </c>
       <c r="G194" t="n">
-        <v>430479554.3529817</v>
+        <v>455946936.6245762</v>
       </c>
       <c r="H194" t="n">
-        <v>581295098.9635888</v>
+        <v>599632471.0464143</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>7.296692260048432</v>
+        <v>7.038139446553543</v>
       </c>
     </row>
     <row r="195">
@@ -7685,21 +7717,21 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>523500694.4294504</v>
+        <v>551126717.7331483</v>
       </c>
       <c r="G195" t="n">
-        <v>443396097.2916011</v>
+        <v>476037160.7352564</v>
       </c>
       <c r="H195" t="n">
-        <v>618077106.9978203</v>
+        <v>638060815.5257775</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>7.369960553576971</v>
+        <v>7.055998947583368</v>
       </c>
     </row>
     <row r="196">
@@ -7723,21 +7755,21 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>517316529.4272693</v>
+        <v>532401671.2887673</v>
       </c>
       <c r="G196" t="n">
-        <v>427614442.2668087</v>
+        <v>456791660.6037717</v>
       </c>
       <c r="H196" t="n">
-        <v>625835718.2700026</v>
+        <v>620526957.9930948</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>6.339104426528941</v>
+        <v>7.033361733229282</v>
       </c>
     </row>
     <row r="197">
@@ -7761,21 +7793,21 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>525905963.2744657</v>
+        <v>541125467.3931412</v>
       </c>
       <c r="G197" t="n">
-        <v>427857239.3295289</v>
+        <v>464276530.6261353</v>
       </c>
       <c r="H197" t="n">
-        <v>646423752.5606722</v>
+        <v>630694752.2558273</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>6.365548028661205</v>
+        <v>7.050430174458898</v>
       </c>
     </row>
     <row r="198">
@@ -7799,21 +7831,21 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>541964580.8011911</v>
+        <v>550675675.2474626</v>
       </c>
       <c r="G198" t="n">
-        <v>433969602.0197504</v>
+        <v>472470448.0012004</v>
       </c>
       <c r="H198" t="n">
-        <v>676834518.9985059</v>
+        <v>641825749.2974004</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>7.430178721321767</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="199">
@@ -7837,21 +7869,21 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>536481394.2445729</v>
+        <v>550600743.6156329</v>
       </c>
       <c r="G199" t="n">
-        <v>423614161.7102244</v>
+        <v>472406157.9240254</v>
       </c>
       <c r="H199" t="n">
-        <v>679420832.4118315</v>
+        <v>641738414.6775744</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>7.21752999809735</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="200">
@@ -7875,21 +7907,21 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>567745028.6379594</v>
+        <v>578281589.4847697</v>
       </c>
       <c r="G200" t="n">
-        <v>442367874.7662046</v>
+        <v>496155889.0997056</v>
       </c>
       <c r="H200" t="n">
-        <v>728656929.9668831</v>
+        <v>674001063.1413267</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>7.231297900402511</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="201">
@@ -7913,21 +7945,21 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>585041707.0336231</v>
+        <v>589847152.3791136</v>
       </c>
       <c r="G201" t="n">
-        <v>450180373.7038147</v>
+        <v>506078991.4840344</v>
       </c>
       <c r="H201" t="n">
-        <v>760303689.2807914</v>
+        <v>687480944.7226882</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>7.311710033254837</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="202">
@@ -7951,21 +7983,21 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>20585013635.06753</v>
+        <v>20085766244.44354</v>
       </c>
       <c r="G202" t="n">
-        <v>18635514669.81844</v>
+        <v>18267233646.81067</v>
       </c>
       <c r="H202" t="n">
-        <v>22738453638.85753</v>
+        <v>22085336697.75801</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J202" t="n">
-        <v>7.038139446553543</v>
+        <v>1.641478178511924</v>
       </c>
     </row>
     <row r="203">
@@ -7989,21 +8021,21 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>21040165105.24316</v>
+        <v>20378644891.96307</v>
       </c>
       <c r="G203" t="n">
-        <v>18880235262.84047</v>
+        <v>18307668940.08395</v>
       </c>
       <c r="H203" t="n">
-        <v>23447194459.86876</v>
+        <v>22683891050.89575</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>7.055998947583368</v>
+        <v>1.801993558891857</v>
       </c>
     </row>
     <row r="204">
@@ -8027,21 +8059,21 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>20945173899.16687</v>
+        <v>20959539750.75731</v>
       </c>
       <c r="G204" t="n">
-        <v>18642309534.81745</v>
+        <v>18623563711.03827</v>
       </c>
       <c r="H204" t="n">
-        <v>23532508611.50005</v>
+        <v>23588520080.24648</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J204" t="n">
-        <v>7.033361733229282</v>
+        <v>-2.238291510711132</v>
       </c>
     </row>
     <row r="205">
@@ -8065,21 +8097,21 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>21123648248.55422</v>
+        <v>20485337298.62429</v>
       </c>
       <c r="G205" t="n">
-        <v>18658404671.61053</v>
+        <v>18020037885.66926</v>
       </c>
       <c r="H205" t="n">
-        <v>23914612378.81558</v>
+        <v>23287911318.55168</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J205" t="n">
-        <v>7.050430174458898</v>
+        <v>1.721493938411056</v>
       </c>
     </row>
     <row r="206">
@@ -8103,21 +8135,21 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>21806862437.57362</v>
+        <v>21151489435.22756</v>
       </c>
       <c r="G206" t="n">
-        <v>19124076280.65281</v>
+        <v>18433324824.0905</v>
       </c>
       <c r="H206" t="n">
-        <v>24865998356.86426</v>
+        <v>24270472614.02648</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>7.061126878716963</v>
+        <v>1.075411853094543</v>
       </c>
     </row>
     <row r="207">
@@ -8141,21 +8173,21 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>21946512599.581</v>
+        <v>21572218010.71106</v>
       </c>
       <c r="G207" t="n">
-        <v>19115974050.55099</v>
+        <v>18636541023.76688</v>
       </c>
       <c r="H207" t="n">
-        <v>25196174362.33571</v>
+        <v>24970330562.31733</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J207" t="n">
-        <v>7.068702085302047</v>
+        <v>0.7603971048866009</v>
       </c>
     </row>
     <row r="208">
@@ -8179,21 +8211,21 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>21954621912.42271</v>
+        <v>21724288587.15269</v>
       </c>
       <c r="G208" t="n">
-        <v>18999385569.96474</v>
+        <v>18613918763.00944</v>
       </c>
       <c r="H208" t="n">
-        <v>25369526900.88104</v>
+        <v>25354398535.13094</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>7.066579967851128</v>
+        <v>-0.2119867351621618</v>
       </c>
     </row>
     <row r="209">
@@ -8217,21 +8249,21 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>22783556206.49572</v>
+        <v>22268823909.21684</v>
       </c>
       <c r="G209" t="n">
-        <v>19594712106.00829</v>
+        <v>18931832116.42387</v>
       </c>
       <c r="H209" t="n">
-        <v>26491352902.06086</v>
+        <v>26194005696.33727</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>7.063721708236462</v>
+        <v>-0.2854178679703168</v>
       </c>
     </row>
     <row r="210">
@@ -8255,22 +8287,16 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>558025759.5945803</v>
+        <v>560597412.3649747</v>
       </c>
       <c r="G210" t="n">
-        <v>496627158.505091</v>
+        <v>498832461.011728</v>
       </c>
       <c r="H210" t="n">
-        <v>627015142.1207789</v>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J210" t="n">
-        <v>1.641478178511924</v>
-      </c>
+        <v>630010040.0701805</v>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8293,22 +8319,16 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>582183155.228376</v>
+        <v>588579452.0553241</v>
       </c>
       <c r="G211" t="n">
-        <v>506014427.5897304</v>
+        <v>511295052.8041262</v>
       </c>
       <c r="H211" t="n">
-        <v>669817316.9609169</v>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J211" t="n">
-        <v>1.801993558891857</v>
-      </c>
+        <v>677545713.540199</v>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8331,22 +8351,16 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>607254662.3228345</v>
+        <v>606462027.8052109</v>
       </c>
       <c r="G212" t="n">
-        <v>522140888.9234654</v>
+        <v>521268536.7179229</v>
       </c>
       <c r="H212" t="n">
-        <v>706242764.6168729</v>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J212" t="n">
-        <v>-2.238291510711132</v>
-      </c>
+        <v>705579111.8439137</v>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8369,22 +8383,16 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>615622177.2135229</v>
+        <v>618757552.3331136</v>
       </c>
       <c r="G213" t="n">
-        <v>526070523.3608134</v>
+        <v>528832679.3012381</v>
       </c>
       <c r="H213" t="n">
-        <v>720417982.4711101</v>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J213" t="n">
-        <v>1.721493938411056</v>
-      </c>
+        <v>723973618.7921499</v>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8407,22 +8415,16 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>614216070.2127899</v>
+        <v>620315004.8715152</v>
       </c>
       <c r="G214" t="n">
-        <v>522660580.0902995</v>
+        <v>528302834.0437738</v>
       </c>
       <c r="H214" t="n">
-        <v>721809517.0721768</v>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J214" t="n">
-        <v>1.075411853094543</v>
-      </c>
+        <v>728352529.0285782</v>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8445,22 +8447,16 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>622496461.9476327</v>
+        <v>630166285.9588327</v>
       </c>
       <c r="G215" t="n">
-        <v>527974940.1135827</v>
+        <v>535360309.9848627</v>
       </c>
       <c r="H215" t="n">
-        <v>733939843.9137236</v>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J215" t="n">
-        <v>0.7603971048866009</v>
-      </c>
+        <v>741761278.4376519</v>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8483,22 +8479,16 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>626578389.1433731</v>
+        <v>639011791.4507825</v>
       </c>
       <c r="G216" t="n">
-        <v>529957858.1672184</v>
+        <v>541815247.4409306</v>
       </c>
       <c r="H216" t="n">
-        <v>740814522.6853613</v>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J216" t="n">
-        <v>-0.2119867351621618</v>
-      </c>
+        <v>753644478.5224611</v>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8521,22 +8511,16 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>619247367.3011535</v>
+        <v>646126961.0343031</v>
       </c>
       <c r="G217" t="n">
-        <v>522439925.2863658</v>
+        <v>546937724.7226084</v>
       </c>
       <c r="H217" t="n">
-        <v>733993103.0332706</v>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
-      <c r="J217" t="n">
-        <v>-0.2854178679703168</v>
-      </c>
+        <v>763304542.5549279</v>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8549,7 +8533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8620,25 +8604,30 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>rmse_SARIMAX_dummies</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>rmse_SARIMA_puro</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rmse_naive_sazonal</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inicio_serie</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>fim_serie</t>
         </is>
@@ -8652,12 +8641,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
+          <t>SARIMAX_dummies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -8671,42 +8660,45 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-139.4035054350692</v>
+        <v>-136.9849703600619</v>
       </c>
       <c r="G2" t="n">
-        <v>-119.0665819860002</v>
+        <v>-113.7427721325544</v>
       </c>
       <c r="H2" t="n">
-        <v>16916151.5310565</v>
+        <v>16975524.85310695</v>
       </c>
       <c r="I2" t="n">
-        <v>10021084.97726765</v>
+        <v>10271022.45506233</v>
       </c>
       <c r="J2" t="n">
-        <v>5.861940390703931</v>
+        <v>5.854039322084874</v>
       </c>
       <c r="K2" t="n">
-        <v>21494077.59992311</v>
+        <v>17931426.92779182</v>
       </c>
       <c r="L2" t="n">
-        <v>16916151.5310565</v>
+        <v>17765078.9914452</v>
       </c>
       <c r="M2" t="n">
-        <v>17551426.51567984</v>
+        <v>17320101.790942</v>
       </c>
       <c r="N2" t="n">
-        <v>34712780.94852228</v>
+        <v>16975524.85310695</v>
       </c>
       <c r="O2" t="n">
+        <v>37032129.8587617</v>
+      </c>
+      <c r="P2" t="n">
         <v>41208589.02814142</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>136</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="R2" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="S2" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -8728,7 +8720,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8737,42 +8729,45 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-292.8695424406562</v>
+        <v>-285.953723085591</v>
       </c>
       <c r="G3" t="n">
-        <v>-272.5326189915872</v>
+        <v>-259.7398291139666</v>
       </c>
       <c r="H3" t="n">
-        <v>54049787.64972811</v>
+        <v>57294817.97821408</v>
       </c>
       <c r="I3" t="n">
-        <v>40015933.70477842</v>
+        <v>43388461.89108662</v>
       </c>
       <c r="J3" t="n">
-        <v>5.362163207762678</v>
+        <v>5.828588312760517</v>
       </c>
       <c r="K3" t="n">
-        <v>54049787.64972811</v>
+        <v>57294817.97821408</v>
       </c>
       <c r="L3" t="n">
-        <v>95298201.77247559</v>
+        <v>88359294.69624563</v>
       </c>
       <c r="M3" t="n">
-        <v>98407043.43872684</v>
+        <v>89813477.70915553</v>
       </c>
       <c r="N3" t="n">
-        <v>96301785.69052705</v>
+        <v>94856867.82565826</v>
       </c>
       <c r="O3" t="n">
+        <v>60620365.14273414</v>
+      </c>
+      <c r="P3" t="n">
         <v>204216797.2102369</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>136</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="R3" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="S3" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -8784,61 +8779,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
+          <t>SARIMAX_dummies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(0, 0, 2, 12)</t>
+          <t>(1, 0, 0, 12)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-270.8000398170574</v>
+        <v>-271.654075020071</v>
       </c>
       <c r="G4" t="n">
-        <v>-253.3683911464268</v>
+        <v>-251.317151571002</v>
       </c>
       <c r="H4" t="n">
-        <v>139633633.6357749</v>
+        <v>135642681.5117923</v>
       </c>
       <c r="I4" t="n">
-        <v>99647646.02777161</v>
+        <v>95287173.59583253</v>
       </c>
       <c r="J4" t="n">
-        <v>7.26753176220924</v>
+        <v>6.851382026957982</v>
       </c>
       <c r="K4" t="n">
-        <v>140844200.7960305</v>
+        <v>236708218.1927961</v>
       </c>
       <c r="L4" t="n">
-        <v>139633633.6357749</v>
+        <v>138892927.5246633</v>
       </c>
       <c r="M4" t="n">
-        <v>144118514.420777</v>
+        <v>136259192.0194818</v>
       </c>
       <c r="N4" t="n">
+        <v>135642681.5117923</v>
+      </c>
+      <c r="O4" t="n">
         <v>170256935.0374551</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>244565914.2946805</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>136</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="R4" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="S4" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -8860,51 +8858,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(1, 0, 1, 12)</t>
+          <t>(1, 0, 0, 12)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-223.0569488967762</v>
+        <v>-209.8630007597051</v>
       </c>
       <c r="G5" t="n">
-        <v>-205.6253002261456</v>
+        <v>-186.5617616738167</v>
       </c>
       <c r="H5" t="n">
-        <v>14826231.14272065</v>
+        <v>10191584.01177009</v>
       </c>
       <c r="I5" t="n">
-        <v>12595012.1643682</v>
+        <v>8522472.309730815</v>
       </c>
       <c r="J5" t="n">
-        <v>9.127390926569698</v>
+        <v>6.511920686849601</v>
       </c>
       <c r="K5" t="n">
-        <v>14826231.14272065</v>
+        <v>10191584.01177009</v>
       </c>
       <c r="L5" t="n">
-        <v>28073194.91370736</v>
+        <v>14931886.33160054</v>
       </c>
       <c r="M5" t="n">
-        <v>29285713.72449881</v>
+        <v>29449224.52532405</v>
       </c>
       <c r="N5" t="n">
-        <v>18494783.97591312</v>
+        <v>28311526.92231091</v>
       </c>
       <c r="O5" t="n">
+        <v>27771247.09479365</v>
+      </c>
+      <c r="P5" t="n">
         <v>25596833.75930577</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>136</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="R5" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R5" s="1" t="n">
+      <c r="S5" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -8916,12 +8917,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_mom</t>
+          <t>SARIMAX_dummies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8935,42 +8936,45 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-307.2151392553509</v>
+        <v>-314.28923065412</v>
       </c>
       <c r="G6" t="n">
-        <v>-286.8782158062819</v>
+        <v>-291.0470324266126</v>
       </c>
       <c r="H6" t="n">
-        <v>218933796.3703232</v>
+        <v>220012367.0037712</v>
       </c>
       <c r="I6" t="n">
-        <v>151872669.5334246</v>
+        <v>156488692.0262182</v>
       </c>
       <c r="J6" t="n">
-        <v>4.363879763267947</v>
+        <v>4.534092845871212</v>
       </c>
       <c r="K6" t="n">
-        <v>226524572.3814671</v>
+        <v>274727665.9540871</v>
       </c>
       <c r="L6" t="n">
-        <v>221402728.8503108</v>
+        <v>253110391.8735456</v>
       </c>
       <c r="M6" t="n">
-        <v>218933796.3703232</v>
+        <v>224369324.4609268</v>
       </c>
       <c r="N6" t="n">
+        <v>220012367.0037712</v>
+      </c>
+      <c r="O6" t="n">
         <v>280544741.7829924</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>717983139.2436274</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>136</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="R6" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R6" s="1" t="n">
+      <c r="S6" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -8992,7 +8996,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -9001,42 +9005,45 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-349.7172252614287</v>
+        <v>-332.2736784090782</v>
       </c>
       <c r="G7" t="n">
-        <v>-332.2855765907981</v>
+        <v>-306.0597844374537</v>
       </c>
       <c r="H7" t="n">
-        <v>91960978.9169251</v>
+        <v>102280692.92348</v>
       </c>
       <c r="I7" t="n">
-        <v>81011903.67588997</v>
+        <v>79455602.01613979</v>
       </c>
       <c r="J7" t="n">
-        <v>4.713738189413857</v>
+        <v>4.591016741492178</v>
       </c>
       <c r="K7" t="n">
-        <v>91960978.9169251</v>
+        <v>102280692.92348</v>
       </c>
       <c r="L7" t="n">
-        <v>173083714.0266942</v>
+        <v>153698364.222582</v>
       </c>
       <c r="M7" t="n">
-        <v>167067746.013883</v>
+        <v>182311727.186992</v>
       </c>
       <c r="N7" t="n">
+        <v>169108902.0261554</v>
+      </c>
+      <c r="O7" t="n">
         <v>375667574.7504422</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>352693527.9223654</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>136</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="R7" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R7" s="1" t="n">
+      <c r="S7" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9058,7 +9065,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9067,42 +9074,45 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-367.2405766926366</v>
+        <v>-348.6723261892503</v>
       </c>
       <c r="G8" t="n">
-        <v>-352.7142028004445</v>
+        <v>-319.5457773318897</v>
       </c>
       <c r="H8" t="n">
-        <v>114578110.4567738</v>
+        <v>47227704.69193309</v>
       </c>
       <c r="I8" t="n">
-        <v>100836662.9898092</v>
+        <v>38502364.35651562</v>
       </c>
       <c r="J8" t="n">
-        <v>9.690764198507743</v>
+        <v>3.844661971956895</v>
       </c>
       <c r="K8" t="n">
-        <v>114578110.4567738</v>
+        <v>47227704.69193309</v>
       </c>
       <c r="L8" t="n">
-        <v>245800705.6434319</v>
+        <v>120764204.0012439</v>
       </c>
       <c r="M8" t="n">
-        <v>121418008.2172597</v>
+        <v>136801575.539456</v>
       </c>
       <c r="N8" t="n">
+        <v>113997099.9830643</v>
+      </c>
+      <c r="O8" t="n">
         <v>126347110.9746562</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>225664287.914459</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>136</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="R8" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="S8" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9124,51 +9134,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(1, 0, 1, 12)</t>
+          <t>(1, 0, 0, 12)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-333.959087777356</v>
+        <v>-319.3966155476003</v>
       </c>
       <c r="G9" t="n">
-        <v>-316.5274391067254</v>
+        <v>-290.2700666902398</v>
       </c>
       <c r="H9" t="n">
-        <v>120216571.1924814</v>
+        <v>183781416.6177844</v>
       </c>
       <c r="I9" t="n">
-        <v>99837681.28671519</v>
+        <v>158506192.2814901</v>
       </c>
       <c r="J9" t="n">
-        <v>5.451076019492267</v>
+        <v>8.614236397247806</v>
       </c>
       <c r="K9" t="n">
-        <v>120216571.1924814</v>
+        <v>183781416.6177844</v>
       </c>
       <c r="L9" t="n">
-        <v>123019164.9223385</v>
+        <v>276315592.7991674</v>
       </c>
       <c r="M9" t="n">
-        <v>184222261.0046521</v>
+        <v>272898559.4342</v>
       </c>
       <c r="N9" t="n">
-        <v>126301125.863519</v>
+        <v>206878513.4881969</v>
       </c>
       <c r="O9" t="n">
+        <v>410808457.1051733</v>
+      </c>
+      <c r="P9" t="n">
         <v>446581351.9788048</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>136</v>
       </c>
-      <c r="Q9" s="1" t="n">
+      <c r="R9" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R9" s="1" t="n">
+      <c r="S9" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9190,51 +9203,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(1, 0, 1, 12)</t>
+          <t>(1, 0, 0, 12)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-416.2415610977344</v>
+        <v>-396.0819003047688</v>
       </c>
       <c r="G10" t="n">
-        <v>-398.8099124271038</v>
+        <v>-369.8680063331443</v>
       </c>
       <c r="H10" t="n">
-        <v>213890740.171835</v>
+        <v>292787222.090215</v>
       </c>
       <c r="I10" t="n">
-        <v>187058445.6223809</v>
+        <v>264307829.7977782</v>
       </c>
       <c r="J10" t="n">
-        <v>7.418868911938498</v>
+        <v>10.62431028061732</v>
       </c>
       <c r="K10" t="n">
-        <v>213890740.171835</v>
+        <v>292787222.090215</v>
       </c>
       <c r="L10" t="n">
-        <v>601616154.723429</v>
+        <v>612794215.1061319</v>
       </c>
       <c r="M10" t="n">
-        <v>256045012.7367123</v>
+        <v>628970168.5900235</v>
       </c>
       <c r="N10" t="n">
+        <v>626597402.7774726</v>
+      </c>
+      <c r="O10" t="n">
         <v>596800577.168786</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>592598666.7989789</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>136</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="R10" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R10" s="1" t="n">
+      <c r="S10" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9246,57 +9262,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SARIMA_puro</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>SARIMAX_dummies</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-162.8138061042913</v>
+        <v>-164.9496530473923</v>
       </c>
       <c r="G11" t="n">
-        <v>-145.3821574336607</v>
+        <v>-141.7074548198849</v>
       </c>
       <c r="H11" t="n">
+        <v>189822956.5788961</v>
+      </c>
+      <c r="I11" t="n">
+        <v>151834451.7951483</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12.74734071546342</v>
+      </c>
+      <c r="K11" t="n">
+        <v>234653004.0318806</v>
+      </c>
+      <c r="L11" t="n">
+        <v>202101783.0235505</v>
+      </c>
+      <c r="M11" t="n">
+        <v>365577516.549103</v>
+      </c>
+      <c r="N11" t="n">
+        <v>189822956.5788961</v>
+      </c>
+      <c r="O11" t="n">
         <v>194883589.0975286</v>
       </c>
-      <c r="I11" t="n">
-        <v>156493956.5948537</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13.11216275964155</v>
-      </c>
-      <c r="K11" t="n">
-        <v>352437353.6478392</v>
-      </c>
-      <c r="L11" t="n">
-        <v>232999471.1762201</v>
-      </c>
-      <c r="M11" t="n">
-        <v>209420309.6801475</v>
-      </c>
-      <c r="N11" t="n">
-        <v>194883589.0975286</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>403756283.3201762</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>136</v>
       </c>
-      <c r="Q11" s="1" t="n">
+      <c r="R11" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R11" s="1" t="n">
+      <c r="S11" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9308,7 +9331,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
+          <t>SARIMAX_pib_var_12m+out1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9318,51 +9341,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(2, 0, 1, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-356.3971758021786</v>
+        <v>-367.6080048418985</v>
       </c>
       <c r="G12" t="n">
-        <v>-327.3444280177943</v>
+        <v>-338.5552570575142</v>
       </c>
       <c r="H12" t="n">
-        <v>290157425.9695348</v>
+        <v>303275268.4611938</v>
       </c>
       <c r="I12" t="n">
-        <v>222245756.8254727</v>
+        <v>226172392.9646232</v>
       </c>
       <c r="J12" t="n">
-        <v>3.195569268833484</v>
+        <v>3.280470548132171</v>
       </c>
       <c r="K12" t="n">
-        <v>801279146.0694308</v>
+        <v>402263079.4028254</v>
       </c>
       <c r="L12" t="n">
-        <v>290157425.9695348</v>
+        <v>303275268.4611938</v>
       </c>
       <c r="M12" t="n">
-        <v>291674362.4773701</v>
+        <v>326791229.0708854</v>
       </c>
       <c r="N12" t="n">
+        <v>365585795.0156326</v>
+      </c>
+      <c r="O12" t="n">
         <v>314849075.5269047</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1367695875.686009</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>136</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="R12" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R12" s="1" t="n">
+      <c r="S12" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9374,10 +9400,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SARIMA_puro</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>SARIMAX_pib_var_mom</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>pib_var_mom</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>(0, 1, 2)</t>
@@ -9389,42 +9419,45 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-409.2162051860296</v>
+        <v>-405.2811475830217</v>
       </c>
       <c r="G13" t="n">
-        <v>-391.784556515399</v>
+        <v>-379.1336745770758</v>
       </c>
       <c r="H13" t="n">
+        <v>59375414.2376551</v>
+      </c>
+      <c r="I13" t="n">
+        <v>47524594.93435598</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.348219674346985</v>
+      </c>
+      <c r="K13" t="n">
+        <v>66141770.69945709</v>
+      </c>
+      <c r="L13" t="n">
+        <v>85800304.38151459</v>
+      </c>
+      <c r="M13" t="n">
+        <v>59375414.2376551</v>
+      </c>
+      <c r="N13" t="n">
+        <v>60058565.39121196</v>
+      </c>
+      <c r="O13" t="n">
         <v>84482931.03852427</v>
       </c>
-      <c r="I13" t="n">
-        <v>65056217.35807408</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.519532941466078</v>
-      </c>
-      <c r="K13" t="n">
-        <v>100294521.0428367</v>
-      </c>
-      <c r="L13" t="n">
-        <v>97689721.75155345</v>
-      </c>
-      <c r="M13" t="n">
-        <v>86084481.09251653</v>
-      </c>
-      <c r="N13" t="n">
-        <v>84482931.03852427</v>
-      </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>224363928.3074245</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>136</v>
       </c>
-      <c r="Q13" s="1" t="n">
+      <c r="R13" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R13" s="1" t="n">
+      <c r="S13" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9436,12 +9469,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
+          <t>SARIMAX_dummies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9455,42 +9488,45 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-268.6473617578308</v>
+        <v>-266.0154442876612</v>
       </c>
       <c r="G14" t="n">
-        <v>-251.2157130872002</v>
+        <v>-242.7732460601538</v>
       </c>
       <c r="H14" t="n">
-        <v>77184986.31963259</v>
+        <v>147369602.6669436</v>
       </c>
       <c r="I14" t="n">
-        <v>65601933.89356694</v>
+        <v>125808598.5819572</v>
       </c>
       <c r="J14" t="n">
-        <v>3.314220464268232</v>
+        <v>5.929893201340746</v>
       </c>
       <c r="K14" t="n">
-        <v>77184986.31963259</v>
+        <v>227141434.0552925</v>
       </c>
       <c r="L14" t="n">
-        <v>94881508.41368236</v>
+        <v>257797304.151022</v>
       </c>
       <c r="M14" t="n">
-        <v>151618248.950521</v>
+        <v>217525732.211706</v>
       </c>
       <c r="N14" t="n">
+        <v>147369602.6669436</v>
+      </c>
+      <c r="O14" t="n">
         <v>155010851.8568569</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>470575174.7278251</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>136</v>
       </c>
-      <c r="Q14" s="1" t="n">
+      <c r="R14" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R14" s="1" t="n">
+      <c r="S14" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9502,12 +9538,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_mom</t>
+          <t>SARIMAX_dummies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9517,46 +9553,49 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(2, 0, 1, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-290.6184413306105</v>
+        <v>-270.2064015860201</v>
       </c>
       <c r="G15" t="n">
-        <v>-273.1867926599799</v>
+        <v>-249.8694781369511</v>
       </c>
       <c r="H15" t="n">
-        <v>150426843.1553291</v>
+        <v>150546928.8824227</v>
       </c>
       <c r="I15" t="n">
-        <v>102725356.4714863</v>
+        <v>92878307.10161684</v>
       </c>
       <c r="J15" t="n">
-        <v>4.839822095247459</v>
+        <v>4.355451079797771</v>
       </c>
       <c r="K15" t="n">
-        <v>184200850.1653788</v>
+        <v>196889882.0430764</v>
       </c>
       <c r="L15" t="n">
-        <v>239817746.1962377</v>
+        <v>164473237.6682884</v>
       </c>
       <c r="M15" t="n">
-        <v>150426843.1553291</v>
+        <v>183937098.2002094</v>
       </c>
       <c r="N15" t="n">
-        <v>177495884.2868564</v>
+        <v>150546928.8824227</v>
       </c>
       <c r="O15" t="n">
+        <v>151237023.5209538</v>
+      </c>
+      <c r="P15" t="n">
         <v>476826124.4213786</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>136</v>
       </c>
-      <c r="Q15" s="1" t="n">
+      <c r="R15" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R15" s="1" t="n">
+      <c r="S15" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9578,7 +9617,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9587,42 +9626,45 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-358.0542587151208</v>
+        <v>-343.6765135480557</v>
       </c>
       <c r="G16" t="n">
-        <v>-343.5278848229286</v>
+        <v>-317.4626195764312</v>
       </c>
       <c r="H16" t="n">
-        <v>86690282.52626842</v>
+        <v>109982109.0870985</v>
       </c>
       <c r="I16" t="n">
-        <v>69980616.91445215</v>
+        <v>94374523.00515294</v>
       </c>
       <c r="J16" t="n">
-        <v>8.074077532753062</v>
+        <v>10.88342577763354</v>
       </c>
       <c r="K16" t="n">
-        <v>86690282.52626842</v>
+        <v>109982109.0870985</v>
       </c>
       <c r="L16" t="n">
-        <v>94353954.11581071</v>
+        <v>125765846.0633651</v>
       </c>
       <c r="M16" t="n">
-        <v>117419535.7013695</v>
+        <v>147278499.4332603</v>
       </c>
       <c r="N16" t="n">
+        <v>140728943.811683</v>
+      </c>
+      <c r="O16" t="n">
         <v>114915585.0661163</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>217669138.6100876</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>136</v>
       </c>
-      <c r="Q16" s="1" t="n">
+      <c r="R16" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R16" s="1" t="n">
+      <c r="S16" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9634,10 +9676,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SARIMA_puro</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>SARIMAX_dummies</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>(1, 1, 1)</t>
@@ -9645,46 +9691,49 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(1, 0, 2, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-275.6895326066527</v>
+        <v>-271.0426768072571</v>
       </c>
       <c r="G17" t="n">
-        <v>-255.3526091575837</v>
+        <v>-247.8004785797496</v>
       </c>
       <c r="H17" t="n">
-        <v>179740829.0259829</v>
+        <v>174137542.5428779</v>
       </c>
       <c r="I17" t="n">
-        <v>148499159.0903953</v>
+        <v>142702623.7312899</v>
       </c>
       <c r="J17" t="n">
-        <v>6.563710163005353</v>
+        <v>6.304789336828903</v>
       </c>
       <c r="K17" t="n">
-        <v>334736071.4244649</v>
+        <v>384171399.4376704</v>
       </c>
       <c r="L17" t="n">
-        <v>233403584.2206423</v>
+        <v>186909888.1465677</v>
       </c>
       <c r="M17" t="n">
-        <v>285651401.3453983</v>
+        <v>394919871.4318012</v>
       </c>
       <c r="N17" t="n">
-        <v>179740829.0259829</v>
+        <v>174137542.5428779</v>
       </c>
       <c r="O17" t="n">
+        <v>587994855.3148432</v>
+      </c>
+      <c r="P17" t="n">
         <v>509273008.0746232</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>136</v>
       </c>
-      <c r="Q17" s="1" t="n">
+      <c r="R17" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R17" s="1" t="n">
+      <c r="S17" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9696,17 +9745,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+          <t>SARIMA_puro+out3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9715,42 +9760,45 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-258.8668463065112</v>
+        <v>-277.1197390264622</v>
       </c>
       <c r="G18" t="n">
-        <v>-241.4351976358806</v>
+        <v>-250.9722660205164</v>
       </c>
       <c r="H18" t="n">
-        <v>29752212.89205748</v>
+        <v>76120899.86638413</v>
       </c>
       <c r="I18" t="n">
-        <v>22113971.7614481</v>
+        <v>68157699.86603524</v>
       </c>
       <c r="J18" t="n">
-        <v>3.31218737014069</v>
+        <v>9.786644873448957</v>
       </c>
       <c r="K18" t="n">
-        <v>29752212.89205748</v>
+        <v>76684155.49007545</v>
       </c>
       <c r="L18" t="n">
-        <v>81474071.66625489</v>
+        <v>80482907.86476828</v>
       </c>
       <c r="M18" t="n">
-        <v>99170203.36548507</v>
+        <v>86834603.58130717</v>
       </c>
       <c r="N18" t="n">
+        <v>88472903.57292093</v>
+      </c>
+      <c r="O18" t="n">
         <v>76120899.86638413</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>202585036.1196307</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>136</v>
       </c>
-      <c r="Q18" s="1" t="n">
+      <c r="R18" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R18" s="1" t="n">
+      <c r="S18" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9762,7 +9810,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
+          <t>SARIMAX_log_pib+out3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9772,7 +9820,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9781,42 +9829,45 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-265.1435189164943</v>
+        <v>-306.4215530208585</v>
       </c>
       <c r="G19" t="n">
-        <v>-247.7118702458637</v>
+        <v>-274.3823492777619</v>
       </c>
       <c r="H19" t="n">
-        <v>331284609.9997428</v>
+        <v>296643672.4112792</v>
       </c>
       <c r="I19" t="n">
-        <v>268384486.8254166</v>
+        <v>220410148.871189</v>
       </c>
       <c r="J19" t="n">
-        <v>6.113553524341292</v>
+        <v>5.001820717863521</v>
       </c>
       <c r="K19" t="n">
-        <v>331284609.9997428</v>
+        <v>296643672.4112792</v>
       </c>
       <c r="L19" t="n">
-        <v>361358813.346</v>
+        <v>1062990769.806968</v>
       </c>
       <c r="M19" t="n">
-        <v>535610628.0227056</v>
+        <v>617787954.1975095</v>
       </c>
       <c r="N19" t="n">
+        <v>604314372.793875</v>
+      </c>
+      <c r="O19" t="n">
         <v>489287198.3284659</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>1068011154.306494</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>136</v>
       </c>
-      <c r="Q19" s="1" t="n">
+      <c r="R19" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R19" s="1" t="n">
+      <c r="S19" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9838,7 +9889,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9847,42 +9898,45 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-286.1835704331784</v>
+        <v>-270.7460291375033</v>
       </c>
       <c r="G20" t="n">
-        <v>-271.6571965409862</v>
+        <v>-244.5321351658789</v>
       </c>
       <c r="H20" t="n">
-        <v>579779172.1067623</v>
+        <v>403644145.8824183</v>
       </c>
       <c r="I20" t="n">
-        <v>391348783.3152097</v>
+        <v>301862885.3416426</v>
       </c>
       <c r="J20" t="n">
-        <v>7.112433915909932</v>
+        <v>5.758666178502465</v>
       </c>
       <c r="K20" t="n">
-        <v>579779172.1067623</v>
+        <v>403644145.8824183</v>
       </c>
       <c r="L20" t="n">
-        <v>1051674250.263158</v>
+        <v>897679786.5301263</v>
       </c>
       <c r="M20" t="n">
-        <v>1166042657.27342</v>
+        <v>931559128.0166049</v>
       </c>
       <c r="N20" t="n">
+        <v>910083233.6692575</v>
+      </c>
+      <c r="O20" t="n">
         <v>879922205.9855846</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>1191952614.696857</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>136</v>
       </c>
-      <c r="Q20" s="1" t="n">
+      <c r="R20" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R20" s="1" t="n">
+      <c r="S20" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9894,17 +9948,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
+          <t>SARIMAX_dummies+out3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9913,42 +9967,45 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-271.6979565262527</v>
+        <v>-317.8513208451864</v>
       </c>
       <c r="G21" t="n">
-        <v>-257.1715826340605</v>
+        <v>-285.8932982823636</v>
       </c>
       <c r="H21" t="n">
-        <v>76156461.40714966</v>
+        <v>75977325.92501538</v>
       </c>
       <c r="I21" t="n">
-        <v>54996019.42541545</v>
+        <v>54280969.68654405</v>
       </c>
       <c r="J21" t="n">
-        <v>7.083548932394715</v>
+        <v>6.989835762371596</v>
       </c>
       <c r="K21" t="n">
-        <v>76797746.85047913</v>
+        <v>99490355.14828005</v>
       </c>
       <c r="L21" t="n">
-        <v>76156461.40714966</v>
+        <v>76865433.2665381</v>
       </c>
       <c r="M21" t="n">
-        <v>84117006.99455473</v>
+        <v>86940377.53618504</v>
       </c>
       <c r="N21" t="n">
+        <v>75977325.92501538</v>
+      </c>
+      <c r="O21" t="n">
         <v>81503544.57559739</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>169972974.6946256</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>136</v>
       </c>
-      <c r="Q21" s="1" t="n">
+      <c r="R21" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R21" s="1" t="n">
+      <c r="S21" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -9960,17 +10017,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
+          <t>SARIMAX_pib_var_mom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9979,42 +10036,45 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-242.6339454970506</v>
+        <v>-234.7616771464551</v>
       </c>
       <c r="G22" t="n">
-        <v>-219.3917472695432</v>
+        <v>-211.5194789189477</v>
       </c>
       <c r="H22" t="n">
-        <v>57633328.26331138</v>
+        <v>47916488.79513602</v>
       </c>
       <c r="I22" t="n">
-        <v>46406924.38963307</v>
+        <v>36830137.67989063</v>
       </c>
       <c r="J22" t="n">
-        <v>7.192223867866011</v>
+        <v>6.105887452451157</v>
       </c>
       <c r="K22" t="n">
-        <v>66121270.64452004</v>
+        <v>52406554.75923501</v>
       </c>
       <c r="L22" t="n">
-        <v>57633328.26331138</v>
+        <v>68740598.56476997</v>
       </c>
       <c r="M22" t="n">
-        <v>68137895.20888004</v>
+        <v>47916488.79513602</v>
       </c>
       <c r="N22" t="n">
+        <v>48633299.39237277</v>
+      </c>
+      <c r="O22" t="n">
         <v>59744322.93945628</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>171899715.0931611</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>136</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="R22" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R22" s="1" t="n">
+      <c r="S22" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -10026,14 +10086,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+          <t>SARIMA_puro+out2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>(0, 1, 1)</t>
@@ -10041,46 +10097,49 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(2, 0, 1, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-277.4087781403047</v>
+        <v>-301.0628930143893</v>
       </c>
       <c r="G23" t="n">
-        <v>-259.9771294696741</v>
+        <v>-280.7259695653203</v>
       </c>
       <c r="H23" t="n">
-        <v>14129246.09251841</v>
+        <v>11550603.57730541</v>
       </c>
       <c r="I23" t="n">
-        <v>11327489.04660899</v>
+        <v>8971071.929162547</v>
       </c>
       <c r="J23" t="n">
-        <v>6.715891520648447</v>
+        <v>5.27068760434325</v>
       </c>
       <c r="K23" t="n">
-        <v>24689233.96531435</v>
+        <v>17928672.28600492</v>
       </c>
       <c r="L23" t="n">
-        <v>14129246.09251841</v>
+        <v>14264365.6032207</v>
       </c>
       <c r="M23" t="n">
-        <v>15204945.19093669</v>
+        <v>13655879.87400663</v>
       </c>
       <c r="N23" t="n">
-        <v>15136125.43366308</v>
+        <v>12015557.87490111</v>
       </c>
       <c r="O23" t="n">
+        <v>11550603.57730541</v>
+      </c>
+      <c r="P23" t="n">
         <v>43290355.50726472</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>136</v>
       </c>
-      <c r="Q23" s="1" t="n">
+      <c r="R23" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R23" s="1" t="n">
+      <c r="S23" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -10092,14 +10151,10 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
+          <t>SARIMA_puro</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>(0, 1, 1)</t>
@@ -10111,42 +10166,45 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-242.8187680536079</v>
+        <v>-235.2210207961478</v>
       </c>
       <c r="G24" t="n">
-        <v>-225.3871193829773</v>
+        <v>-220.6946469039556</v>
       </c>
       <c r="H24" t="n">
-        <v>335564965.3136093</v>
+        <v>445047854.2251575</v>
       </c>
       <c r="I24" t="n">
-        <v>248452331.4664231</v>
+        <v>345549670.1661455</v>
       </c>
       <c r="J24" t="n">
-        <v>5.748175034765514</v>
+        <v>7.682929420202295</v>
       </c>
       <c r="K24" t="n">
-        <v>335564965.3136093</v>
+        <v>465198963.3518437</v>
       </c>
       <c r="L24" t="n">
-        <v>409310073.3755224</v>
+        <v>459077695.7406542</v>
       </c>
       <c r="M24" t="n">
-        <v>430242649.8567045</v>
+        <v>626584713.4111029</v>
       </c>
       <c r="N24" t="n">
+        <v>639970604.8967795</v>
+      </c>
+      <c r="O24" t="n">
         <v>445047854.2251575</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>920855346.3898607</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>136</v>
       </c>
-      <c r="Q24" s="1" t="n">
+      <c r="R24" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R24" s="1" t="n">
+      <c r="S24" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -10158,61 +10216,64 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
+          <t>SARIMAX_pib_var_12m+out4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(1, 1, 2)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(1, 0, 1, 12)</t>
+          <t>(0, 0, 0, 12)</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-313.0804435183616</v>
+        <v>-325.962241204537</v>
       </c>
       <c r="G25" t="n">
-        <v>-292.7435200692926</v>
+        <v>-288.1936690848374</v>
       </c>
       <c r="H25" t="n">
-        <v>177122431.7761291</v>
+        <v>147185320.0338855</v>
       </c>
       <c r="I25" t="n">
-        <v>141159140.8549074</v>
+        <v>113555766.2956067</v>
       </c>
       <c r="J25" t="n">
-        <v>3.884583776721018</v>
+        <v>3.158096378236425</v>
       </c>
       <c r="K25" t="n">
-        <v>177122431.7761291</v>
+        <v>385142896.2788457</v>
       </c>
       <c r="L25" t="n">
-        <v>201443047.5310932</v>
+        <v>147185320.0338855</v>
       </c>
       <c r="M25" t="n">
-        <v>223941266.7764835</v>
+        <v>152096172.7886318</v>
       </c>
       <c r="N25" t="n">
+        <v>176842122.4462956</v>
+      </c>
+      <c r="O25" t="n">
         <v>230490202.9167342</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>880757725.5696619</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>136</v>
       </c>
-      <c r="Q25" s="1" t="n">
+      <c r="R25" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R25" s="1" t="n">
+      <c r="S25" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -10224,17 +10285,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
+          <t>SARIMAX_log_pib</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(2, 1, 1)</t>
+          <t>(0, 0, 2)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10243,42 +10304,45 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-294.4019749409863</v>
+        <v>-316.3163493775793</v>
       </c>
       <c r="G26" t="n">
-        <v>-271.1597767134788</v>
+        <v>-290.1024554059548</v>
       </c>
       <c r="H26" t="n">
-        <v>17471227.55127371</v>
+        <v>23462744.43802107</v>
       </c>
       <c r="I26" t="n">
-        <v>14514234.83454414</v>
+        <v>17872494.3712892</v>
       </c>
       <c r="J26" t="n">
-        <v>2.936388515072821</v>
+        <v>3.600224654963592</v>
       </c>
       <c r="K26" t="n">
-        <v>30219657.83250977</v>
+        <v>23462744.43802107</v>
       </c>
       <c r="L26" t="n">
-        <v>17471227.55127371</v>
+        <v>53957816.87353569</v>
       </c>
       <c r="M26" t="n">
-        <v>52001353.08117141</v>
+        <v>49603789.24937128</v>
       </c>
       <c r="N26" t="n">
-        <v>54689888.13083836</v>
+        <v>44905296.99422503</v>
       </c>
       <c r="O26" t="n">
+        <v>48539162.07313929</v>
+      </c>
+      <c r="P26" t="n">
         <v>110554363.5568706</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>136</v>
       </c>
-      <c r="Q26" s="1" t="n">
+      <c r="R26" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R26" s="1" t="n">
+      <c r="S26" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -10290,12 +10354,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
+          <t>SARIMAX_pib_var_mom+out3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10309,42 +10373,45 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-401.5480502719084</v>
+        <v>-409.1460628323409</v>
       </c>
       <c r="G27" t="n">
-        <v>-384.1164016012779</v>
+        <v>-377.1880402695182</v>
       </c>
       <c r="H27" t="n">
-        <v>657340553.2753468</v>
+        <v>1404358411.506782</v>
       </c>
       <c r="I27" t="n">
-        <v>516341053.1036725</v>
+        <v>1210959881.461246</v>
       </c>
       <c r="J27" t="n">
-        <v>2.760607017098619</v>
+        <v>6.223649109595669</v>
       </c>
       <c r="K27" t="n">
-        <v>657340553.2753468</v>
+        <v>2431343309.03903</v>
       </c>
       <c r="L27" t="n">
-        <v>1333019730.12152</v>
+        <v>3624437407.557021</v>
       </c>
       <c r="M27" t="n">
-        <v>1379939715.420467</v>
+        <v>1404358411.506782</v>
       </c>
       <c r="N27" t="n">
-        <v>976635776.0471323</v>
+        <v>3624775057.380325</v>
       </c>
       <c r="O27" t="n">
+        <v>3548581855.191233</v>
+      </c>
+      <c r="P27" t="n">
         <v>3016591733.957785</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>136</v>
       </c>
-      <c r="Q27" s="1" t="n">
+      <c r="R27" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R27" s="1" t="n">
+      <c r="S27" s="1" t="n">
         <v>46113</v>
       </c>
     </row>
@@ -10356,14 +10423,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_mom</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
+          <t>SARIMA_puro</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>(1, 1, 1)</t>
@@ -10371,46 +10434,49 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(1, 0, 2, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-356.6372982098709</v>
+        <v>-361.2349145154329</v>
       </c>
       <c r="G28" t="n">
-        <v>-333.3950999823635</v>
+        <v>-343.8032658448024</v>
       </c>
       <c r="H28" t="n">
-        <v>30864531.61349719</v>
+        <v>32063286.58699303</v>
       </c>
       <c r="I28" t="n">
-        <v>23923257.41620488</v>
+        <v>27619314.01566176</v>
       </c>
       <c r="J28" t="n">
-        <v>4.674212848372203</v>
+        <v>5.404402259758259</v>
       </c>
       <c r="K28" t="n">
-        <v>41470725.16819794</v>
+        <v>38461294.7978078</v>
       </c>
       <c r="L28" t="n">
-        <v>31019520.42381774</v>
+        <v>51064566.10638636</v>
       </c>
       <c r="M28" t="n">
-        <v>30864531.61349719</v>
+        <v>55385935.67931326</v>
       </c>
       <c r="N28" t="n">
-        <v>34109959.59748114</v>
+        <v>33175482.68379957</v>
       </c>
       <c r="O28" t="n">
+        <v>32063286.58699303</v>
+      </c>
+      <c r="P28" t="n">
         <v>136793906.1677228</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>136</v>
       </c>
-      <c r="Q28" s="1" t="n">
+      <c r="R28" s="1" t="n">
         <v>42005</v>
       </c>
-      <c r="R28" s="1" t="n">
+      <c r="S28" s="1" t="n">
         <v>46113</v>
       </c>
     </row>

--- a/Planilhas/previsoes_icms_estados_com_pib.xlsx
+++ b/Planilhas/previsoes_icms_estados_com_pib.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="previsoes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="modelos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pib_tratado" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="previsoes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="modelos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pib_tratado" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,36 +481,30 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C2" t="n">
         <v>2026</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>207406151.5798294</v>
+        <v>215155939.1176117</v>
       </c>
       <c r="G2" t="n">
-        <v>159381030.9606968</v>
+        <v>166530026.6745651</v>
       </c>
       <c r="H2" t="n">
-        <v>269902330.6215352</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>6.339104426528941</v>
-      </c>
+        <v>277980368.2374107</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,36 +513,30 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C3" t="n">
         <v>2026</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>207936450.9006145</v>
+        <v>213836366.502095</v>
       </c>
       <c r="G3" t="n">
-        <v>159060464.7410969</v>
+        <v>164623266.242951</v>
       </c>
       <c r="H3" t="n">
-        <v>271831015.2275836</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>6.365548028661205</v>
-      </c>
+        <v>277761416.6112819</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,36 +545,30 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C4" t="n">
         <v>2026</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>210194713.187289</v>
+        <v>216730510.5253341</v>
       </c>
       <c r="G4" t="n">
-        <v>160708385.1284049</v>
+        <v>166783957.7861002</v>
       </c>
       <c r="H4" t="n">
-        <v>274919179.9580694</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>7.430178721321767</v>
-      </c>
+        <v>281634485.8107607</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,111 +577,105 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C5" t="n">
         <v>2026</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>209342829.2177058</v>
+        <v>221196941.3244698</v>
       </c>
       <c r="G5" t="n">
-        <v>160019590.613479</v>
+        <v>170203451.5015088</v>
       </c>
       <c r="H5" t="n">
-        <v>273869093.0083035</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>7.21752999809735</v>
-      </c>
+        <v>287468241.2117079</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C6" t="n">
         <v>2026</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>213213411.4389406</v>
+        <v>827188908.6569142</v>
       </c>
       <c r="G6" t="n">
-        <v>162945230.7759643</v>
+        <v>710564576.0742162</v>
       </c>
       <c r="H6" t="n">
-        <v>278989195.3323539</v>
+        <v>962954689.3336122</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7.231297900402511</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C7" t="n">
         <v>2026</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>218111420.3501868</v>
+        <v>851256260.0549227</v>
       </c>
       <c r="G7" t="n">
-        <v>166655514.1329136</v>
+        <v>711172794.2393541</v>
       </c>
       <c r="H7" t="n">
-        <v>285454651.3788622</v>
+        <v>1018932706.864499</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7.311710033254837</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="8">
@@ -709,27 +685,27 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C8" t="n">
         <v>2026</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>780280775.6207198</v>
+        <v>875684754.1050519</v>
       </c>
       <c r="G8" t="n">
-        <v>672342480.9528507</v>
+        <v>713338792.8055595</v>
       </c>
       <c r="H8" t="n">
-        <v>905547553.5926577</v>
+        <v>1074978392.1832</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -737,7 +713,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7.033361733229282</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="9">
@@ -747,27 +723,27 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C9" t="n">
         <v>2026</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>794232911.9533757</v>
+        <v>919658520.367658</v>
       </c>
       <c r="G9" t="n">
-        <v>675966190.5808948</v>
+        <v>738659120.3943915</v>
       </c>
       <c r="H9" t="n">
-        <v>933191522.3272521</v>
+        <v>1145009613.681136</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -775,13 +751,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7.050430174458898</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -799,27 +775,27 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>807845264.0203948</v>
+        <v>1486687734.971693</v>
       </c>
       <c r="G10" t="n">
-        <v>680166892.9407607</v>
+        <v>1265418264.990952</v>
       </c>
       <c r="H10" t="n">
-        <v>959490938.7290934</v>
+        <v>1746648110.323478</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7.061126878716963</v>
+        <v>1.075411853094543</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
@@ -837,27 +813,27 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>840412401.2847667</v>
+        <v>1496793142.874879</v>
       </c>
       <c r="G11" t="n">
-        <v>700851506.8703945</v>
+        <v>1261491757.861546</v>
       </c>
       <c r="H11" t="n">
-        <v>1007764123.083836</v>
+        <v>1775984423.6756</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>7.068702085302047</v>
+        <v>0.7603971048866009</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="B12" s="1" t="n">
@@ -875,27 +851,27 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>877772568.0987439</v>
+        <v>1482318561.906137</v>
       </c>
       <c r="G12" t="n">
-        <v>725775046.170084</v>
+        <v>1245198691.23624</v>
       </c>
       <c r="H12" t="n">
-        <v>1061602607.271375</v>
+        <v>1764592538.071189</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>7.066579967851128</v>
+        <v>-0.2119867351621618</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="B13" s="1" t="n">
@@ -913,51 +889,51 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>933272256.7352694</v>
+        <v>1552355431.001843</v>
       </c>
       <c r="G13" t="n">
-        <v>765745614.0648912</v>
+        <v>1299837618.908867</v>
       </c>
       <c r="H13" t="n">
-        <v>1137449681.974845</v>
+        <v>1853929559.435127</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7.063721708236462</v>
+        <v>-0.2854178679703168</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C14" t="n">
         <v>2026</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1465587652.839658</v>
+        <v>166975663.5108964</v>
       </c>
       <c r="G14" t="n">
-        <v>1246862045.636779</v>
+        <v>136864057.5012145</v>
       </c>
       <c r="H14" t="n">
-        <v>1722682293.25971</v>
+        <v>203712155.7985135</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -965,37 +941,37 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-2.238291510711132</v>
+        <v>1.075411853094543</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C15" t="n">
         <v>2026</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1521520208.957679</v>
+        <v>164432078.6222007</v>
       </c>
       <c r="G15" t="n">
-        <v>1281495973.445816</v>
+        <v>129899653.2561978</v>
       </c>
       <c r="H15" t="n">
-        <v>1806500991.214002</v>
+        <v>208144577.7741333</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1003,37 +979,37 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1.721493938411056</v>
+        <v>0.7603971048866009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C16" t="n">
         <v>2026</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1526150304.451783</v>
+        <v>166982369.3810335</v>
       </c>
       <c r="G16" t="n">
-        <v>1281332766.250472</v>
+        <v>126082051.0778152</v>
       </c>
       <c r="H16" t="n">
-        <v>1817743846.974234</v>
+        <v>221150524.1685437</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1041,37 +1017,37 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1.075411853094543</v>
+        <v>-0.2119867351621618</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C17" t="n">
         <v>2026</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1517594394.417916</v>
+        <v>170574848.8361162</v>
       </c>
       <c r="G17" t="n">
-        <v>1270193531.914188</v>
+        <v>124434443.4814246</v>
       </c>
       <c r="H17" t="n">
-        <v>1813182549.038735</v>
+        <v>233824158.6607592</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1079,165 +1055,165 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.7603971048866009</v>
+        <v>-0.2854178679703168</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C18" t="n">
         <v>2026</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1501762924.033504</v>
+        <v>3748411196.580654</v>
       </c>
       <c r="G18" t="n">
-        <v>1253107458.669201</v>
+        <v>3284760426.724011</v>
       </c>
       <c r="H18" t="n">
-        <v>1799759361.736445</v>
+        <v>4277507237.465192</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-0.2119867351621618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C19" t="n">
         <v>2026</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1574334157.188555</v>
+        <v>3874489138.850692</v>
       </c>
       <c r="G19" t="n">
-        <v>1309720568.354516</v>
+        <v>3335873581.896645</v>
       </c>
       <c r="H19" t="n">
-        <v>1892409799.751812</v>
+        <v>4500070436.882966</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>-0.2854178679703168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C20" t="n">
         <v>2026</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>151431257.4462026</v>
+        <v>4107613044.672731</v>
       </c>
       <c r="G20" t="n">
-        <v>123785205.9334852</v>
+        <v>3517730427.947528</v>
       </c>
       <c r="H20" t="n">
-        <v>185251747.644707</v>
+        <v>4796412138.553233</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7.033361733229282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C21" t="n">
         <v>2026</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>147599087.8507375</v>
+        <v>3954736922.318766</v>
       </c>
       <c r="G21" t="n">
-        <v>116930175.6112476</v>
+        <v>3379699552.667824</v>
       </c>
       <c r="H21" t="n">
-        <v>186311964.5590796</v>
+        <v>4627613751.170765</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7.050430174458898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
@@ -1255,27 +1231,27 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>156862802.5368105</v>
+        <v>2163031704.381512</v>
       </c>
       <c r="G22" t="n">
-        <v>119659265.0555028</v>
+        <v>1896976433.383531</v>
       </c>
       <c r="H22" t="n">
-        <v>205633377.4763632</v>
+        <v>2466401833.898612</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7.061126878716963</v>
+        <v>7.430178721321767</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
@@ -1293,27 +1269,27 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>153813899.562394</v>
+        <v>2136196155.435845</v>
       </c>
       <c r="G23" t="n">
-        <v>114360529.4248855</v>
+        <v>1810448735.097286</v>
       </c>
       <c r="H23" t="n">
-        <v>206878333.0889508</v>
+        <v>2520554117.901422</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7.068702085302047</v>
+        <v>7.21752999809735</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
@@ -1331,27 +1307,27 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>148874521.2392505</v>
+        <v>2179662211.847013</v>
       </c>
       <c r="G24" t="n">
-        <v>108210089.7229161</v>
+        <v>1826484139.492777</v>
       </c>
       <c r="H24" t="n">
-        <v>204820300.3155108</v>
+        <v>2601132555.727074</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>7.066579967851128</v>
+        <v>7.231297900402511</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
@@ -1369,243 +1345,279 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>151075933.8510561</v>
+        <v>2201232284.547151</v>
       </c>
       <c r="G25" t="n">
-        <v>107787834.8387968</v>
+        <v>1831735744.212626</v>
       </c>
       <c r="H25" t="n">
-        <v>211748736.0526654</v>
+        <v>2645263426.147467</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>7.063721708236462</v>
+        <v>7.311710033254837</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C26" t="n">
         <v>2026</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3635601511.476365</v>
+        <v>1217781030.65529</v>
       </c>
       <c r="G26" t="n">
-        <v>3161797477.855823</v>
+        <v>1072374396.433239</v>
       </c>
       <c r="H26" t="n">
-        <v>4180406380.491125</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>1382903810.046516</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>7.061126878716963</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C27" t="n">
         <v>2026</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3778281749.463452</v>
+        <v>1285805579.162115</v>
       </c>
       <c r="G27" t="n">
-        <v>3213849216.257967</v>
+        <v>1117036859.381505</v>
       </c>
       <c r="H27" t="n">
-        <v>4441842792.78358</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+        <v>1480072903.162604</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>7.068702085302047</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C28" t="n">
         <v>2026</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3782756473.036574</v>
+        <v>1274094019.172597</v>
       </c>
       <c r="G28" t="n">
-        <v>3194376120.510206</v>
+        <v>1093396275.765151</v>
       </c>
       <c r="H28" t="n">
-        <v>4479512115.816415</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+        <v>1484654379.817963</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>7.066579967851128</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C29" t="n">
         <v>2026</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3880368801.894344</v>
+        <v>1279971284.984542</v>
       </c>
       <c r="G29" t="n">
-        <v>3265252115.6965</v>
+        <v>1086178930.26141</v>
       </c>
       <c r="H29" t="n">
-        <v>4611362769.304303</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+        <v>1508339413.277594</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>7.063721708236462</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C30" t="n">
         <v>2026</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4040657222.547934</v>
+        <v>2185559995.051222</v>
       </c>
       <c r="G30" t="n">
-        <v>3394136840.223615</v>
+        <v>1905343512.667652</v>
       </c>
       <c r="H30" t="n">
-        <v>4810327797.229626</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+        <v>2506987564.29518</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>7.061126878716963</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C31" t="n">
         <v>2026</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4068580957.011603</v>
+        <v>2218967404.426049</v>
       </c>
       <c r="G31" t="n">
-        <v>3412812491.185352</v>
+        <v>1915192539.071785</v>
       </c>
       <c r="H31" t="n">
-        <v>4850354669.795548</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+        <v>2570924980.88555</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>7.068702085302047</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C32" t="n">
         <v>2026</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1955736899.787891</v>
+        <v>2206338105.204497</v>
       </c>
       <c r="G32" t="n">
-        <v>1726908828.005319</v>
+        <v>1897923151.84743</v>
       </c>
       <c r="H32" t="n">
-        <v>2214886367.573871</v>
+        <v>2564870885.177279</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1613,37 +1625,37 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>7.033361733229282</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C33" t="n">
         <v>2026</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2025446490.989215</v>
+        <v>2202923198.380638</v>
       </c>
       <c r="G33" t="n">
-        <v>1759616176.851628</v>
+        <v>1880210637.247067</v>
       </c>
       <c r="H33" t="n">
-        <v>2331436560.898612</v>
+        <v>2581024977.642381</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1651,13 +1663,13 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>7.050430174458898</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -1675,13 +1687,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2046147169.539501</v>
+        <v>3012050779.686258</v>
       </c>
       <c r="G34" t="n">
-        <v>1752449635.991932</v>
+        <v>2722721618.288314</v>
       </c>
       <c r="H34" t="n">
-        <v>2389066226.741928</v>
+        <v>3332125413.949644</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1695,7 +1707,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -1713,13 +1725,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2092874729.45274</v>
+        <v>3063496019.770922</v>
       </c>
       <c r="G35" t="n">
-        <v>1769745684.913527</v>
+        <v>2747019800.948843</v>
       </c>
       <c r="H35" t="n">
-        <v>2475002295.8219</v>
+        <v>3416432549.889382</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1733,7 +1745,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
@@ -1751,13 +1763,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2156862274.330124</v>
+        <v>3058634714.389875</v>
       </c>
       <c r="G36" t="n">
-        <v>1802832724.775383</v>
+        <v>2722323976.193189</v>
       </c>
       <c r="H36" t="n">
-        <v>2580414037.585278</v>
+        <v>3436492643.007506</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1771,7 +1783,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -1789,13 +1801,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2176080526.900595</v>
+        <v>3022339808.102904</v>
       </c>
       <c r="G37" t="n">
-        <v>1799635608.609282</v>
+        <v>2671403191.136233</v>
       </c>
       <c r="H37" t="n">
-        <v>2631269595.301755</v>
+        <v>3419378230.119688</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1809,31 +1821,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C38" t="n">
         <v>2026</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1229599916.952255</v>
+        <v>1630056536.928603</v>
       </c>
       <c r="G38" t="n">
-        <v>1084934305.003347</v>
+        <v>1260207312.411586</v>
       </c>
       <c r="H38" t="n">
-        <v>1393555304.497747</v>
+        <v>2108450163.250491</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -1841,31 +1853,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C39" t="n">
         <v>2026</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1200563539.91366</v>
+        <v>1552271411.452087</v>
       </c>
       <c r="G39" t="n">
-        <v>1042677879.683195</v>
+        <v>1199696338.572192</v>
       </c>
       <c r="H39" t="n">
-        <v>1382356757.973955</v>
+        <v>2008463689.802666</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
@@ -1873,31 +1885,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C40" t="n">
         <v>2026</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1159415415.035083</v>
+        <v>1603072011.027406</v>
       </c>
       <c r="G40" t="n">
-        <v>997369007.0633384</v>
+        <v>1238571883.508851</v>
       </c>
       <c r="H40" t="n">
-        <v>1347790130.935567</v>
+        <v>2074841118.836918</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -1905,31 +1917,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C41" t="n">
         <v>2026</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1212011115.124857</v>
+        <v>1564995104.75566</v>
       </c>
       <c r="G41" t="n">
-        <v>1037804278.917133</v>
+        <v>1208776041.618617</v>
       </c>
       <c r="H41" t="n">
-        <v>1415460480.38938</v>
+        <v>2026189793.29666</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
@@ -1937,31 +1949,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C42" t="n">
         <v>2026</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1198458297.807771</v>
+        <v>8043645059.471945</v>
       </c>
       <c r="G42" t="n">
-        <v>1023624898.326479</v>
+        <v>7143270971.577847</v>
       </c>
       <c r="H42" t="n">
-        <v>1403152945.900893</v>
+        <v>9057506862.080589</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
@@ -1969,31 +1981,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C43" t="n">
         <v>2026</v>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1212363228.407338</v>
+        <v>7880433818.686196</v>
       </c>
       <c r="G43" t="n">
-        <v>1034076905.840108</v>
+        <v>6797612946.623663</v>
       </c>
       <c r="H43" t="n">
-        <v>1421388089.505919</v>
+        <v>9135741863.846256</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
@@ -2001,83 +2013,71 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C44" t="n">
         <v>2026</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2061211298.767317</v>
+        <v>8117578224.275035</v>
       </c>
       <c r="G44" t="n">
-        <v>1784782158.685495</v>
+        <v>6895801191.598603</v>
       </c>
       <c r="H44" t="n">
-        <v>2380454106.116328</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>7.033361733229282</v>
-      </c>
+        <v>9555825986.907295</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C45" t="n">
         <v>2026</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2081011895.697336</v>
+        <v>8297646741.85224</v>
       </c>
       <c r="G45" t="n">
-        <v>1784795846.420232</v>
+        <v>6980655384.374812</v>
       </c>
       <c r="H45" t="n">
-        <v>2426389841.01164</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>7.050430174458898</v>
-      </c>
+        <v>9863105634.276684</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -2095,27 +2095,27 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2095431127.635049</v>
+        <v>1534383507.826966</v>
       </c>
       <c r="G46" t="n">
-        <v>1781131875.067538</v>
+        <v>1393875300.058149</v>
       </c>
       <c r="H46" t="n">
-        <v>2465191753.696172</v>
+        <v>1689055505.175512</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>7.061126878716963</v>
+        <v>7.430178721321767</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
@@ -2133,27 +2133,27 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2132965550.138094</v>
+        <v>1531816870.256794</v>
       </c>
       <c r="G47" t="n">
-        <v>1797761658.325185</v>
+        <v>1362921150.426808</v>
       </c>
       <c r="H47" t="n">
-        <v>2530670301.598436</v>
+        <v>1721642461.31811</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>7.068702085302047</v>
+        <v>7.21752999809735</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -2171,27 +2171,27 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2139080062.184734</v>
+        <v>1578251458.368325</v>
       </c>
       <c r="G48" t="n">
-        <v>1788491912.588368</v>
+        <v>1399122883.751032</v>
       </c>
       <c r="H48" t="n">
-        <v>2558392062.178344</v>
+        <v>1780313719.952697</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>7.066579967851128</v>
+        <v>7.231297900402511</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -2209,51 +2209,51 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2153824226.866662</v>
+        <v>1578087585.982712</v>
       </c>
       <c r="G49" t="n">
-        <v>1787079518.37479</v>
+        <v>1394033213.330832</v>
       </c>
       <c r="H49" t="n">
-        <v>2595832335.685065</v>
+        <v>1786442679.570312</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>7.063721708236462</v>
+        <v>7.311710033254837</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C50" t="n">
         <v>2026</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2750336379.174155</v>
+        <v>2511726298.9642</v>
       </c>
       <c r="G50" t="n">
-        <v>2475090932.527276</v>
+        <v>2116544695.824824</v>
       </c>
       <c r="H50" t="n">
-        <v>3056190824.8296</v>
+        <v>2980692547.31701</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2261,37 +2261,37 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>7.033361733229282</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C51" t="n">
         <v>2026</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2866445532.975989</v>
+        <v>2550671236.578301</v>
       </c>
       <c r="G51" t="n">
-        <v>2540239672.591656</v>
+        <v>2092822176.207838</v>
       </c>
       <c r="H51" t="n">
-        <v>3234541245.131875</v>
+        <v>3108684450.628536</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>7.050430174458898</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C52" t="n">
         <v>2026</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2916067704.790989</v>
+        <v>2511075932.489252</v>
       </c>
       <c r="G52" t="n">
-        <v>2549296026.264463</v>
+        <v>2014821318.968145</v>
       </c>
       <c r="H52" t="n">
-        <v>3335607466.264039</v>
+        <v>3129559072.740016</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2337,37 +2337,37 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>7.061126878716963</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C53" t="n">
         <v>2026</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2975879311.17945</v>
+        <v>2510590912.203196</v>
       </c>
       <c r="G53" t="n">
-        <v>2569698971.988516</v>
+        <v>1975959890.716547</v>
       </c>
       <c r="H53" t="n">
-        <v>3446262683.388525</v>
+        <v>3189875846.190166</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2375,165 +2375,165 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>7.068702085302047</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C54" t="n">
         <v>2026</v>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2984233937.892956</v>
+        <v>2335383976.3103</v>
       </c>
       <c r="G54" t="n">
-        <v>2547811193.157033</v>
+        <v>2006878026.911897</v>
       </c>
       <c r="H54" t="n">
-        <v>3495412933.262518</v>
+        <v>2717663078.507733</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>7.066579967851128</v>
+        <v>1.075411853094543</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C55" t="n">
         <v>2026</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2939050914.02654</v>
+        <v>2317379312.695381</v>
       </c>
       <c r="G55" t="n">
-        <v>2482827577.629394</v>
+        <v>1947280419.21247</v>
       </c>
       <c r="H55" t="n">
-        <v>3479105981.047555</v>
+        <v>2757818969.432446</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>7.063721708236462</v>
+        <v>0.7603971048866009</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C56" t="n">
         <v>2026</v>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1532283731.194218</v>
+        <v>2493197563.47568</v>
       </c>
       <c r="G56" t="n">
-        <v>1206709850.446847</v>
+        <v>2066929446.180325</v>
       </c>
       <c r="H56" t="n">
-        <v>1945698406.301271</v>
+        <v>3007376038.891055</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>-0.2119867351621618</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C57" t="n">
         <v>2026</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1530800172.731901</v>
+        <v>2380538576.169736</v>
       </c>
       <c r="G57" t="n">
-        <v>1190887100.112567</v>
+        <v>1951273653.682344</v>
       </c>
       <c r="H57" t="n">
-        <v>1967734110.659621</v>
+        <v>2904238419.83303</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.2854178679703168</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
@@ -2551,27 +2551,27 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1652052630.115747</v>
+        <v>945211881.5779274</v>
       </c>
       <c r="G58" t="n">
-        <v>1282248636.900203</v>
+        <v>840468661.1257761</v>
       </c>
       <c r="H58" t="n">
-        <v>2128509100.442722</v>
+        <v>1063008702.643804</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -2589,27 +2589,27 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1540394436.715255</v>
+        <v>928976082.5234114</v>
       </c>
       <c r="G59" t="n">
-        <v>1194387876.76033</v>
+        <v>821436341.3055692</v>
       </c>
       <c r="H59" t="n">
-        <v>1986636893.116628</v>
+        <v>1050594572.586015</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -2627,27 +2627,27 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1601249682.043001</v>
+        <v>975414791.6953675</v>
       </c>
       <c r="G60" t="n">
-        <v>1240652341.987623</v>
+        <v>858062310.8858221</v>
       </c>
       <c r="H60" t="n">
-        <v>2066655143.8053</v>
+        <v>1108816928.313636</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PB</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
@@ -2665,295 +2665,315 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1546953840.390549</v>
+        <v>1029102101.297105</v>
       </c>
       <c r="G61" t="n">
-        <v>1197769641.099421</v>
+        <v>900963636.2529433</v>
       </c>
       <c r="H61" t="n">
-        <v>1997935247.467531</v>
+        <v>1175464904.775348</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C62" t="n">
         <v>2026</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>7622548791.970963</v>
+        <v>2563316094.741641</v>
       </c>
       <c r="G62" t="n">
-        <v>6799994273.370621</v>
+        <v>2185934843.522444</v>
       </c>
       <c r="H62" t="n">
-        <v>8544602796.728146</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+        <v>3005848697.197947</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>7.061126878716963</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C63" t="n">
         <v>2026</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>7867698765.092675</v>
+        <v>2534183461.533232</v>
       </c>
       <c r="G63" t="n">
-        <v>6849691890.230468</v>
+        <v>2144562437.935578</v>
       </c>
       <c r="H63" t="n">
-        <v>9037002663.802746</v>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+        <v>2994590273.105151</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>7.068702085302047</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C64" t="n">
         <v>2026</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>8125117287.03696</v>
+        <v>2661747074.852479</v>
       </c>
       <c r="G64" t="n">
-        <v>6999891532.651165</v>
+        <v>2236190566.502339</v>
       </c>
       <c r="H64" t="n">
-        <v>9431221986.82172</v>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+        <v>3168288783.888096</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>7.066579967851128</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C65" t="n">
         <v>2026</v>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>8018858853.684537</v>
+        <v>2708709466.253912</v>
       </c>
       <c r="G65" t="n">
-        <v>6872950100.007731</v>
+        <v>2259957040.612117</v>
       </c>
       <c r="H65" t="n">
-        <v>9355821936.673534</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+        <v>3246569222.654902</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>7.063721708236462</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C66" t="n">
         <v>2026</v>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>8223834288.858061</v>
+        <v>817508875.9268764</v>
       </c>
       <c r="G66" t="n">
-        <v>7029250043.276602</v>
+        <v>698071075.1492382</v>
       </c>
       <c r="H66" t="n">
-        <v>9621431873.132225</v>
+        <v>957382114.8173872</v>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C67" t="n">
         <v>2026</v>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>8417788707.10976</v>
+        <v>814075881.2750851</v>
       </c>
       <c r="G67" t="n">
-        <v>7183433921.69058</v>
+        <v>682730546.9159557</v>
       </c>
       <c r="H67" t="n">
-        <v>9864247028.650652</v>
+        <v>970689744.9769263</v>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C68" t="n">
         <v>2026</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1515981927.490436</v>
+        <v>833644973.3578233</v>
       </c>
       <c r="G68" t="n">
-        <v>1375289201.587634</v>
+        <v>696862210.9911182</v>
       </c>
       <c r="H68" t="n">
-        <v>1671067584.784767</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>997275976.0015506</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>6.339104426528941</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C69" t="n">
         <v>2026</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1563523555.404045</v>
+        <v>845557294.8308041</v>
       </c>
       <c r="G69" t="n">
-        <v>1388180393.621645</v>
+        <v>705443420.6401277</v>
       </c>
       <c r="H69" t="n">
-        <v>1761014576.733457</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+        <v>1013500328.903511</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>6.365548028661205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
@@ -2971,27 +2991,27 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1561900862.837709</v>
+        <v>4950146748.257338</v>
       </c>
       <c r="G70" t="n">
-        <v>1381923747.053171</v>
+        <v>4218504956.875086</v>
       </c>
       <c r="H70" t="n">
-        <v>1765317594.791513</v>
+        <v>5808681767.541248</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>7.430178721321767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
@@ -3009,27 +3029,27 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1551881061.519242</v>
+        <v>4922919130.131982</v>
       </c>
       <c r="G71" t="n">
-        <v>1368421685.732648</v>
+        <v>4067977846.731762</v>
       </c>
       <c r="H71" t="n">
-        <v>1759936176.261833</v>
+        <v>5957538038.534326</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>7.21752999809735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -3047,27 +3067,27 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1599807525.36706</v>
+        <v>5028901107.844913</v>
       </c>
       <c r="G72" t="n">
-        <v>1406043086.615961</v>
+        <v>4089767086.694093</v>
       </c>
       <c r="H72" t="n">
-        <v>1820274316.330488</v>
+        <v>6183688659.132542</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>7.231297900402511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -3085,51 +3105,51 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1599483443.970827</v>
+        <v>5164015561.40391</v>
       </c>
       <c r="G73" t="n">
-        <v>1401250007.622656</v>
+        <v>4098120063.304558</v>
       </c>
       <c r="H73" t="n">
-        <v>1825760766.18707</v>
+        <v>6507143838.269712</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>pib_var_12m</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>7.311710033254837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C74" t="n">
         <v>2026</v>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2252976207.973721</v>
+        <v>6472335897.670183</v>
       </c>
       <c r="G74" t="n">
-        <v>1896382220.767966</v>
+        <v>5541091154.686009</v>
       </c>
       <c r="H74" t="n">
-        <v>2676623804.05575</v>
+        <v>7560087138.585232</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3137,37 +3157,37 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>7.033361733229282</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C75" t="n">
         <v>2026</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2292646381.685365</v>
+        <v>6223440173.260494</v>
       </c>
       <c r="G75" t="n">
-        <v>1889505896.033827</v>
+        <v>5246191776.085944</v>
       </c>
       <c r="H75" t="n">
-        <v>2781799962.883469</v>
+        <v>7382728127.992496</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3175,37 +3195,37 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>7.050430174458898</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C76" t="n">
         <v>2026</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2362661858.693663</v>
+        <v>6388434862.201414</v>
       </c>
       <c r="G76" t="n">
-        <v>1911939612.428791</v>
+        <v>5311116950.187662</v>
       </c>
       <c r="H76" t="n">
-        <v>2919637744.957123</v>
+        <v>7684278160.575687</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3213,37 +3233,37 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>7.061126878716963</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C77" t="n">
         <v>2026</v>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2404918881.168227</v>
+        <v>6645704565.75744</v>
       </c>
       <c r="G77" t="n">
-        <v>1914909781.363911</v>
+        <v>5455796064.344591</v>
       </c>
       <c r="H77" t="n">
-        <v>3020317135.191609</v>
+        <v>8095131976.058365</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3251,37 +3271,37 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>7.068702085302047</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C78" t="n">
         <v>2026</v>
       </c>
       <c r="D78" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2372009810.480129</v>
+        <v>880259697.417096</v>
       </c>
       <c r="G78" t="n">
-        <v>1861486236.104368</v>
+        <v>752407302.4577022</v>
       </c>
       <c r="H78" t="n">
-        <v>3022547484.846684</v>
+        <v>1029837339.916564</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3289,37 +3309,37 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>7.066579967851128</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C79" t="n">
         <v>2026</v>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2375542952.173555</v>
+        <v>910123882.3170352</v>
       </c>
       <c r="G79" t="n">
-        <v>1839879845.045239</v>
+        <v>771583585.9714686</v>
       </c>
       <c r="H79" t="n">
-        <v>3067159158.690981</v>
+        <v>1073539531.197936</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3327,89 +3347,89 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>7.063721708236462</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C80" t="n">
         <v>2026</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2275294382.881609</v>
+        <v>875140752.3072135</v>
       </c>
       <c r="G80" t="n">
-        <v>1948213567.474051</v>
+        <v>741860323.1183692</v>
       </c>
       <c r="H80" t="n">
-        <v>2657287997.170031</v>
+        <v>1032365948.794158</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C81" t="n">
         <v>2026</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2236172377.555151</v>
+        <v>890305801.2958099</v>
       </c>
       <c r="G81" t="n">
-        <v>1890958248.720526</v>
+        <v>754715972.1811171</v>
       </c>
       <c r="H81" t="n">
-        <v>2644408942.14566</v>
+        <v>1050255260.307059</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
@@ -3427,27 +3447,27 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2329162594.139697</v>
+        <v>869669354.8442993</v>
       </c>
       <c r="G82" t="n">
-        <v>1946842531.212798</v>
+        <v>727710175.2826755</v>
       </c>
       <c r="H82" t="n">
-        <v>2786562499.515574</v>
+        <v>1039321439.282485</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
@@ -3465,27 +3485,27 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2294034875.388876</v>
+        <v>816640517.4963598</v>
       </c>
       <c r="G83" t="n">
-        <v>1896675381.820615</v>
+        <v>677051531.9728987</v>
       </c>
       <c r="H83" t="n">
-        <v>2774642440.104273</v>
+        <v>985008826.246061</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
@@ -3503,27 +3523,27 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2477072595.477556</v>
+        <v>817767057.9979982</v>
       </c>
       <c r="G84" t="n">
-        <v>2026987599.394507</v>
+        <v>672560037.5585886</v>
       </c>
       <c r="H84" t="n">
-        <v>3027097277.30885</v>
+        <v>994324556.6213787</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -3541,319 +3561,331 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2355077934.57654</v>
+        <v>918467050.5182968</v>
       </c>
       <c r="G85" t="n">
-        <v>1908343354.151123</v>
+        <v>750081299.3965651</v>
       </c>
       <c r="H85" t="n">
-        <v>2906391067.343578</v>
+        <v>1124653718.958778</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C86" t="n">
         <v>2026</v>
       </c>
       <c r="D86" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>920681975.5760103</v>
+        <v>202161558.3553387</v>
       </c>
       <c r="G86" t="n">
-        <v>821887172.888934</v>
+        <v>173116640.0308458</v>
       </c>
       <c r="H86" t="n">
-        <v>1031352390.098797</v>
+        <v>236079533.8297749</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>7.033361733229282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C87" t="n">
         <v>2026</v>
       </c>
       <c r="D87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>984937326.3765035</v>
+        <v>196917360.3838774</v>
       </c>
       <c r="G87" t="n">
-        <v>870526288.2084587</v>
+        <v>167000443.5286314</v>
       </c>
       <c r="H87" t="n">
-        <v>1114385113.959237</v>
+        <v>232193675.6647344</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>7.050430174458898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C88" t="n">
         <v>2026</v>
       </c>
       <c r="D88" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>941709718.6110523</v>
+        <v>200686473.5623952</v>
       </c>
       <c r="G88" t="n">
-        <v>827137532.5307332</v>
+        <v>168647146.6949989</v>
       </c>
       <c r="H88" t="n">
-        <v>1072152041.527092</v>
+        <v>238812582.7218888</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>7.061126878716963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C89" t="n">
         <v>2026</v>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>924313652.4970319</v>
+        <v>209153939.1923879</v>
       </c>
       <c r="G89" t="n">
-        <v>807490628.4089631</v>
+        <v>174242046.3953766</v>
       </c>
       <c r="H89" t="n">
-        <v>1058037948.843792</v>
+        <v>251060930.3820359</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>7.068702085302047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C90" t="n">
         <v>2026</v>
       </c>
       <c r="D90" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>969091536.737309</v>
+        <v>4669538892.735298</v>
       </c>
       <c r="G90" t="n">
-        <v>842478031.6610416</v>
+        <v>3887557595.663722</v>
       </c>
       <c r="H90" t="n">
-        <v>1114733407.023398</v>
+        <v>5608815544.00351</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>7.066579967851128</v>
+        <v>7.430178721321767</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C91" t="n">
         <v>2026</v>
       </c>
       <c r="D91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1016547851.046051</v>
+        <v>4712868934.414354</v>
       </c>
       <c r="G91" t="n">
-        <v>879783653.2976435</v>
+        <v>3861910886.999944</v>
       </c>
       <c r="H91" t="n">
-        <v>1174572327.631939</v>
+        <v>5751332499.08369</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>7.063721708236462</v>
+        <v>7.21752999809735</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C92" t="n">
         <v>2026</v>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2497802821.851573</v>
+        <v>4820785281.242793</v>
       </c>
       <c r="G92" t="n">
-        <v>2143224460.316083</v>
+        <v>3932028298.628303</v>
       </c>
       <c r="H92" t="n">
-        <v>2911043174.605031</v>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
+        <v>5910428146.194797</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pib_var_12m</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>7.231297900402511</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C93" t="n">
         <v>2026</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2554435698.511311</v>
+        <v>4896554556.586543</v>
       </c>
       <c r="G93" t="n">
-        <v>2144743383.686439</v>
+        <v>3983921288.977215</v>
       </c>
       <c r="H93" t="n">
-        <v>3042388095.21976</v>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+        <v>6018253069.398319</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>pib_var_12m</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>7.311710033254837</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
@@ -3871,21 +3903,27 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2558247093.539563</v>
+        <v>4198261249.880991</v>
       </c>
       <c r="G94" t="n">
-        <v>2133430275.51524</v>
+        <v>3685333809.87261</v>
       </c>
       <c r="H94" t="n">
-        <v>3067655065.513233</v>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+        <v>4782578304.042844</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>pib_var_12m</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>7.430178721321767</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -3903,21 +3941,27 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2532988272.785382</v>
+        <v>4303381162.971148</v>
       </c>
       <c r="G95" t="n">
-        <v>2106784942.265199</v>
+        <v>3714101211.267642</v>
       </c>
       <c r="H95" t="n">
-        <v>3045412686.104453</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+        <v>4986156375.500128</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>pib_var_12m</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>7.21752999809735</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -3935,21 +3979,27 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2667816922.811404</v>
+        <v>4356442135.183993</v>
       </c>
       <c r="G96" t="n">
-        <v>2216054000.859074</v>
+        <v>3758198781.214113</v>
       </c>
       <c r="H96" t="n">
-        <v>3211675857.573797</v>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+        <v>5049915978.918842</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>pib_var_12m</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>7.231297900402511</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -3967,273 +4017,279 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2734042993.68786</v>
+        <v>4403533804.566877</v>
       </c>
       <c r="G97" t="n">
-        <v>2269259157.224233</v>
+        <v>3794030033.385573</v>
       </c>
       <c r="H97" t="n">
-        <v>3294022662.654852</v>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+        <v>5110953207.36292</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>pib_var_12m</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>7.311710033254837</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="C98" t="n">
         <v>2026</v>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>808430231.7949942</v>
+        <v>556271668.5494654</v>
       </c>
       <c r="G98" t="n">
-        <v>684809832.3518099</v>
+        <v>485827662.4139227</v>
       </c>
       <c r="H98" t="n">
-        <v>954366320.1149142</v>
+        <v>636929909.8641415</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>-2.238291510711132</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46235</v>
+        <v>46296</v>
       </c>
       <c r="C99" t="n">
         <v>2026</v>
       </c>
       <c r="D99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>815234253.1056976</v>
+        <v>550394819.7036551</v>
       </c>
       <c r="G99" t="n">
-        <v>682426992.7163446</v>
+        <v>476683756.5270988</v>
       </c>
       <c r="H99" t="n">
-        <v>973887162.3342323</v>
+        <v>635504049.4009314</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>1.721493938411056</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46266</v>
+        <v>46327</v>
       </c>
       <c r="C100" t="n">
         <v>2026</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sep</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>813472934.748633</v>
+        <v>578778785.8972794</v>
       </c>
       <c r="G100" t="n">
-        <v>678487042.847188</v>
+        <v>498150224.2880453</v>
       </c>
       <c r="H100" t="n">
-        <v>975314447.8509866</v>
+        <v>672457557.3231711</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>1.075411853094543</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46296</v>
+        <v>46357</v>
       </c>
       <c r="C101" t="n">
         <v>2026</v>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Oct</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>815701175.3926837</v>
+        <v>590410749.8849186</v>
       </c>
       <c r="G101" t="n">
-        <v>678829013.0787293</v>
+        <v>508161794.9490644</v>
       </c>
       <c r="H101" t="n">
-        <v>980170845.2609079</v>
+        <v>685972178.6337996</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>0.7603971048866009</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46327</v>
+        <v>46266</v>
       </c>
       <c r="C102" t="n">
         <v>2026</v>
       </c>
       <c r="D102" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nov</t>
+          <t>Sep</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>838369052.9103237</v>
+        <v>22210144813.97545</v>
       </c>
       <c r="G102" t="n">
-        <v>696368751.1810309</v>
+        <v>19997165388.82895</v>
       </c>
       <c r="H102" t="n">
-        <v>1009325400.781854</v>
+        <v>24668022845.54432</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>-0.2119867351621618</v>
+        <v>7.061126878716963</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46357</v>
+        <v>46296</v>
       </c>
       <c r="C103" t="n">
         <v>2026</v>
       </c>
       <c r="D103" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dec</t>
+          <t>Oct</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>854601582.2776476</v>
+        <v>22561104561.10141</v>
       </c>
       <c r="G103" t="n">
-        <v>708573263.1875019</v>
+        <v>20014901821.80946</v>
       </c>
       <c r="H103" t="n">
-        <v>1030724559.30107</v>
+        <v>25431223372.89256</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>pib_var_mom</t>
+          <t>log_pib</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>-0.2854178679703168</v>
+        <v>7.068702085302047</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46204</v>
+        <v>46327</v>
       </c>
       <c r="C104" t="n">
         <v>2026</v>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jul</t>
+          <t>Nov</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>4803843259.025083</v>
+        <v>22580586706.9115</v>
       </c>
       <c r="G104" t="n">
-        <v>4162201188.899261</v>
+        <v>19951126968.81229</v>
       </c>
       <c r="H104" t="n">
-        <v>5544400428.991195</v>
+        <v>25556596217.61718</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -4241,37 +4297,37 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>7.033361733229282</v>
+        <v>7.066579967851128</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46235</v>
+        <v>46357</v>
       </c>
       <c r="C105" t="n">
         <v>2026</v>
       </c>
       <c r="D105" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aug</t>
+          <t>Dec</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4987044924.011847</v>
+        <v>22741776574.89343</v>
       </c>
       <c r="G105" t="n">
-        <v>4269267288.046805</v>
+        <v>19978208098.01737</v>
       </c>
       <c r="H105" t="n">
-        <v>5825500114.21062</v>
+        <v>25887627120.7575</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -4279,13 +4335,13 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>7.050430174458898</v>
+        <v>7.063721708236462</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
@@ -4303,13 +4359,13 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>5023964023.572824</v>
+        <v>592228786.4600677</v>
       </c>
       <c r="G106" t="n">
-        <v>4300872678.906815</v>
+        <v>528891705.725151</v>
       </c>
       <c r="H106" t="n">
-        <v>5868626298.551467</v>
+        <v>663150757.9251601</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -4323,7 +4379,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
@@ -4341,13 +4397,13 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>5033541133.243765</v>
+        <v>603912002.7929357</v>
       </c>
       <c r="G107" t="n">
-        <v>4309071370.046596</v>
+        <v>532063082.4647353</v>
       </c>
       <c r="H107" t="n">
-        <v>5879813575.652832</v>
+        <v>685463282.7143151</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -4361,7 +4417,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
@@ -4379,13 +4435,13 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>5080324598.573091</v>
+        <v>603073740.1708969</v>
       </c>
       <c r="G108" t="n">
-        <v>4349121363.819518</v>
+        <v>524966485.7706409</v>
       </c>
       <c r="H108" t="n">
-        <v>5934462588.599744</v>
+        <v>692802199.6486362</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -4399,7 +4455,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
@@ -4417,13 +4473,13 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>5153025626.407529</v>
+        <v>599412568.9258935</v>
       </c>
       <c r="G109" t="n">
-        <v>4411361121.771282</v>
+        <v>516127934.436297</v>
       </c>
       <c r="H109" t="n">
-        <v>6019383218.33663</v>
+        <v>696136372.0387528</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -4431,2010 +4487,6 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>7.063721708236462</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C110" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D110" t="n">
-        <v>7</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>5786098391.40745</v>
-      </c>
-      <c r="G110" t="n">
-        <v>4933160363.702547</v>
-      </c>
-      <c r="H110" t="n">
-        <v>6786508470.590343</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>7.033361733229282</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C111" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D111" t="n">
-        <v>8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>5816654776.949256</v>
-      </c>
-      <c r="G111" t="n">
-        <v>4873575113.446412</v>
-      </c>
-      <c r="H111" t="n">
-        <v>6942228652.813523</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>7.050430174458898</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C112" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D112" t="n">
-        <v>9</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>6298582305.568387</v>
-      </c>
-      <c r="G112" t="n">
-        <v>5195974501.425385</v>
-      </c>
-      <c r="H112" t="n">
-        <v>7635168157.41419</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>7.061126878716963</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C113" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D113" t="n">
-        <v>10</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>6057022079.791013</v>
-      </c>
-      <c r="G113" t="n">
-        <v>4926759485.617586</v>
-      </c>
-      <c r="H113" t="n">
-        <v>7446581588.197204</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>7.068702085302047</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C114" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D114" t="n">
-        <v>11</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>6220750275.547284</v>
-      </c>
-      <c r="G114" t="n">
-        <v>4994910287.602218</v>
-      </c>
-      <c r="H114" t="n">
-        <v>7747433239.546383</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>7.066579967851128</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C115" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D115" t="n">
-        <v>12</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>6463902749.005223</v>
-      </c>
-      <c r="G115" t="n">
-        <v>5128381803.673752</v>
-      </c>
-      <c r="H115" t="n">
-        <v>8147216870.371553</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>7.063721708236462</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="B116" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C116" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D116" t="n">
-        <v>7</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>832416633.1037208</v>
-      </c>
-      <c r="G116" t="n">
-        <v>725986160.8132677</v>
-      </c>
-      <c r="H116" t="n">
-        <v>954449944.7365652</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C117" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D117" t="n">
-        <v>8</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>865658986.7853457</v>
-      </c>
-      <c r="G117" t="n">
-        <v>740640973.1333004</v>
-      </c>
-      <c r="H117" t="n">
-        <v>1011779672.723238</v>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C118" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D118" t="n">
-        <v>9</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>857751068.1209307</v>
-      </c>
-      <c r="G118" t="n">
-        <v>728596349.9929864</v>
-      </c>
-      <c r="H118" t="n">
-        <v>1009800412.628583</v>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C119" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D119" t="n">
-        <v>10</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>897835767.9751034</v>
-      </c>
-      <c r="G119" t="n">
-        <v>759611610.1992943</v>
-      </c>
-      <c r="H119" t="n">
-        <v>1061212145.038107</v>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C120" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D120" t="n">
-        <v>11</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>874971472.9647938</v>
-      </c>
-      <c r="G120" t="n">
-        <v>738134735.2983938</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1037175249.844724</v>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>RN</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C121" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D121" t="n">
-        <v>12</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>879849296.1296161</v>
-      </c>
-      <c r="G121" t="n">
-        <v>740432909.2774326</v>
-      </c>
-      <c r="H121" t="n">
-        <v>1045516446.12236</v>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C122" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D122" t="n">
-        <v>7</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>781532594.8635811</v>
-      </c>
-      <c r="G122" t="n">
-        <v>658072833.1897243</v>
-      </c>
-      <c r="H122" t="n">
-        <v>928154401.8063253</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>7.033361733229282</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C123" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D123" t="n">
-        <v>8</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>766033851.6957486</v>
-      </c>
-      <c r="G123" t="n">
-        <v>638252044.3815445</v>
-      </c>
-      <c r="H123" t="n">
-        <v>919398327.2116756</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>7.050430174458898</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C124" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D124" t="n">
-        <v>9</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>753044587.9052948</v>
-      </c>
-      <c r="G124" t="n">
-        <v>621682432.3783835</v>
-      </c>
-      <c r="H124" t="n">
-        <v>912163705.8392984</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>7.061126878716963</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C125" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D125" t="n">
-        <v>10</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>708392960.9058837</v>
-      </c>
-      <c r="G125" t="n">
-        <v>580103393.1703025</v>
-      </c>
-      <c r="H125" t="n">
-        <v>865053700.7179409</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>7.068702085302047</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="B126" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C126" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D126" t="n">
-        <v>11</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>711942924.2465973</v>
-      </c>
-      <c r="G126" t="n">
-        <v>578842169.8943838</v>
-      </c>
-      <c r="H126" t="n">
-        <v>875649276.6884605</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J126" t="n">
-        <v>7.066579967851128</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>RO</t>
-        </is>
-      </c>
-      <c r="B127" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C127" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D127" t="n">
-        <v>12</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>804758293.8768286</v>
-      </c>
-      <c r="G127" t="n">
-        <v>650135795.7325425</v>
-      </c>
-      <c r="H127" t="n">
-        <v>996154827.6753755</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J127" t="n">
-        <v>7.063721708236462</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B128" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C128" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D128" t="n">
-        <v>7</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>181188936.5499681</v>
-      </c>
-      <c r="G128" t="n">
-        <v>156848847.2450911</v>
-      </c>
-      <c r="H128" t="n">
-        <v>209306165.1693829</v>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C129" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D129" t="n">
-        <v>8</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>180590301.2993337</v>
-      </c>
-      <c r="G129" t="n">
-        <v>154463364.4251842</v>
-      </c>
-      <c r="H129" t="n">
-        <v>211136518.0005546</v>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C130" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D130" t="n">
-        <v>9</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>196657465.3737064</v>
-      </c>
-      <c r="G130" t="n">
-        <v>166339920.3248786</v>
-      </c>
-      <c r="H130" t="n">
-        <v>232500764.7693711</v>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C131" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D131" t="n">
-        <v>10</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>193039380.1877124</v>
-      </c>
-      <c r="G131" t="n">
-        <v>161580967.968863</v>
-      </c>
-      <c r="H131" t="n">
-        <v>230622472.2607002</v>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C132" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D132" t="n">
-        <v>11</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>195092433.8937732</v>
-      </c>
-      <c r="G132" t="n">
-        <v>161694603.5917894</v>
-      </c>
-      <c r="H132" t="n">
-        <v>235388546.7859173</v>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>RR</t>
-        </is>
-      </c>
-      <c r="B133" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C133" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D133" t="n">
-        <v>12</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>204423349.2344458</v>
-      </c>
-      <c r="G133" t="n">
-        <v>167846005.0518825</v>
-      </c>
-      <c r="H133" t="n">
-        <v>248971702.9565936</v>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C134" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D134" t="n">
-        <v>7</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>4803975654.664263</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4006279205.871163</v>
-      </c>
-      <c r="H134" t="n">
-        <v>5760502677.094018</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>6.339104426528941</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B135" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C135" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D135" t="n">
-        <v>8</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>4770738709.329062</v>
-      </c>
-      <c r="G135" t="n">
-        <v>3906288368.804505</v>
-      </c>
-      <c r="H135" t="n">
-        <v>5826489414.977898</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J135" t="n">
-        <v>6.365548028661205</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C136" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D136" t="n">
-        <v>9</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F136" t="n">
-        <v>4886741321.084857</v>
-      </c>
-      <c r="G136" t="n">
-        <v>3982619613.601126</v>
-      </c>
-      <c r="H136" t="n">
-        <v>5996113878.825953</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J136" t="n">
-        <v>7.430178721321767</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B137" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C137" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D137" t="n">
-        <v>10</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
-        <v>4766817187.82256</v>
-      </c>
-      <c r="G137" t="n">
-        <v>3877991646.994992</v>
-      </c>
-      <c r="H137" t="n">
-        <v>5859359217.477428</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J137" t="n">
-        <v>7.21752999809735</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B138" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C138" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D138" t="n">
-        <v>11</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>4952453590.915842</v>
-      </c>
-      <c r="G138" t="n">
-        <v>4025015252.55732</v>
-      </c>
-      <c r="H138" t="n">
-        <v>6093590963.311744</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J138" t="n">
-        <v>7.231297900402511</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B139" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C139" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D139" t="n">
-        <v>12</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>5108370316.094956</v>
-      </c>
-      <c r="G139" t="n">
-        <v>4148669258.216747</v>
-      </c>
-      <c r="H139" t="n">
-        <v>6290076567.245296</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J139" t="n">
-        <v>7.311710033254837</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C140" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D140" t="n">
-        <v>7</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>4218730946.674078</v>
-      </c>
-      <c r="G140" t="n">
-        <v>3720633583.176445</v>
-      </c>
-      <c r="H140" t="n">
-        <v>4783510765.720446</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J140" t="n">
-        <v>6.339104426528941</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B141" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C141" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D141" t="n">
-        <v>8</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F141" t="n">
-        <v>4293302799.947289</v>
-      </c>
-      <c r="G141" t="n">
-        <v>3728429244.318689</v>
-      </c>
-      <c r="H141" t="n">
-        <v>4943757202.881684</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J141" t="n">
-        <v>6.365548028661205</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C142" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D142" t="n">
-        <v>9</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F142" t="n">
-        <v>4331615074.594744</v>
-      </c>
-      <c r="G142" t="n">
-        <v>3760730530.395905</v>
-      </c>
-      <c r="H142" t="n">
-        <v>4989160750.233597</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J142" t="n">
-        <v>7.430178721321767</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C143" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D143" t="n">
-        <v>10</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>4377051304.397729</v>
-      </c>
-      <c r="G143" t="n">
-        <v>3796246519.125326</v>
-      </c>
-      <c r="H143" t="n">
-        <v>5046716019.312702</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>7.21752999809735</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C144" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D144" t="n">
-        <v>11</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>4415589757.659429</v>
-      </c>
-      <c r="G144" t="n">
-        <v>3829563668.339079</v>
-      </c>
-      <c r="H144" t="n">
-        <v>5091293577.161777</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J144" t="n">
-        <v>7.231297900402511</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B145" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C145" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D145" t="n">
-        <v>12</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>4456135570.919322</v>
-      </c>
-      <c r="G145" t="n">
-        <v>3863397746.20526</v>
-      </c>
-      <c r="H145" t="n">
-        <v>5139813586.606951</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
-      <c r="J145" t="n">
-        <v>7.311710033254837</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C146" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D146" t="n">
-        <v>7</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>524087479.3296691</v>
-      </c>
-      <c r="G146" t="n">
-        <v>457321917.8075867</v>
-      </c>
-      <c r="H146" t="n">
-        <v>600600310.842066</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J146" t="n">
-        <v>7.033361733229282</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="B147" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C147" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D147" t="n">
-        <v>8</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>528440956.4791012</v>
-      </c>
-      <c r="G147" t="n">
-        <v>456650123.124806</v>
-      </c>
-      <c r="H147" t="n">
-        <v>611518163.1260093</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J147" t="n">
-        <v>7.050430174458898</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="B148" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C148" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D148" t="n">
-        <v>9</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>545382921.2751505</v>
-      </c>
-      <c r="G148" t="n">
-        <v>467969108.1623368</v>
-      </c>
-      <c r="H148" t="n">
-        <v>635602918.2922802</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J148" t="n">
-        <v>7.061126878716963</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="B149" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C149" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D149" t="n">
-        <v>10</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>545124854.9479005</v>
-      </c>
-      <c r="G149" t="n">
-        <v>467747672.7922531</v>
-      </c>
-      <c r="H149" t="n">
-        <v>635302161.3299434</v>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J149" t="n">
-        <v>7.068702085302047</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="B150" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C150" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D150" t="n">
-        <v>11</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>573264791.0025913</v>
-      </c>
-      <c r="G150" t="n">
-        <v>491893355.3488159</v>
-      </c>
-      <c r="H150" t="n">
-        <v>668097092.6517228</v>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J150" t="n">
-        <v>7.066579967851128</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="B151" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C151" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D151" t="n">
-        <v>12</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>585137213.9162117</v>
-      </c>
-      <c r="G151" t="n">
-        <v>502080614.1429968</v>
-      </c>
-      <c r="H151" t="n">
-        <v>681933437.5099217</v>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J151" t="n">
-        <v>7.063721708236462</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="B152" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C152" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D152" t="n">
-        <v>7</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>21592165736.39709</v>
-      </c>
-      <c r="G152" t="n">
-        <v>19523723050.86805</v>
-      </c>
-      <c r="H152" t="n">
-        <v>23879749777.915</v>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J152" t="n">
-        <v>7.033361733229282</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="B153" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C153" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D153" t="n">
-        <v>8</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>21801287659.59661</v>
-      </c>
-      <c r="G153" t="n">
-        <v>18953901862.07461</v>
-      </c>
-      <c r="H153" t="n">
-        <v>25076427380.23839</v>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J153" t="n">
-        <v>7.050430174458898</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="B154" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C154" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D154" t="n">
-        <v>9</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>22895957822.38369</v>
-      </c>
-      <c r="G154" t="n">
-        <v>19345558449.04534</v>
-      </c>
-      <c r="H154" t="n">
-        <v>27097945297.632</v>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J154" t="n">
-        <v>7.061126878716963</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="B155" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C155" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D155" t="n">
-        <v>10</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>23253098324.76303</v>
-      </c>
-      <c r="G155" t="n">
-        <v>19204510114.88704</v>
-      </c>
-      <c r="H155" t="n">
-        <v>28155187425.58031</v>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J155" t="n">
-        <v>7.068702085302047</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="B156" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C156" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D156" t="n">
-        <v>11</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>23317368636.37066</v>
-      </c>
-      <c r="G156" t="n">
-        <v>18894636025.24047</v>
-      </c>
-      <c r="H156" t="n">
-        <v>28775345521.24204</v>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J156" t="n">
-        <v>7.066579967851128</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="B157" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C157" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D157" t="n">
-        <v>12</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>24190611308.89869</v>
-      </c>
-      <c r="G157" t="n">
-        <v>19285421207.16822</v>
-      </c>
-      <c r="H157" t="n">
-        <v>30343422070.59024</v>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J157" t="n">
-        <v>7.063721708236462</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="B158" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C158" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D158" t="n">
-        <v>7</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>561613217.2670186</v>
-      </c>
-      <c r="G158" t="n">
-        <v>498070408.8241951</v>
-      </c>
-      <c r="H158" t="n">
-        <v>633262687.8067396</v>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J158" t="n">
-        <v>7.033361733229282</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="B159" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C159" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D159" t="n">
-        <v>8</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>576022082.9611847</v>
-      </c>
-      <c r="G159" t="n">
-        <v>502720686.215544</v>
-      </c>
-      <c r="H159" t="n">
-        <v>660011511.6740599</v>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J159" t="n">
-        <v>7.050430174458898</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="B160" s="1" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C160" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D160" t="n">
-        <v>9</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>584507868.4398527</v>
-      </c>
-      <c r="G160" t="n">
-        <v>505520232.4776926</v>
-      </c>
-      <c r="H160" t="n">
-        <v>675837338.0894825</v>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J160" t="n">
-        <v>7.061126878716963</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="B161" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="C161" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D161" t="n">
-        <v>10</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="F161" t="n">
-        <v>595406012.8860402</v>
-      </c>
-      <c r="G161" t="n">
-        <v>510572257.7556096</v>
-      </c>
-      <c r="H161" t="n">
-        <v>694335257.7345484</v>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J161" t="n">
-        <v>7.068702085302047</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="B162" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="C162" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D162" t="n">
-        <v>11</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="F162" t="n">
-        <v>594816152.1766996</v>
-      </c>
-      <c r="G162" t="n">
-        <v>505965152.3408163</v>
-      </c>
-      <c r="H162" t="n">
-        <v>699270005.5595373</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J162" t="n">
-        <v>7.066579967851128</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>TO</t>
-        </is>
-      </c>
-      <c r="B163" s="1" t="n">
-        <v>46357</v>
-      </c>
-      <c r="C163" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D163" t="n">
-        <v>12</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>591081377.912885</v>
-      </c>
-      <c r="G163" t="n">
-        <v>498940449.4387761</v>
-      </c>
-      <c r="H163" t="n">
-        <v>700238266.3269438</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>log_pib</t>
-        </is>
-      </c>
-      <c r="J163" t="n">
         <v>7.063721708236462</v>
       </c>
     </row>
@@ -6557,14 +4609,10 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_12m</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>pib_var_12m</t>
-        </is>
-      </c>
+          <t>SARIMA_puro</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>(1, 1, 1)</t>
@@ -6576,46 +4624,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-142.0013765717459</v>
+        <v>-145.0634277096511</v>
       </c>
       <c r="G2" t="n">
-        <v>-115.7215482392928</v>
+        <v>-127.4565841108669</v>
       </c>
       <c r="H2" t="n">
-        <v>16888403.58807146</v>
+        <v>17317929.24645062</v>
       </c>
       <c r="I2" t="n">
-        <v>10006940.66412126</v>
+        <v>10166335.16707563</v>
       </c>
       <c r="J2" t="n">
-        <v>5.811285835520886</v>
+        <v>5.749408503639112</v>
       </c>
       <c r="K2" t="n">
-        <v>17796369.64321426</v>
+        <v>18160900.45300554</v>
       </c>
       <c r="L2" t="n">
-        <v>16888403.58807146</v>
+        <v>17653158.26652335</v>
       </c>
       <c r="M2" t="n">
-        <v>17418365.18470662</v>
+        <v>17539888.95306782</v>
       </c>
       <c r="N2" t="n">
-        <v>17393590.25296653</v>
+        <v>17843350.14591356</v>
       </c>
       <c r="O2" t="n">
-        <v>33638884.23680163</v>
+        <v>17317929.24645062</v>
       </c>
       <c r="P2" t="n">
-        <v>42113286.28845543</v>
+        <v>44742786.74644543</v>
       </c>
       <c r="Q2" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R2" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S2" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="3">
@@ -6636,7 +4684,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6645,46 +4693,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-291.4274560101209</v>
+        <v>-291.2522339491474</v>
       </c>
       <c r="G3" t="n">
-        <v>-265.082172843706</v>
+        <v>-261.8358097230544</v>
       </c>
       <c r="H3" t="n">
-        <v>63535860.89660419</v>
+        <v>55075575.31428906</v>
       </c>
       <c r="I3" t="n">
-        <v>51223126.29020963</v>
+        <v>42263501.98832518</v>
       </c>
       <c r="J3" t="n">
-        <v>6.844367240826895</v>
+        <v>5.600372479591252</v>
       </c>
       <c r="K3" t="n">
-        <v>63535860.89660419</v>
+        <v>55075575.31428906</v>
       </c>
       <c r="L3" t="n">
-        <v>88363741.79397143</v>
+        <v>74771715.99281029</v>
       </c>
       <c r="M3" t="n">
-        <v>82853442.14211747</v>
+        <v>76808160.79530102</v>
       </c>
       <c r="N3" t="n">
-        <v>71526418.73777196</v>
+        <v>82556078.67443156</v>
       </c>
       <c r="O3" t="n">
-        <v>86396450.11585179</v>
+        <v>78244145.28519912</v>
       </c>
       <c r="P3" t="n">
-        <v>198030961.3447905</v>
+        <v>196518665.9472979</v>
       </c>
       <c r="Q3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R3" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S3" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="4">
@@ -6714,46 +4762,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-276.7430060146413</v>
+        <v>-282.0161545226933</v>
       </c>
       <c r="G4" t="n">
-        <v>-253.3831586080163</v>
+        <v>-258.5403630576478</v>
       </c>
       <c r="H4" t="n">
-        <v>134168310.8420942</v>
+        <v>133661038.3478121</v>
       </c>
       <c r="I4" t="n">
-        <v>91574635.60463881</v>
+        <v>91946907.70086189</v>
       </c>
       <c r="J4" t="n">
-        <v>6.482425380782803</v>
+        <v>6.48017303171234</v>
       </c>
       <c r="K4" t="n">
-        <v>144793037.1485734</v>
+        <v>144987948.9357656</v>
       </c>
       <c r="L4" t="n">
-        <v>136344076.646068</v>
+        <v>135036993.6865501</v>
       </c>
       <c r="M4" t="n">
-        <v>134168310.8420942</v>
+        <v>133661038.3478121</v>
       </c>
       <c r="N4" t="n">
-        <v>139742770.7776461</v>
+        <v>143260655.6068596</v>
       </c>
       <c r="O4" t="n">
-        <v>136847698.2462698</v>
+        <v>173607085.4834566</v>
       </c>
       <c r="P4" t="n">
-        <v>242495018.1198631</v>
+        <v>243158498.0800611</v>
       </c>
       <c r="Q4" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R4" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S4" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="5">
@@ -6764,65 +4812,65 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
+          <t>SARIMAX_pib_var_mom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(2, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(1, 0, 0, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-214.6061246367365</v>
+        <v>-223.2459871345233</v>
       </c>
       <c r="G5" t="n">
-        <v>-191.1880951554789</v>
+        <v>-199.7701956694778</v>
       </c>
       <c r="H5" t="n">
-        <v>10863601.68149797</v>
+        <v>9913687.250227692</v>
       </c>
       <c r="I5" t="n">
-        <v>8507777.370291825</v>
+        <v>8174359.309652234</v>
       </c>
       <c r="J5" t="n">
-        <v>6.593113522145604</v>
+        <v>6.118906658714742</v>
       </c>
       <c r="K5" t="n">
-        <v>10863601.68149797</v>
+        <v>11406526.79473003</v>
       </c>
       <c r="L5" t="n">
-        <v>15992255.71751611</v>
+        <v>14583642.49745251</v>
       </c>
       <c r="M5" t="n">
-        <v>16729306.83044146</v>
+        <v>9913687.250227692</v>
       </c>
       <c r="N5" t="n">
-        <v>27494288.5735496</v>
+        <v>14531857.0301384</v>
       </c>
       <c r="O5" t="n">
-        <v>26397535.32865553</v>
+        <v>23111672.13035361</v>
       </c>
       <c r="P5" t="n">
-        <v>28441646.44702839</v>
+        <v>28953156.92945905</v>
       </c>
       <c r="Q5" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R5" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S5" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="6">
@@ -6833,13 +4881,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SARIMA_puro</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>SARIMAX_dummies</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6848,46 +4900,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-312.2201021135799</v>
+        <v>-328.0316935266717</v>
       </c>
       <c r="G6" t="n">
-        <v>-288.8602547069549</v>
+        <v>-304.5559020616262</v>
       </c>
       <c r="H6" t="n">
-        <v>213698388.3999594</v>
+        <v>216701897.5541917</v>
       </c>
       <c r="I6" t="n">
-        <v>148066358.3187708</v>
+        <v>170003852.5213653</v>
       </c>
       <c r="J6" t="n">
-        <v>4.211159847259829</v>
+        <v>4.87354121090731</v>
       </c>
       <c r="K6" t="n">
-        <v>254904011.1805611</v>
+        <v>344435771.2085369</v>
       </c>
       <c r="L6" t="n">
-        <v>236485589.0507077</v>
+        <v>227831479.1443118</v>
       </c>
       <c r="M6" t="n">
-        <v>267442723.4496782</v>
+        <v>281853886.6734993</v>
       </c>
       <c r="N6" t="n">
-        <v>226518007.5004999</v>
+        <v>216701897.5541917</v>
       </c>
       <c r="O6" t="n">
-        <v>213698388.3999594</v>
+        <v>304589928.6115661</v>
       </c>
       <c r="P6" t="n">
-        <v>726678630.1862638</v>
+        <v>729104858.3716953</v>
       </c>
       <c r="Q6" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R6" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="7">
@@ -6898,17 +4950,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib</t>
+          <t>SARIMAX_pib_var_12m</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>pib_var_12m</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -6917,46 +4969,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-338.8828405491917</v>
+        <v>-337.1456488831431</v>
       </c>
       <c r="G7" t="n">
-        <v>-312.5375573827769</v>
+        <v>-304.8664356187055</v>
       </c>
       <c r="H7" t="n">
-        <v>90803865.16074952</v>
+        <v>81221941.85470641</v>
       </c>
       <c r="I7" t="n">
-        <v>74723185.59601349</v>
+        <v>67790952.04753745</v>
       </c>
       <c r="J7" t="n">
-        <v>4.337733533537921</v>
+        <v>3.847406663139551</v>
       </c>
       <c r="K7" t="n">
-        <v>90803865.16074952</v>
+        <v>147239914.2278383</v>
       </c>
       <c r="L7" t="n">
-        <v>141906514.1732701</v>
+        <v>81221941.85470641</v>
       </c>
       <c r="M7" t="n">
-        <v>194142644.296387</v>
+        <v>214331424.2485079</v>
       </c>
       <c r="N7" t="n">
-        <v>172667910.5198847</v>
+        <v>208483025.5770078</v>
       </c>
       <c r="O7" t="n">
-        <v>137665621.3085402</v>
+        <v>141031871.459946</v>
       </c>
       <c r="P7" t="n">
-        <v>377773320.7932717</v>
+        <v>402271500.880136</v>
       </c>
       <c r="Q7" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R7" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S7" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="8">
@@ -6967,61 +5019,65 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SARIMA_puro</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>SARIMAX_log_pib</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(2, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(1, 0, 0, 12)</t>
+          <t>(0, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-346.3300032732141</v>
+        <v>-346.8712838996037</v>
       </c>
       <c r="G8" t="n">
-        <v>-328.8101177182453</v>
+        <v>-323.3381445187292</v>
       </c>
       <c r="H8" t="n">
-        <v>120834869.9249941</v>
+        <v>94029211.74541552</v>
       </c>
       <c r="I8" t="n">
-        <v>97305991.81458411</v>
+        <v>73159259.84535858</v>
       </c>
       <c r="J8" t="n">
-        <v>8.958845607591947</v>
+        <v>6.69397673683787</v>
       </c>
       <c r="K8" t="n">
-        <v>162061299.9278821</v>
+        <v>94029211.74541552</v>
       </c>
       <c r="L8" t="n">
-        <v>145944502.432165</v>
+        <v>132952043.9176872</v>
       </c>
       <c r="M8" t="n">
-        <v>167474970.3173492</v>
+        <v>136047490.1267437</v>
       </c>
       <c r="N8" t="n">
-        <v>120996757.1266413</v>
+        <v>116796961.5573121</v>
       </c>
       <c r="O8" t="n">
-        <v>120834869.9249941</v>
+        <v>135505109.4219157</v>
       </c>
       <c r="P8" t="n">
-        <v>245558105.0716324</v>
+        <v>256689873.78783</v>
       </c>
       <c r="Q8" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="9">
@@ -7042,55 +5098,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(0, 0, 1, 12)</t>
+          <t>(0, 0, 0, 12)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-318.2657083551018</v>
+        <v>-321.1624287470828</v>
       </c>
       <c r="G9" t="n">
-        <v>-294.8476788738442</v>
+        <v>-294.6876469435991</v>
       </c>
       <c r="H9" t="n">
-        <v>104357890.6127599</v>
+        <v>125560317.3447878</v>
       </c>
       <c r="I9" t="n">
-        <v>81385221.48405445</v>
+        <v>97977205.67437406</v>
       </c>
       <c r="J9" t="n">
-        <v>4.488484817065559</v>
+        <v>5.176318492596337</v>
       </c>
       <c r="K9" t="n">
-        <v>104357890.6127599</v>
+        <v>125560317.3447878</v>
       </c>
       <c r="L9" t="n">
-        <v>171834822.0846914</v>
+        <v>171219837.5016599</v>
       </c>
       <c r="M9" t="n">
-        <v>349254126.6394918</v>
+        <v>160629521.0560497</v>
       </c>
       <c r="N9" t="n">
-        <v>138222524.7944777</v>
+        <v>142951243.3328057</v>
       </c>
       <c r="O9" t="n">
-        <v>145450030.4714171</v>
+        <v>145763616.1596485</v>
       </c>
       <c r="P9" t="n">
-        <v>451373434.3417343</v>
+        <v>460140017.8993087</v>
       </c>
       <c r="Q9" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R9" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="10">
@@ -7116,50 +5172,50 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(1, 0, 0, 12)</t>
+          <t>(1, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-396.7169139430864</v>
+        <v>-401.1270382625303</v>
       </c>
       <c r="G10" t="n">
-        <v>-373.2988844618288</v>
+        <v>-374.6522564590466</v>
       </c>
       <c r="H10" t="n">
-        <v>174570940.2476049</v>
+        <v>130003592.4520796</v>
       </c>
       <c r="I10" t="n">
-        <v>137809857.1766118</v>
+        <v>92546828.81827915</v>
       </c>
       <c r="J10" t="n">
-        <v>5.451273244677999</v>
+        <v>3.603387611017798</v>
       </c>
       <c r="K10" t="n">
-        <v>174570940.2476049</v>
+        <v>130003592.4520796</v>
       </c>
       <c r="L10" t="n">
-        <v>369374764.1898875</v>
+        <v>274787849.7280935</v>
       </c>
       <c r="M10" t="n">
-        <v>214267926.7732769</v>
+        <v>157672641.9192771</v>
       </c>
       <c r="N10" t="n">
-        <v>212822085.4832594</v>
+        <v>154562735.6791958</v>
       </c>
       <c r="O10" t="n">
-        <v>437661139.5033857</v>
+        <v>345209597.4599652</v>
       </c>
       <c r="P10" t="n">
-        <v>615699989.4908388</v>
+        <v>632800784.0883782</v>
       </c>
       <c r="Q10" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R10" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="11">
@@ -7170,17 +5226,13 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SARIMAX_dummies</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>dummies</t>
-        </is>
-      </c>
+          <t>SARIMA_puro</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7189,46 +5241,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-169.7145019924179</v>
+        <v>-154.9877731150171</v>
       </c>
       <c r="G11" t="n">
-        <v>-146.3546545857929</v>
+        <v>-140.3154034493636</v>
       </c>
       <c r="H11" t="n">
-        <v>197461454.8658045</v>
+        <v>181822127.4185804</v>
       </c>
       <c r="I11" t="n">
-        <v>157710078.1308893</v>
+        <v>114249486.6948304</v>
       </c>
       <c r="J11" t="n">
-        <v>12.92540448448853</v>
+        <v>10.37071090876976</v>
       </c>
       <c r="K11" t="n">
-        <v>310354624.2962399</v>
+        <v>185235499.775006</v>
       </c>
       <c r="L11" t="n">
-        <v>221150640.9153607</v>
+        <v>201346343.1929713</v>
       </c>
       <c r="M11" t="n">
-        <v>198186755.389875</v>
+        <v>189621293.7616771</v>
       </c>
       <c r="N11" t="n">
-        <v>197461454.8658045</v>
+        <v>192113851.0742797</v>
       </c>
       <c r="O11" t="n">
-        <v>407916021.9434373</v>
+        <v>181822127.4185804</v>
       </c>
       <c r="P11" t="n">
-        <v>424340351.1487547</v>
+        <v>470335448.4504371</v>
       </c>
       <c r="Q11" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R11" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S11" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="12">
@@ -7254,46 +5306,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-364.8174601334998</v>
+        <v>-367.7667485619788</v>
       </c>
       <c r="G12" t="n">
-        <v>-347.2975745785311</v>
+        <v>-350.1599049631947</v>
       </c>
       <c r="H12" t="n">
-        <v>298312106.3247675</v>
+        <v>273094711.8957458</v>
       </c>
       <c r="I12" t="n">
-        <v>236183459.9497047</v>
+        <v>220586296.3115093</v>
       </c>
       <c r="J12" t="n">
-        <v>3.383951232623334</v>
+        <v>3.124194472550007</v>
       </c>
       <c r="K12" t="n">
-        <v>374356968.8676563</v>
+        <v>474636988.0974531</v>
       </c>
       <c r="L12" t="n">
-        <v>450802419.9826454</v>
+        <v>447289275.4861051</v>
       </c>
       <c r="M12" t="n">
-        <v>547932771.1454333</v>
+        <v>547144189.9676397</v>
       </c>
       <c r="N12" t="n">
-        <v>511496634.5133468</v>
+        <v>277965627.4088016</v>
       </c>
       <c r="O12" t="n">
-        <v>298312106.3247675</v>
+        <v>273094711.8957458</v>
       </c>
       <c r="P12" t="n">
-        <v>1383077604.958836</v>
+        <v>1393753555.776618</v>
       </c>
       <c r="Q12" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R12" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S12" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="13">
@@ -7323,46 +5375,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-412.6151574952773</v>
+        <v>-420.6311726847232</v>
       </c>
       <c r="G13" t="n">
-        <v>-386.3353291628242</v>
+        <v>-394.220907286547</v>
       </c>
       <c r="H13" t="n">
-        <v>63712992.2956339</v>
+        <v>66314834.94632042</v>
       </c>
       <c r="I13" t="n">
-        <v>51819180.75845337</v>
+        <v>56020479.31615689</v>
       </c>
       <c r="J13" t="n">
-        <v>3.610782989800845</v>
+        <v>3.884462155483766</v>
       </c>
       <c r="K13" t="n">
-        <v>69292144.47078723</v>
+        <v>74153941.30316235</v>
       </c>
       <c r="L13" t="n">
-        <v>63712992.2956339</v>
+        <v>66314834.94632042</v>
       </c>
       <c r="M13" t="n">
-        <v>77799513.98984027</v>
+        <v>79819270.22953856</v>
       </c>
       <c r="N13" t="n">
-        <v>65143191.15142557</v>
+        <v>70480209.41456063</v>
       </c>
       <c r="O13" t="n">
-        <v>99894251.28834918</v>
+        <v>103293953.2890868</v>
       </c>
       <c r="P13" t="n">
-        <v>228864798.5551459</v>
+        <v>229142000.9909791</v>
       </c>
       <c r="Q13" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R13" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S13" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="14">
@@ -7392,46 +5444,46 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-259.0085548189801</v>
+        <v>-265.0335217054204</v>
       </c>
       <c r="G14" t="n">
-        <v>-235.5905253377225</v>
+        <v>-241.500382324546</v>
       </c>
       <c r="H14" t="n">
-        <v>118246482.4426879</v>
+        <v>106350178.281012</v>
       </c>
       <c r="I14" t="n">
-        <v>100208740.0438107</v>
+        <v>81126640.25771201</v>
       </c>
       <c r="J14" t="n">
-        <v>4.752342584623371</v>
+        <v>3.944541644514606</v>
       </c>
       <c r="K14" t="n">
-        <v>118246482.4426879</v>
+        <v>106350178.281012</v>
       </c>
       <c r="L14" t="n">
-        <v>157277331.6072137</v>
+        <v>134380451.3572981</v>
       </c>
       <c r="M14" t="n">
-        <v>144767237.2729962</v>
+        <v>412308588.995541</v>
       </c>
       <c r="N14" t="n">
-        <v>241522602.8744147</v>
+        <v>124964411.4402131</v>
       </c>
       <c r="O14" t="n">
-        <v>195908349.6183568</v>
+        <v>208225202.4231481</v>
       </c>
       <c r="P14" t="n">
-        <v>483367795.4396541</v>
+        <v>492671857.5572779</v>
       </c>
       <c r="Q14" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R14" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S14" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="15">
@@ -7442,17 +5494,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SARIMAX_dummies</t>
+          <t>SARIMAX_pib_var_mom</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dummies</t>
+          <t>pib_var_mom</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7461,46 +5513,46 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-278.7041734852306</v>
+        <v>-292.9070024484278</v>
       </c>
       <c r="G15" t="n">
-        <v>-258.2643070044338</v>
+        <v>-266.4967370502516</v>
       </c>
       <c r="H15" t="n">
-        <v>154029194.9034608</v>
+        <v>148219831.1340747</v>
       </c>
       <c r="I15" t="n">
-        <v>90090254.19661255</v>
+        <v>97580440.04463881</v>
       </c>
       <c r="J15" t="n">
-        <v>4.099874619322526</v>
+        <v>4.493054463483832</v>
       </c>
       <c r="K15" t="n">
-        <v>267431863.3625906</v>
+        <v>190222058.1668349</v>
       </c>
       <c r="L15" t="n">
-        <v>173535470.9124513</v>
+        <v>150693257.664377</v>
       </c>
       <c r="M15" t="n">
-        <v>175048277.1866445</v>
+        <v>148219831.1340747</v>
       </c>
       <c r="N15" t="n">
-        <v>154029194.9034608</v>
+        <v>149843213.0195982</v>
       </c>
       <c r="O15" t="n">
-        <v>154111392.8781591</v>
+        <v>149440118.4524451</v>
       </c>
       <c r="P15" t="n">
-        <v>460870867.8658751</v>
+        <v>442017484.7281109</v>
       </c>
       <c r="Q15" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R15" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="16">
@@ -7521,7 +5573,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7530,46 +5582,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-355.8678370676713</v>
+        <v>-356.2128317757447</v>
       </c>
       <c r="G16" t="n">
-        <v>-326.5953002160992</v>
+        <v>-329.738049972261</v>
       </c>
       <c r="H16" t="n">
-        <v>56081710.5778802</v>
+        <v>94667487.53532825</v>
       </c>
       <c r="I16" t="n">
-        <v>42128921.60818936</v>
+        <v>80474059.06651378</v>
       </c>
       <c r="J16" t="n">
-        <v>4.862533227567367</v>
+        <v>9.106906472840235</v>
       </c>
       <c r="K16" t="n">
-        <v>56081710.5778802</v>
+        <v>94667487.53532825</v>
       </c>
       <c r="L16" t="n">
-        <v>118763615.3188237</v>
+        <v>122907732.4350661</v>
       </c>
       <c r="M16" t="n">
-        <v>115769764.5599601</v>
+        <v>126259517.4145337</v>
       </c>
       <c r="N16" t="n">
-        <v>124277293.3803288</v>
+        <v>130187331.9491408</v>
       </c>
       <c r="O16" t="n">
-        <v>94307317.57412636</v>
+        <v>102214277.5101939</v>
       </c>
       <c r="P16" t="n">
-        <v>216441562.2432064</v>
+        <v>218595563.8624136</v>
       </c>
       <c r="Q16" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R16" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S16" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="17">
@@ -7580,13 +5632,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SARIMA_puro</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>SARIMAX_log_pib</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7595,46 +5651,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-281.3774523367415</v>
+        <v>-282.0633573647343</v>
       </c>
       <c r="G17" t="n">
-        <v>-263.8575667817727</v>
+        <v>-255.5885755612506</v>
       </c>
       <c r="H17" t="n">
-        <v>192289171.195481</v>
+        <v>225787672.1534011</v>
       </c>
       <c r="I17" t="n">
-        <v>163683517.995622</v>
+        <v>190351645.7222713</v>
       </c>
       <c r="J17" t="n">
-        <v>7.172515032112607</v>
+        <v>8.338873856322719</v>
       </c>
       <c r="K17" t="n">
-        <v>269357381.969035</v>
+        <v>225787672.1534011</v>
       </c>
       <c r="L17" t="n">
-        <v>220675125.0643624</v>
+        <v>265662687.9062502</v>
       </c>
       <c r="M17" t="n">
-        <v>439340840.8023409</v>
+        <v>256452493.8665371</v>
       </c>
       <c r="N17" t="n">
-        <v>388591901.381788</v>
+        <v>342005527.1709642</v>
       </c>
       <c r="O17" t="n">
-        <v>192289171.195481</v>
+        <v>537556018.1283146</v>
       </c>
       <c r="P17" t="n">
-        <v>539819620.1131917</v>
+        <v>552520194.3425807</v>
       </c>
       <c r="Q17" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R17" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S17" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="18">
@@ -7645,17 +5701,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SARIMAX_pib_var_mom+out2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>pib_var_mom</t>
-        </is>
-      </c>
+          <t>SARIMA_puro+out3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7664,46 +5716,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>-252.7649157209385</v>
+        <v>-284.1716940737806</v>
       </c>
       <c r="G18" t="n">
-        <v>-220.6451255368291</v>
+        <v>-251.892480809343</v>
       </c>
       <c r="H18" t="n">
-        <v>70176047.09088023</v>
+        <v>71280815.71095912</v>
       </c>
       <c r="I18" t="n">
-        <v>60361307.38145865</v>
+        <v>61759333.2875015</v>
       </c>
       <c r="J18" t="n">
-        <v>8.486812983311601</v>
+        <v>8.545083248920573</v>
       </c>
       <c r="K18" t="n">
-        <v>282419979.2762337</v>
+        <v>324201699.3665773</v>
       </c>
       <c r="L18" t="n">
-        <v>74791281.81350578</v>
+        <v>76786756.09524281</v>
       </c>
       <c r="M18" t="n">
-        <v>70176047.09088023</v>
+        <v>73825895.17185599</v>
       </c>
       <c r="N18" t="n">
-        <v>78712944.74636102</v>
+        <v>81632319.42700239</v>
       </c>
       <c r="O18" t="n">
-        <v>77454216.03103282</v>
+        <v>71280815.71095912</v>
       </c>
       <c r="P18" t="n">
-        <v>195062375.6595871</v>
+        <v>193320814.5128967</v>
       </c>
       <c r="Q18" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R18" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S18" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="19">
@@ -7714,17 +5766,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib+out3</t>
+          <t>SARIMAX_dummies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>log_pib</t>
+          <t>dummies</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(2, 1, 0)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7733,46 +5785,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-308.8108388950645</v>
+        <v>-273.5519235473678</v>
       </c>
       <c r="G19" t="n">
-        <v>-276.6110483583353</v>
+        <v>-250.0761320823223</v>
       </c>
       <c r="H19" t="n">
-        <v>305475920.3893557</v>
+        <v>290691264.1066064</v>
       </c>
       <c r="I19" t="n">
-        <v>231699586.7426058</v>
+        <v>235474365.9086459</v>
       </c>
       <c r="J19" t="n">
-        <v>5.221040292277473</v>
+        <v>5.258583951851528</v>
       </c>
       <c r="K19" t="n">
-        <v>305475920.3893557</v>
+        <v>296603234.4811639</v>
       </c>
       <c r="L19" t="n">
-        <v>586692279.0260884</v>
+        <v>527323592.2868596</v>
       </c>
       <c r="M19" t="n">
-        <v>572628194.6283358</v>
+        <v>431972830.6329582</v>
       </c>
       <c r="N19" t="n">
-        <v>491352623.1085382</v>
+        <v>290691264.1066064</v>
       </c>
       <c r="O19" t="n">
-        <v>470989478.302508</v>
+        <v>417392482.6071773</v>
       </c>
       <c r="P19" t="n">
-        <v>1069207682.104888</v>
+        <v>1073019805.589406</v>
       </c>
       <c r="Q19" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R19" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S19" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="20">
@@ -7802,46 +5854,46 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-274.9629020441197</v>
+        <v>-278.1528188399556</v>
       </c>
       <c r="G20" t="n">
-        <v>-248.6176188777048</v>
+        <v>-251.6780370364718</v>
       </c>
       <c r="H20" t="n">
-        <v>422658906.0730223</v>
+        <v>420796040.1598482</v>
       </c>
       <c r="I20" t="n">
-        <v>342752256.1069026</v>
+        <v>339401916.8885447</v>
       </c>
       <c r="J20" t="n">
-        <v>6.519380450760765</v>
+        <v>6.350809300527849</v>
       </c>
       <c r="K20" t="n">
-        <v>422658906.0730223</v>
+        <v>420796040.1598482</v>
       </c>
       <c r="L20" t="n">
-        <v>950159370.0604625</v>
+        <v>1042035953.514092</v>
       </c>
       <c r="M20" t="n">
-        <v>1057887719.909913</v>
+        <v>1122278167.931468</v>
       </c>
       <c r="N20" t="n">
-        <v>993067009.0586839</v>
+        <v>1087960217.91148</v>
       </c>
       <c r="O20" t="n">
-        <v>975267872.9211905</v>
+        <v>1070738575.609371</v>
       </c>
       <c r="P20" t="n">
-        <v>1260615029.784826</v>
+        <v>1334690065.496534</v>
       </c>
       <c r="Q20" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R20" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S20" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="21">
@@ -7852,13 +5904,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SARIMA_puro+out3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>SARIMAX_log_pib</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>log_pib</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(0, 0, 2)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -7867,46 +5923,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-319.8448797704586</v>
+        <v>-291.7969569236124</v>
       </c>
       <c r="G21" t="n">
-        <v>-293.5650514380055</v>
+        <v>-265.3221751201286</v>
       </c>
       <c r="H21" t="n">
-        <v>69137741.01334783</v>
+        <v>68908992.38690336</v>
       </c>
       <c r="I21" t="n">
-        <v>48596173.34259854</v>
+        <v>53558485.03682414</v>
       </c>
       <c r="J21" t="n">
-        <v>6.343159812885289</v>
+        <v>7.166024215363788</v>
       </c>
       <c r="K21" t="n">
-        <v>69770040.555581</v>
+        <v>68908992.38690336</v>
       </c>
       <c r="L21" t="n">
-        <v>69252315.15635073</v>
+        <v>69605484.23048119</v>
       </c>
       <c r="M21" t="n">
-        <v>96613350.15746953</v>
+        <v>80938612.75028172</v>
       </c>
       <c r="N21" t="n">
-        <v>73336280.91090848</v>
+        <v>75332572.24029633</v>
       </c>
       <c r="O21" t="n">
-        <v>69137741.01334783</v>
+        <v>71722810.47088422</v>
       </c>
       <c r="P21" t="n">
-        <v>161731204.2128137</v>
+        <v>156660551.189118</v>
       </c>
       <c r="Q21" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R21" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S21" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="22">
@@ -7936,46 +5992,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-255.3188467271003</v>
+        <v>-240.288823639852</v>
       </c>
       <c r="G22" t="n">
-        <v>-228.9735635606855</v>
+        <v>-213.8140418363682</v>
       </c>
       <c r="H22" t="n">
-        <v>52660462.26085785</v>
+        <v>88728995.66156217</v>
       </c>
       <c r="I22" t="n">
-        <v>40204427.30909246</v>
+        <v>53725534.56991363</v>
       </c>
       <c r="J22" t="n">
-        <v>6.339050364506233</v>
+        <v>7.472668152482384</v>
       </c>
       <c r="K22" t="n">
-        <v>52660462.26085785</v>
+        <v>88728995.66156217</v>
       </c>
       <c r="L22" t="n">
-        <v>83165768.75407654</v>
+        <v>118013923.260794</v>
       </c>
       <c r="M22" t="n">
-        <v>80331853.50985606</v>
+        <v>126665153.5316713</v>
       </c>
       <c r="N22" t="n">
-        <v>65865453.7475109</v>
+        <v>100627917.8869946</v>
       </c>
       <c r="O22" t="n">
-        <v>63214173.39137055</v>
+        <v>97992549.35215341</v>
       </c>
       <c r="P22" t="n">
-        <v>173670797.85964</v>
+        <v>202406802.0212476</v>
       </c>
       <c r="Q22" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R22" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S22" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="23">
@@ -7986,10 +6042,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SARIMA_puro+out2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>SARIMAX_dummies</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dummies</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>(0, 1, 1)</t>
@@ -8001,46 +6061,46 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-306.4935289535435</v>
+        <v>-286.730651041451</v>
       </c>
       <c r="G23" t="n">
-        <v>-286.0536624727467</v>
+        <v>-266.1893335095361</v>
       </c>
       <c r="H23" t="n">
-        <v>12165163.83070321</v>
+        <v>12408268.72429977</v>
       </c>
       <c r="I23" t="n">
-        <v>10307341.55970282</v>
+        <v>10352445.83678635</v>
       </c>
       <c r="J23" t="n">
-        <v>5.933407938158129</v>
+        <v>5.934478104083206</v>
       </c>
       <c r="K23" t="n">
-        <v>22188670.24826225</v>
+        <v>36798072.54739226</v>
       </c>
       <c r="L23" t="n">
-        <v>16186779.18073217</v>
+        <v>15253211.16830272</v>
       </c>
       <c r="M23" t="n">
-        <v>14538365.77345017</v>
+        <v>15086038.96187033</v>
       </c>
       <c r="N23" t="n">
-        <v>14976659.01848167</v>
+        <v>12408268.72429977</v>
       </c>
       <c r="O23" t="n">
-        <v>12165163.83070321</v>
+        <v>14894246.71068129</v>
       </c>
       <c r="P23" t="n">
-        <v>42715925.88715092</v>
+        <v>41903357.83090895</v>
       </c>
       <c r="Q23" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R23" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S23" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="24">
@@ -8066,50 +6126,50 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(1, 0, 1, 12)</t>
+          <t>(1, 0, 0, 12)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-247.5585123060411</v>
+        <v>-246.1838557462025</v>
       </c>
       <c r="G24" t="n">
-        <v>-221.2786839735879</v>
+        <v>-222.708064281157</v>
       </c>
       <c r="H24" t="n">
-        <v>347768023.1038877</v>
+        <v>365614163.5867174</v>
       </c>
       <c r="I24" t="n">
-        <v>246387726.7333618</v>
+        <v>275517454.4154227</v>
       </c>
       <c r="J24" t="n">
-        <v>5.561669663212775</v>
+        <v>6.285208434935575</v>
       </c>
       <c r="K24" t="n">
-        <v>441411419.7484601</v>
+        <v>371834627.3479339</v>
       </c>
       <c r="L24" t="n">
-        <v>347768023.1038877</v>
+        <v>365614163.5867174</v>
       </c>
       <c r="M24" t="n">
-        <v>667061693.0001653</v>
+        <v>485226650.3366629</v>
       </c>
       <c r="N24" t="n">
-        <v>668056734.9940549</v>
+        <v>494838681.9111412</v>
       </c>
       <c r="O24" t="n">
-        <v>706471403.3852874</v>
+        <v>543208277.8542451</v>
       </c>
       <c r="P24" t="n">
-        <v>912412564.5440662</v>
+        <v>899296185.2693682</v>
       </c>
       <c r="Q24" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R24" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="25">
@@ -8139,46 +6199,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-333.1261819472227</v>
+        <v>-337.6324696746041</v>
       </c>
       <c r="G25" t="n">
-        <v>-295.166429911457</v>
+        <v>-299.4843085439051</v>
       </c>
       <c r="H25" t="n">
-        <v>146845962.277753</v>
+        <v>160026689.0674368</v>
       </c>
       <c r="I25" t="n">
-        <v>111389439.7934123</v>
+        <v>124128266.7879635</v>
       </c>
       <c r="J25" t="n">
-        <v>3.009185278176846</v>
+        <v>3.320540679328427</v>
       </c>
       <c r="K25" t="n">
-        <v>342495335.0072939</v>
+        <v>350756421.6841555</v>
       </c>
       <c r="L25" t="n">
-        <v>146845962.277753</v>
+        <v>160026689.0674368</v>
       </c>
       <c r="M25" t="n">
-        <v>188406711.2413476</v>
+        <v>166212287.4444202</v>
       </c>
       <c r="N25" t="n">
-        <v>156084495.6119549</v>
+        <v>163640061.1628552</v>
       </c>
       <c r="O25" t="n">
-        <v>225199016.5730371</v>
+        <v>219805267.0133897</v>
       </c>
       <c r="P25" t="n">
-        <v>885585493.4971564</v>
+        <v>876791419.4790629</v>
       </c>
       <c r="Q25" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R25" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="26">
@@ -8208,46 +6268,46 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-322.0435531272685</v>
+        <v>-329.5451599821236</v>
       </c>
       <c r="G26" t="n">
-        <v>-295.6982699608537</v>
+        <v>-303.0703781786398</v>
       </c>
       <c r="H26" t="n">
-        <v>21508299.82748034</v>
+        <v>23497654.86164366</v>
       </c>
       <c r="I26" t="n">
-        <v>15800196.54961447</v>
+        <v>17546602.91240829</v>
       </c>
       <c r="J26" t="n">
-        <v>3.126693472213432</v>
+        <v>3.457822902559572</v>
       </c>
       <c r="K26" t="n">
-        <v>21508299.82748034</v>
+        <v>23497654.86164366</v>
       </c>
       <c r="L26" t="n">
-        <v>44729517.74304114</v>
+        <v>38753483.96821985</v>
       </c>
       <c r="M26" t="n">
-        <v>43033730.89759567</v>
+        <v>37785843.67950209</v>
       </c>
       <c r="N26" t="n">
-        <v>48451244.53657837</v>
+        <v>38513400.538434</v>
       </c>
       <c r="O26" t="n">
-        <v>41822408.20484929</v>
+        <v>44357335.09486744</v>
       </c>
       <c r="P26" t="n">
-        <v>108167767.1289065</v>
+        <v>103958261.3128892</v>
       </c>
       <c r="Q26" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R26" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S26" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="27">
@@ -8258,7 +6318,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARIMAX_log_pib+out4</t>
+          <t>SARIMAX_log_pib</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8268,55 +6328,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(1, 0, 1, 12)</t>
+          <t>(0, 0, 1, 12)</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-394.7579600965331</v>
+        <v>-397.9548771170472</v>
       </c>
       <c r="G27" t="n">
-        <v>-359.6309158746466</v>
+        <v>-368.5384528909541</v>
       </c>
       <c r="H27" t="n">
-        <v>997854603.4392191</v>
+        <v>1071466545.895074</v>
       </c>
       <c r="I27" t="n">
-        <v>849988457.4154634</v>
+        <v>907080894.2669778</v>
       </c>
       <c r="J27" t="n">
-        <v>4.362314105564112</v>
+        <v>4.674495863890511</v>
       </c>
       <c r="K27" t="n">
-        <v>997854603.4392191</v>
+        <v>1071466545.895074</v>
       </c>
       <c r="L27" t="n">
-        <v>3844528940.798631</v>
+        <v>2295927917.232726</v>
       </c>
       <c r="M27" t="n">
-        <v>3821954028.960672</v>
+        <v>1649669017.874381</v>
       </c>
       <c r="N27" t="n">
-        <v>1932779065.29304</v>
+        <v>1620090724.192588</v>
       </c>
       <c r="O27" t="n">
-        <v>3620424543.372721</v>
+        <v>3051656616.125039</v>
       </c>
       <c r="P27" t="n">
-        <v>3358208685.448835</v>
+        <v>3586733012.50486</v>
       </c>
       <c r="Q27" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R27" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="28">
@@ -8337,7 +6397,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8346,46 +6406,46 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-351.4922305992045</v>
+        <v>-377.3138452772674</v>
       </c>
       <c r="G28" t="n">
-        <v>-322.2196937476324</v>
+        <v>-350.8390634737837</v>
       </c>
       <c r="H28" t="n">
-        <v>25149890.42176</v>
+        <v>21518766.71477059</v>
       </c>
       <c r="I28" t="n">
-        <v>20943027.09267654</v>
+        <v>18165209.96853181</v>
       </c>
       <c r="J28" t="n">
-        <v>4.066728293042162</v>
+        <v>3.496344765695634</v>
       </c>
       <c r="K28" t="n">
-        <v>25149890.42176</v>
+        <v>21518766.71477059</v>
       </c>
       <c r="L28" t="n">
-        <v>34726377.48642625</v>
+        <v>27031349.09121908</v>
       </c>
       <c r="M28" t="n">
-        <v>36602884.48474922</v>
+        <v>26786570.04178364</v>
       </c>
       <c r="N28" t="n">
-        <v>38210642.81030507</v>
+        <v>28735898.21937118</v>
       </c>
       <c r="O28" t="n">
-        <v>28266420.23264162</v>
+        <v>29538481.32832102</v>
       </c>
       <c r="P28" t="n">
-        <v>132634655.1771429</v>
+        <v>128305572.4311414</v>
       </c>
       <c r="Q28" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R28" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="S28" s="1" t="n">
-        <v>46174</v>
+        <v>46235</v>
       </c>
     </row>
   </sheetData>
